--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -634,7 +634,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -1641,7 +1641,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.11"/>
@@ -2645,7 +2645,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -4138,7 +4138,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -5619,7 +5619,7 @@
         <v>83</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>1</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G37" s="3" t="n">
         <f aca="false">ROUND(F37*0.0025,0)*D37</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>59</v>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -415,7 +415,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -436,7 +435,6 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="127">
   <si>
     <t xml:space="preserve">neurons</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t xml:space="preserve">Simulated_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta_eta</t>
   </si>
   <si>
     <t xml:space="preserve">Axo-Axonic</t>
@@ -415,6 +418,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -435,6 +439,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -479,7 +484,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -505,6 +510,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -632,7 +641,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -1639,7 +1648,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.11"/>
@@ -2643,7 +2652,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -4135,8 +4144,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P42"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -4197,16 +4206,19 @@
       <c r="O1" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="P1" s="7" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
@@ -4241,6 +4253,9 @@
       </c>
       <c r="N2" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4248,10 +4263,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
@@ -4286,10 +4301,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
@@ -4324,10 +4339,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>1</v>
@@ -4362,6 +4377,9 @@
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4369,10 +4387,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
@@ -4407,10 +4425,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
@@ -4445,6 +4463,9 @@
       </c>
       <c r="N7" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4452,10 +4473,10 @@
         <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1</v>
@@ -4489,6 +4510,9 @@
       </c>
       <c r="N8" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4496,10 +4520,10 @@
         <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -4535,10 +4559,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
@@ -4572,6 +4596,9 @@
       </c>
       <c r="N10" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4579,10 +4606,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>1</v>
@@ -4617,10 +4644,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>1</v>
@@ -4656,10 +4683,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
@@ -4695,10 +4722,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>1</v>
@@ -4733,10 +4760,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
@@ -4771,10 +4798,10 @@
         <v>31</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
@@ -4808,6 +4835,9 @@
       </c>
       <c r="N16" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P16" s="0" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4815,10 +4845,10 @@
         <v>33</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>1</v>
@@ -4854,10 +4884,10 @@
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
@@ -4899,10 +4929,10 @@
         <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
@@ -4938,10 +4968,10 @@
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
@@ -4976,10 +5006,10 @@
         <v>38</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5015,10 +5045,10 @@
         <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
@@ -5054,10 +5084,10 @@
         <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>1</v>
@@ -5092,10 +5122,10 @@
         <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
@@ -5130,10 +5160,10 @@
         <v>42</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>1</v>
@@ -5169,10 +5199,10 @@
         <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
@@ -5207,10 +5237,10 @@
         <v>44</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1</v>
@@ -5245,6 +5275,9 @@
       </c>
       <c r="N27" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P27" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5252,10 +5285,10 @@
         <v>47</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -5291,10 +5324,10 @@
         <v>48</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -5330,10 +5363,10 @@
         <v>49</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
@@ -5367,6 +5400,9 @@
       </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5374,10 +5410,10 @@
         <v>52</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>1</v>
@@ -5413,10 +5449,10 @@
         <v>53</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>1</v>
@@ -5452,10 +5488,10 @@
         <v>54</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1</v>
@@ -5489,6 +5525,9 @@
       </c>
       <c r="N33" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5496,10 +5535,10 @@
         <v>55</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1</v>
@@ -5537,7 +5576,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1</v>
@@ -5573,10 +5612,10 @@
         <v>57</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1</v>
@@ -5611,10 +5650,10 @@
         <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5656,10 +5695,10 @@
         <v>61</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -5692,13 +5731,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1</v>
@@ -5736,13 +5775,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>1</v>
@@ -5783,10 +5822,10 @@
         <v>8</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>1</v>
@@ -5827,10 +5866,10 @@
         <v>8</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>1</v>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -513,7 +513,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4254,7 +4254,7 @@
       <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       <c r="N7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="2" t="n">
         <v>35</v>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       <c r="N8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       <c r="N10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       <c r="N16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16" s="2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5276,8 +5276,8 @@
       <c r="N27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="0" t="n">
-        <v>1</v>
+      <c r="P27" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5401,7 +5401,7 @@
       <c r="N30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P30" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       <c r="N33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P33" s="0" t="n">
+      <c r="P33" s="2" t="n">
         <v>5</v>
       </c>
     </row>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4598,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4837,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="127">
   <si>
     <t xml:space="preserve">neurons</t>
   </si>
@@ -641,7 +641,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -1648,7 +1648,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.11"/>
@@ -2652,7 +2652,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -4145,7 +4145,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -5276,8 +5276,8 @@
       <c r="N27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="n">
-        <v>3</v>
+      <c r="P27" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -641,7 +641,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -1648,7 +1648,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.11"/>
@@ -2652,7 +2652,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -4145,7 +4145,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -4923,6 +4923,9 @@
       <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="P18" s="0" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="128">
   <si>
     <t xml:space="preserve">neurons</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t xml:space="preserve">Simulated_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta_eta_stable</t>
   </si>
   <si>
     <t xml:space="preserve">Delta_eta</t>
@@ -4144,7 +4147,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
@@ -4209,16 +4212,19 @@
       <c r="P1" s="7" t="s">
         <v>82</v>
       </c>
+      <c r="Q1" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
@@ -4256,6 +4262,9 @@
       </c>
       <c r="P2" s="2" t="n">
         <v>14</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4263,10 +4272,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
@@ -4294,6 +4303,9 @@
       </c>
       <c r="N3" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4301,10 +4313,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
@@ -4332,6 +4344,9 @@
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4339,10 +4354,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>1</v>
@@ -4380,6 +4395,9 @@
       </c>
       <c r="P5" s="2" t="n">
         <v>50</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4387,10 +4405,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
@@ -4418,6 +4436,9 @@
       </c>
       <c r="N6" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4425,10 +4446,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
@@ -4466,6 +4487,9 @@
       </c>
       <c r="P7" s="2" t="n">
         <v>35</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4473,10 +4497,10 @@
         <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1</v>
@@ -4512,6 +4536,9 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4520,10 +4547,10 @@
         <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -4552,6 +4579,9 @@
       </c>
       <c r="N9" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q9" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4559,10 +4589,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
@@ -4599,6 +4629,9 @@
       </c>
       <c r="P10" s="2" t="n">
         <v>50</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4606,10 +4639,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>1</v>
@@ -4637,6 +4670,9 @@
       </c>
       <c r="N11" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q11" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4644,10 +4680,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>1</v>
@@ -4676,6 +4712,9 @@
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,10 +4722,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
@@ -4715,6 +4754,9 @@
       </c>
       <c r="N13" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4722,10 +4764,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>1</v>
@@ -4753,6 +4795,9 @@
       </c>
       <c r="N14" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,10 +4805,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
@@ -4791,6 +4836,9 @@
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4798,10 +4846,10 @@
         <v>31</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
@@ -4838,6 +4886,9 @@
       </c>
       <c r="P16" s="2" t="n">
         <v>50</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4845,10 +4896,10 @@
         <v>33</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>1</v>
@@ -4877,6 +4928,9 @@
       </c>
       <c r="N17" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4884,10 +4938,10 @@
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
@@ -4923,7 +4977,10 @@
       <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4932,10 +4989,10 @@
         <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
@@ -4964,6 +5021,9 @@
       </c>
       <c r="N19" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4971,10 +5031,10 @@
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
@@ -5002,6 +5062,9 @@
       </c>
       <c r="N20" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,10 +5072,10 @@
         <v>38</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5041,6 +5104,9 @@
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5048,10 +5114,10 @@
         <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
@@ -5080,6 +5146,9 @@
       </c>
       <c r="N22" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5087,10 +5156,10 @@
         <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>1</v>
@@ -5118,6 +5187,9 @@
       </c>
       <c r="N23" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5125,10 +5197,10 @@
         <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
@@ -5156,6 +5228,9 @@
       </c>
       <c r="N24" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5163,10 +5238,10 @@
         <v>42</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>1</v>
@@ -5195,6 +5270,9 @@
       </c>
       <c r="N25" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q25" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5202,10 +5280,10 @@
         <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
@@ -5233,6 +5311,9 @@
       </c>
       <c r="N26" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5240,10 +5321,10 @@
         <v>44</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1</v>
@@ -5281,6 +5362,9 @@
       </c>
       <c r="P27" s="2" t="s">
         <v>78</v>
+      </c>
+      <c r="Q27" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5288,10 +5372,10 @@
         <v>47</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -5320,6 +5404,9 @@
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5327,10 +5414,10 @@
         <v>48</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -5359,6 +5446,9 @@
       </c>
       <c r="N29" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q29" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5366,10 +5456,10 @@
         <v>49</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
@@ -5406,6 +5496,9 @@
       </c>
       <c r="P30" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5413,10 +5506,10 @@
         <v>52</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>1</v>
@@ -5445,6 +5538,9 @@
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q31" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5452,10 +5548,10 @@
         <v>53</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>1</v>
@@ -5484,6 +5580,9 @@
       </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5491,10 +5590,10 @@
         <v>54</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1</v>
@@ -5531,6 +5630,9 @@
       </c>
       <c r="P33" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="Q33" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5538,10 +5640,10 @@
         <v>55</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1</v>
@@ -5569,6 +5671,9 @@
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5579,7 +5684,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1</v>
@@ -5608,6 +5713,9 @@
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q35" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5615,10 +5723,10 @@
         <v>57</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1</v>
@@ -5646,6 +5754,9 @@
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5653,10 +5764,10 @@
         <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5691,6 +5802,9 @@
       </c>
       <c r="N37" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q37" s="0" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5698,10 +5812,10 @@
         <v>61</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -5731,16 +5845,19 @@
       <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q38" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1</v>
@@ -5775,16 +5892,19 @@
       <c r="N39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q39" s="0" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>1</v>
@@ -5819,16 +5939,19 @@
       <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q40" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>1</v>
@@ -5863,16 +5986,19 @@
       <c r="N41" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="Q41" s="0" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>1</v>
@@ -5906,6 +6032,9 @@
       </c>
       <c r="N42" s="3" t="n">
         <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -4264,7 +4264,7 @@
         <v>14</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,8 +4396,8 @@
       <c r="P5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q5" s="0" t="n">
-        <v>15</v>
+      <c r="Q5" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4437,8 +4437,8 @@
       <c r="N6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>15</v>
+      <c r="Q6" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4488,8 +4488,8 @@
       <c r="P7" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Q7" s="0" t="n">
-        <v>15</v>
+      <c r="Q7" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4539,7 +4539,7 @@
         <v>15</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4631,7 +4631,7 @@
         <v>50</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4671,8 +4671,8 @@
       <c r="N11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="0" t="n">
-        <v>15</v>
+      <c r="Q11" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4713,8 +4713,8 @@
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="2" t="n">
-        <v>15</v>
+      <c r="Q12" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4755,8 +4755,8 @@
       <c r="N13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="0" t="n">
-        <v>15</v>
+      <c r="Q13" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4888,7 +4888,7 @@
         <v>50</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4929,8 +4929,8 @@
       <c r="N17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="0" t="n">
-        <v>15</v>
+      <c r="Q17" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4980,8 +4980,8 @@
       <c r="P18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="Q18" s="2" t="n">
-        <v>15</v>
+      <c r="Q18" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5022,8 +5022,8 @@
       <c r="N19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="0" t="n">
-        <v>15</v>
+      <c r="Q19" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5064,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5188,8 +5188,8 @@
       <c r="N23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="0" t="n">
-        <v>15</v>
+      <c r="Q23" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5229,8 +5229,8 @@
       <c r="N24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="2" t="n">
-        <v>15</v>
+      <c r="Q24" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5271,8 +5271,8 @@
       <c r="N25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="0" t="n">
-        <v>15</v>
+      <c r="Q25" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5364,7 +5364,7 @@
         <v>78</v>
       </c>
       <c r="Q27" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5447,8 +5447,8 @@
       <c r="N29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="0" t="n">
-        <v>15</v>
+      <c r="Q29" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5497,8 +5497,8 @@
       <c r="P30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" s="2" t="n">
-        <v>15</v>
+      <c r="Q30" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5539,8 +5539,8 @@
       <c r="N31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="0" t="n">
-        <v>15</v>
+      <c r="Q31" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5632,7 +5632,7 @@
         <v>3</v>
       </c>
       <c r="Q33" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5673,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5714,8 +5714,8 @@
       <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="0" t="n">
-        <v>15</v>
+      <c r="Q35" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5755,8 +5755,8 @@
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="2" t="n">
-        <v>15</v>
+      <c r="Q36" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5803,8 +5803,8 @@
       <c r="N37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="0" t="n">
-        <v>15</v>
+      <c r="Q37" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5893,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="Q39" s="0" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5940,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5986,8 +5986,8 @@
       <c r="N41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="0" t="n">
-        <v>15</v>
+      <c r="Q41" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6033,8 +6033,8 @@
       <c r="N42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="2" t="n">
-        <v>15</v>
+      <c r="Q42" s="0" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="127">
   <si>
     <t xml:space="preserve">neurons</t>
   </si>
@@ -269,9 +269,6 @@
   </si>
   <si>
     <t xml:space="preserve">Simulated_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta_eta_stable</t>
   </si>
   <si>
     <t xml:space="preserve">Delta_eta</t>
@@ -4212,19 +4209,17 @@
       <c r="P1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q1" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="Q1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
@@ -4263,19 +4258,17 @@
       <c r="P2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
@@ -4304,19 +4297,17 @@
       <c r="N3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
@@ -4345,19 +4336,17 @@
       <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>1</v>
@@ -4396,19 +4385,17 @@
       <c r="P5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q5" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
@@ -4437,19 +4424,17 @@
       <c r="N6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
@@ -4488,19 +4473,17 @@
       <c r="P7" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="Q7" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1</v>
@@ -4538,19 +4521,17 @@
       <c r="P8" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -4580,19 +4561,17 @@
       <c r="N9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
@@ -4630,19 +4609,17 @@
       <c r="P10" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q10" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>1</v>
@@ -4671,19 +4648,17 @@
       <c r="N11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>1</v>
@@ -4713,19 +4688,17 @@
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
@@ -4755,19 +4728,17 @@
       <c r="N13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>1</v>
@@ -4796,19 +4767,17 @@
       <c r="N14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
@@ -4837,19 +4806,17 @@
       <c r="N15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
@@ -4887,19 +4854,17 @@
       <c r="P16" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q16" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>1</v>
@@ -4929,19 +4894,17 @@
       <c r="N17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
@@ -4980,19 +4943,17 @@
       <c r="P18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="Q18" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
@@ -5022,19 +4983,17 @@
       <c r="N19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
@@ -5063,19 +5022,17 @@
       <c r="N20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5105,19 +5062,17 @@
       <c r="N21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
@@ -5147,19 +5102,17 @@
       <c r="N22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>1</v>
@@ -5188,19 +5141,17 @@
       <c r="N23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
@@ -5229,19 +5180,17 @@
       <c r="N24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>1</v>
@@ -5271,19 +5220,17 @@
       <c r="N25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
@@ -5312,19 +5259,17 @@
       <c r="N26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1</v>
@@ -5363,19 +5308,17 @@
       <c r="P27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="Q27" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -5405,19 +5348,17 @@
       <c r="N28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -5447,19 +5388,17 @@
       <c r="N29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
@@ -5497,19 +5436,17 @@
       <c r="P30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>1</v>
@@ -5539,19 +5476,17 @@
       <c r="N31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>1</v>
@@ -5581,19 +5516,17 @@
       <c r="N32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1</v>
@@ -5631,19 +5564,17 @@
       <c r="P33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q33" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1</v>
@@ -5672,9 +5603,7 @@
       <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
@@ -5684,7 +5613,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1</v>
@@ -5714,19 +5643,17 @@
       <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1</v>
@@ -5755,19 +5682,17 @@
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5803,19 +5728,17 @@
       <c r="N37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -5845,19 +5768,17 @@
       <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1</v>
@@ -5892,19 +5813,17 @@
       <c r="N39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>1</v>
@@ -5939,19 +5858,17 @@
       <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>1</v>
@@ -5986,19 +5903,17 @@
       <c r="N41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>1</v>
@@ -6033,9 +5948,7 @@
       <c r="N42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="0" t="n">
-        <v>50</v>
-      </c>
+      <c r="Q42" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="127">
   <si>
     <t xml:space="preserve">neurons</t>
   </si>
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Q2" s="2"/>
     </row>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q5" s="2"/>
     </row>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
@@ -5305,8 +5305,8 @@
       <c r="N27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>78</v>
+      <c r="P27" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="Q27" s="2"/>
     </row>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="local_model" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,387 +23,408 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="134">
+  <si>
+    <t xml:space="preserve">Hippocampome_Neurons_Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model_Neurons_Names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulated_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_include</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_neuron_parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Npops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OutPlaceThetaPhase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OutPlaceFiringRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InPlacePeakRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CenterPlaceField</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SigmaPlaceField</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SlopePhasePrecession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PrecessionOnset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta_eta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Источник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Axo-Axonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axo-Axonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simulated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Horizontal Axo-Axonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal Axo-Axonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Back-Projection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back-Projection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Horizontal Basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal Basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Basket CCK+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basket CCK+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Bistratified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bistratified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Hippocampo-subicular Projecting ENK+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hippocampo-subicular Projecting ENK+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Ivy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific LM-R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific LM-R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific LMO-O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific LMO-O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 LMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific LMR-R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific LMR-R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 LMR Projecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMR Projecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Neurogliaform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neurogliaform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Neurogliaform Projecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neurogliaform Projecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.jneurosci.org/content/30/5/1595.long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 O-LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Recurrent O-LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurrent O-LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 O-LMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-LMR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific O-R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific O-R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific O-Targeting QuadD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific O-Targeting QuadD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Oriens-Alveus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriens-Alveus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Oriens-Bistratified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriens-Bistratified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Oriens-Bistratified Projecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Oriens-Bistratified Projecting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 OR-LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OR-LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Perforant Path-Associated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perforant Path-Associated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Perforant Path-Associated QuadD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Perforant Path-Associated QuadD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Quadrilaminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quadrilaminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific R-O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific R-O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 R-Receiving Apical-Targeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-Receiving Apical-Targeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Radiatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Interneuron Specific RO-O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interneuron Specific RO-O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Schaffer Collateral-Associated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schaffer Collateral-Associated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1523/JNEUROSCI.3269-05.2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Schaffer Collateral-Receiving R-Targeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 SO-SO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SO-SO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Trilaminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trilaminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Radial Trilaminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radial Trilaminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3 Pyramidal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3 Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC LIII Pyramidal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEC Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1 Pyramidal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyramidal (deep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyramidal (superficial)</t>
+  </si>
   <si>
     <t xml:space="preserve">neurons</t>
   </si>
   <si>
-    <t xml:space="preserve">is_include</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_neuron_parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Npops</t>
-  </si>
-  <si>
     <t xml:space="preserve">ThetaPhase</t>
   </si>
   <si>
-    <t xml:space="preserve">R</t>
-  </si>
-  <si>
     <t xml:space="preserve">MeanFiringRate</t>
   </si>
   <si>
-    <t xml:space="preserve">CA1 Pyramidal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Axo-Axonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Horizontal Axo-Axonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Back-Projection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Basket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Horizontal Basket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Basket CCK+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Bistratified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Hippocampo-subicular Projecting ENK+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Ivy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific LM-R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific LMO-O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 LMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific LMR-R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 LMR Projecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Neurogliaform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Neurogliaform Projecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 O-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Recurrent O-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 O-LMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific O-R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific O-Targeting QuadD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Oriens-Alveus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Oriens-Bistratified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Oriens-Bistratified Projecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 OR-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Perforant Path-Associated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Perforant Path-Associated QuadD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Quadrilaminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific R-O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 R-Receiving Apical-Targeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Radiatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Interneuron Specific RO-O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Schaffer Collateral-Associated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Schaffer Collateral-Receiving R-Targeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 SO-SO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Trilaminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.0</t>
   </si>
   <si>
-    <t xml:space="preserve">CA1 Radial Trilaminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OutPlaceThetaPhase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OutPlaceFiringRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InPlacePeakRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CenterPlaceField</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SigmaPlaceField</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SlopePhasePrecession</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PrecessionOnset</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA1 Pyramidal (deep)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA1 Pyramidal (superficial)</t>
   </si>
   <si>
     <t xml:space="preserve">-2.74</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA3_generator</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">MEC_generator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hippocampome_Neurons_Names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model_Neurons_Names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulated_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta_eta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axo-Axonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">simulated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal Axo-Axonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Back-Projection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal Basket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basket CCK+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bistratified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hippocampo-subicular Projecting ENK+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific LM-R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific LMO-O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific LMR-R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMR Projecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neurogliaform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neurogliaform Projecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recurrent O-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-LMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific O-R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific O-Targeting QuadD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriens-Alveus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriens-Bistratified</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Oriens-Bistratified Projecting</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OR-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perforant Path-Associated</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Perforant Path-Associated QuadD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Quadrilaminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific R-O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-Receiving Apical-Targeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radiatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interneuron Specific RO-O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schaffer Collateral-Associated</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SO-SO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trilaminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radial Trilaminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3 Pyramidal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3 Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC LIII Pyramidal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEC Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pyramidal (deep)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pyramidal (superficial)</t>
   </si>
 </sst>
 </file>
@@ -413,7 +434,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -434,6 +455,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -484,7 +512,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -506,14 +534,30 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -640,8 +684,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Q42"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -666,7 +710,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -678,960 +722,1846 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <f aca="false">ROUND(F2*0.0025,0)*D2</f>
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>793</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>336</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <f aca="false">ROUND(F5*0.0025,0)*D5</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <f aca="false">ROUND(F7*0.0025,0)*D7</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="P7" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>804</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6"/>
+      <c r="Q9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="P10" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>837</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <f aca="false">ROUND(F12*0.0025,0)*D12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <f aca="false">ROUND(F13*0.0025,0)*D13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>658</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6"/>
+      <c r="Q17" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <f aca="false">ROUND(F18*0.0025,0)*D18</f>
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3"/>
+      <c r="P18" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <f aca="false">ROUND(F19*0.0025,0)*D19</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>574</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <f aca="false">ROUND(F21*0.0025,0)*D21</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <f aca="false">ROUND(F22*0.0025,0)*D22</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>607</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <f aca="false">ROUND(F25*0.0025,0)*D25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <f aca="false">ROUND(F27*0.0025,0)*D27</f>
+        <v>1</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3"/>
+      <c r="P27" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <f aca="false">ROUND(F28*0.0025,0)*D28</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <f aca="false">ROUND(F29*0.0025,0)*D29</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>698</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+      <c r="P30" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <f aca="false">ROUND(F31*0.0025,0)*D31</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <f aca="false">ROUND(F32*0.0025,0)*D32</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3"/>
+      <c r="P33" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>986</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6"/>
+      <c r="Q34" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <f aca="false">ROUND(F35*0.0025,0)*D35</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <f aca="false">ROUND(F38*0.0025,0)*D38</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
         <v>160000</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <f aca="false">ROUND(D3*0.0025,0)*B3</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <f aca="false">ROUND(D4*0.0025,0)*B4</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>793</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <f aca="false">ROUND(D5*0.0025,0)*B5</f>
-        <v>2</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>336</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <f aca="false">ROUND(D6*0.0025,0)*B6</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>333</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <f aca="false">ROUND(D7*0.0025,0)*B7</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <f aca="false">ROUND(D8*0.0025,0)*B8</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="G41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>804</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <f aca="false">ROUND(D9*0.0025,0)*B9</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="I41" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <f aca="false">ROUND(D10*0.0025,0)*B10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>778</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <f aca="false">ROUND(D11*0.0025,0)*B11</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>837</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <f aca="false">ROUND(D12*0.0025,0)*B12</f>
-        <v>2</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <f aca="false">ROUND(D13*0.0025,0)*B13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <f aca="false">ROUND(D14*0.0025,0)*B14</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <f aca="false">ROUND(D15*0.0025,0)*B15</f>
-        <v>3</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>658</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <f aca="false">ROUND(D16*0.0025,0)*B16</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>1114</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <f aca="false">ROUND(D17*0.0025,0)*B17</f>
-        <v>3</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <f aca="false">ROUND(D18*0.0025,0)*B18</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>521</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <f aca="false">ROUND(D19*0.0025,0)*B19</f>
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <f aca="false">ROUND(D20*0.0025,0)*B20</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>574</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <f aca="false">ROUND(D21*0.0025,0)*B21</f>
-        <v>1</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="K41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <f aca="false">ROUND(D22*0.0025,0)*B22</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <f aca="false">ROUND(D23*0.0025,0)*B23</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>607</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <f aca="false">ROUND(D24*0.0025,0)*B24</f>
-        <v>2</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <f aca="false">ROUND(D25*0.0025,0)*B25</f>
-        <v>1</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <f aca="false">ROUND(D26*0.0025,0)*B26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>729</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <f aca="false">ROUND(D27*0.0025,0)*B27</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>463</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <f aca="false">ROUND(D28*0.0025,0)*B28</f>
-        <v>1</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <f aca="false">ROUND(D29*0.0025,0)*B29</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <f aca="false">ROUND(D30*0.0025,0)*B30</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>698</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <f aca="false">ROUND(D31*0.0025,0)*B31</f>
-        <v>2</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <f aca="false">ROUND(D32*0.0025,0)*B32</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <f aca="false">ROUND(D33*0.0025,0)*B33</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <f aca="false">ROUND(D34*0.0025,0)*B34</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>986</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <f aca="false">ROUND(D35*0.0025,0)*B35</f>
-        <v>2</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <f aca="false">ROUND(D36*0.0025,0)*B36</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>313</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <f aca="false">ROUND(D37*0.0025,0)*B37</f>
-        <v>1</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>401</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <f aca="false">ROUND(D38*0.0025,0)*B38</f>
-        <v>1</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <f aca="false">ROUND(D39*0.0025,0)*B39</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="6"/>
+      <c r="I42" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q9" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
+    <hyperlink ref="Q17" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1648,7 +2578,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.11"/>
@@ -1659,33 +2589,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
+      <c r="A2" s="10" t="s">
+        <v>122</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -1705,7 +2635,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
@@ -1721,19 +2651,19 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
@@ -1750,14 +2680,14 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="6"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
@@ -1774,14 +2704,14 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="6"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
@@ -1797,19 +2727,19 @@
         <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
@@ -1826,14 +2756,14 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="6"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
@@ -1849,19 +2779,19 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
@@ -1877,19 +2807,19 @@
         <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
@@ -1906,14 +2836,14 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="6"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
@@ -1929,19 +2859,19 @@
         <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -1958,14 +2888,14 @@
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="6"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
@@ -1982,14 +2912,14 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="6"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>1</v>
@@ -2006,14 +2936,14 @@
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="6"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
@@ -2030,14 +2960,14 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="6"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>1</v>
@@ -2054,14 +2984,14 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="6"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1</v>
@@ -2077,19 +3007,19 @@
         <v>111</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>1</v>
@@ -2106,14 +3036,14 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="6"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>1</v>
@@ -2129,19 +3059,19 @@
         <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
@@ -2158,14 +3088,14 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="6"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>1</v>
@@ -2182,14 +3112,14 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="6"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
@@ -2206,14 +3136,14 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="6"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>1</v>
@@ -2230,14 +3160,14 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="6"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>1</v>
@@ -2254,14 +3184,14 @@
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="6"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>1</v>
@@ -2278,14 +3208,14 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="6"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>1</v>
@@ -2302,14 +3232,14 @@
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="6"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>1</v>
@@ -2326,14 +3256,14 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="6"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>44</v>
+      <c r="A28" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>1</v>
@@ -2349,19 +3279,19 @@
         <v>46</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>0</v>
@@ -2378,14 +3308,14 @@
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="6"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
@@ -2402,14 +3332,14 @@
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="6"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>1</v>
@@ -2425,19 +3355,19 @@
         <v>70</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="I31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
@@ -2454,14 +3384,14 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="6"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>1</v>
@@ -2478,14 +3408,14 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="6"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>1</v>
@@ -2501,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I34" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>55</v>
+      <c r="A35" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>1</v>
@@ -2530,14 +3460,14 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="6"/>
+      <c r="I35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
@@ -2554,14 +3484,14 @@
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="6"/>
+      <c r="I36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>1</v>
@@ -2578,14 +3508,14 @@
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="6"/>
+      <c r="I37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>1</v>
@@ -2601,19 +3531,19 @@
         <v>40</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I38" s="6"/>
+        <v>128</v>
+      </c>
+      <c r="I38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>0</v>
@@ -2630,10 +3560,10 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3"/>
-      <c r="I39" s="6"/>
+      <c r="I39" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2652,7 +3582,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -2667,48 +3597,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -2723,13 +3653,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>8</v>
@@ -2746,7 +3676,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
@@ -2761,13 +3691,13 @@
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>8</v>
@@ -2784,7 +3714,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
@@ -2800,10 +3730,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>29</v>
@@ -2823,7 +3753,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
@@ -2838,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8</v>
@@ -2855,7 +3785,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
@@ -2870,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>8</v>
@@ -2887,7 +3817,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
@@ -2903,13 +3833,13 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>8</v>
@@ -2926,7 +3856,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
@@ -2941,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>8</v>
@@ -2958,7 +3888,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
@@ -2974,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>8</v>
@@ -2997,7 +3927,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -3012,10 +3942,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>27</v>
@@ -3035,7 +3965,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
@@ -3051,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>8</v>
@@ -3068,7 +3998,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -3083,13 +4013,13 @@
         <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>8</v>
@@ -3106,7 +4036,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
@@ -3121,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>8</v>
@@ -3138,7 +4068,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>1</v>
@@ -3154,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>8</v>
@@ -3171,7 +4101,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
@@ -3187,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>8</v>
@@ -3204,7 +4134,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>1</v>
@@ -3219,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>8</v>
@@ -3236,7 +4166,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1</v>
@@ -3251,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>8</v>
@@ -3268,7 +4198,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>1</v>
@@ -3283,13 +4213,13 @@
         <v>1</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>8</v>
@@ -3306,7 +4236,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>1</v>
@@ -3322,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>8</v>
@@ -3339,7 +4269,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>1</v>
@@ -3355,13 +4285,13 @@
         <v>1</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>8</v>
@@ -3378,7 +4308,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
@@ -3394,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>8</v>
@@ -3411,7 +4341,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>1</v>
@@ -3426,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>8</v>
@@ -3443,7 +4373,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
@@ -3459,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>8</v>
@@ -3476,7 +4406,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>1</v>
@@ -3492,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>8</v>
@@ -3509,7 +4439,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>1</v>
@@ -3524,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>8</v>
@@ -3541,7 +4471,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>1</v>
@@ -3556,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>8</v>
@@ -3573,7 +4503,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>1</v>
@@ -3589,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>8</v>
@@ -3606,7 +4536,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>1</v>
@@ -3621,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8</v>
@@ -3638,7 +4568,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>1</v>
@@ -3654,13 +4584,13 @@
         <v>1</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>8</v>
@@ -3677,7 +4607,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
@@ -3693,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>8</v>
@@ -3710,7 +4640,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
@@ -3726,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>8</v>
@@ -3743,7 +4673,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
@@ -3758,13 +4688,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>8</v>
@@ -3781,7 +4711,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>1</v>
@@ -3797,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>8</v>
@@ -3814,7 +4744,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>1</v>
@@ -3830,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>8</v>
@@ -3847,7 +4777,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>1</v>
@@ -3862,13 +4792,13 @@
         <v>1</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>8</v>
@@ -3885,7 +4815,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
@@ -3900,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>8</v>
@@ -3917,7 +4847,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>1</v>
@@ -3933,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>8</v>
@@ -3950,7 +4880,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>1</v>
@@ -3965,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>8</v>
@@ -3982,7 +4912,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>1</v>
@@ -3998,13 +4928,13 @@
         <v>1</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>8</v>
@@ -4021,7 +4951,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
@@ -4037,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>8</v>
@@ -4054,7 +4984,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>1</v>
@@ -4069,13 +4999,13 @@
         <v>1</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>8</v>
@@ -4092,7 +5022,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>1</v>
@@ -4107,13 +5037,13 @@
         <v>1</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>8</v>
@@ -4145,7 +5075,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -4162,64 +5092,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q1" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
@@ -4235,10 +5165,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>29</v>
@@ -4262,13 +5192,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
@@ -4283,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>8</v>
@@ -4301,13 +5231,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
@@ -4322,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>8</v>
@@ -4340,13 +5270,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>1</v>
@@ -4362,13 +5292,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>8</v>
@@ -4389,13 +5319,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
@@ -4410,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>8</v>
@@ -4428,13 +5358,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
@@ -4450,13 +5380,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>8</v>
@@ -4477,13 +5407,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1</v>
@@ -4498,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>27</v>
@@ -4525,13 +5455,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -4547,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>8</v>
@@ -4565,13 +5495,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
@@ -4586,13 +5516,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>8</v>
@@ -4613,13 +5543,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>1</v>
@@ -4634,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>8</v>
@@ -4652,13 +5582,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>1</v>
@@ -4674,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>8</v>
@@ -4692,13 +5622,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
@@ -4714,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
@@ -4732,13 +5662,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>1</v>
@@ -4753,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>8</v>
@@ -4771,13 +5701,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
@@ -4792,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>8</v>
@@ -4810,13 +5740,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
@@ -4831,13 +5761,13 @@
         <v>1</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>8</v>
@@ -4858,13 +5788,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>1</v>
@@ -4880,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>8</v>
@@ -4898,13 +5828,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
@@ -4920,13 +5850,13 @@
         <v>1</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>8</v>
@@ -4947,13 +5877,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
@@ -4969,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>8</v>
@@ -4987,13 +5917,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
@@ -5008,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>8</v>
@@ -5026,13 +5956,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5048,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>8</v>
@@ -5066,13 +5996,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
@@ -5088,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>8</v>
@@ -5106,13 +6036,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>1</v>
@@ -5127,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>8</v>
@@ -5145,13 +6075,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
@@ -5166,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>8</v>
@@ -5184,13 +6114,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>1</v>
@@ -5206,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>8</v>
@@ -5224,13 +6154,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
@@ -5245,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>8</v>
@@ -5263,13 +6193,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1</v>
@@ -5285,13 +6215,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>8</v>
@@ -5312,13 +6242,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -5334,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>8</v>
@@ -5352,13 +6282,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -5374,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8</v>
@@ -5392,13 +6322,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
@@ -5413,13 +6343,13 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>8</v>
@@ -5440,13 +6370,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>1</v>
@@ -5462,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>8</v>
@@ -5480,13 +6410,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>1</v>
@@ -5502,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
@@ -5520,13 +6450,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1</v>
@@ -5541,13 +6471,13 @@
         <v>1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>8</v>
@@ -5568,13 +6498,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1</v>
@@ -5589,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>8</v>
@@ -5607,13 +6537,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1</v>
@@ -5629,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>8</v>
@@ -5647,13 +6577,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1</v>
@@ -5668,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>8</v>
@@ -5686,13 +6616,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5708,13 +6638,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>8</v>
@@ -5732,13 +6662,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -5754,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>8</v>
@@ -5772,13 +6702,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1</v>
@@ -5793,13 +6723,13 @@
         <v>1</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>8</v>
@@ -5817,13 +6747,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>1</v>
@@ -5838,13 +6768,13 @@
         <v>1</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>8</v>
@@ -5862,13 +6792,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>1</v>
@@ -5883,13 +6813,13 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>8</v>
@@ -5907,13 +6837,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>1</v>
@@ -5928,13 +6858,13 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>8</v>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -927,7 +927,7 @@
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1112,6 +1112,9 @@
         <v>0</v>
       </c>
       <c r="O9" s="6"/>
+      <c r="P9" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="Q9" s="8" t="s">
         <v>43</v>
       </c>
@@ -1892,7 +1895,7 @@
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2024,7 +2027,7 @@
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2156,7 +2159,7 @@
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2203,6 +2206,9 @@
         <v>0</v>
       </c>
       <c r="O34" s="6"/>
+      <c r="P34" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="Q34" s="9" t="s">
         <v>104</v>
       </c>
@@ -2334,6 +2340,9 @@
         <v>0</v>
       </c>
       <c r="O37" s="3"/>
+      <c r="P37" s="0" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -76,18 +76,36 @@
     <t xml:space="preserve">Источник</t>
   </si>
   <si>
+    <t xml:space="preserve">CA1 Pyramidal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyramidal (deep)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simulated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyramidal (superficial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA1 Axo-Axonic</t>
   </si>
   <si>
     <t xml:space="preserve">Axo-Axonic</t>
   </si>
   <si>
-    <t xml:space="preserve">simulated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.3</t>
   </si>
   <si>
@@ -139,9 +157,6 @@
     <t xml:space="preserve">Bistratified</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA1 Hippocampo-subicular Projecting ENK+</t>
   </si>
   <si>
@@ -376,12 +391,6 @@
     <t xml:space="preserve">1.4</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">EC LIII Pyramidal</t>
   </si>
   <si>
@@ -389,15 +398,6 @@
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1 Pyramidal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pyramidal (deep)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pyramidal (superficial)</t>
   </si>
   <si>
     <t xml:space="preserve">neurons</t>
@@ -434,7 +434,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -455,6 +455,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -512,7 +517,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -537,19 +542,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -557,7 +554,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -684,7 +681,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
@@ -746,41 +743,40 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <f aca="false">ROUND(F2*0.0025,0)*D2</f>
-        <v>1</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="F2" s="4" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>29</v>
+      <c r="J2" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>8</v>
@@ -795,37 +791,38 @@
         <v>0</v>
       </c>
       <c r="O2" s="3"/>
-      <c r="P2" s="2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="3"/>
       <c r="K3" s="3" t="n">
         <v>8</v>
       </c>
@@ -842,10 +839,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
@@ -857,16 +854,21 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>793</v>
+        <v>312</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3"/>
+        <f aca="false">ROUND(F4*0.0025,0)*D4</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="I4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="K4" s="3" t="n">
         <v>8</v>
       </c>
@@ -880,13 +882,16 @@
         <v>0</v>
       </c>
       <c r="O4" s="3"/>
+      <c r="P4" s="2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -898,21 +903,16 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="G5" s="3" t="n">
-        <f aca="false">ROUND(F5*0.0025,0)*D5</f>
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>29</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
@@ -926,9 +926,6 @@
         <v>0</v>
       </c>
       <c r="O5" s="3"/>
-      <c r="P5" s="2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -947,14 +944,14 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>333</v>
+        <v>793</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="n">
@@ -988,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">ROUND(F7*0.0025,0)*D7</f>
@@ -998,7 +995,7 @@
         <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>35</v>
@@ -1037,94 +1034,85 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>804</v>
+        <v>333</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <f aca="false">ROUND(F9*0.0025,0)*D9</f>
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7" t="n">
+      <c r="K9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3"/>
+      <c r="P9" s="2" t="n">
         <v>50</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -1136,19 +1124,19 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>778</v>
+        <v>804</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>27</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>27</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>8</v>
@@ -1164,49 +1152,59 @@
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4"/>
+      <c r="P11" s="2" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="Q11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>837</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
@@ -1222,20 +1220,23 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>171</v>
+        <v>778</v>
       </c>
       <c r="G12" s="3" t="n">
-        <f aca="false">ROUND(F12*0.0025,0)*D12</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="K12" s="3" t="n">
         <v>8</v>
       </c>
@@ -1249,13 +1250,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3"/>
+      <c r="P12" s="2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>19</v>
@@ -1264,18 +1268,17 @@
         <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>136</v>
+        <v>837</v>
       </c>
       <c r="G13" s="3" t="n">
-        <f aca="false">ROUND(F13*0.0025,0)*D13</f>
         <v>0</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="n">
@@ -1294,10 +1297,10 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>19</v>
@@ -1309,14 +1312,15 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1010</v>
+        <v>171</v>
       </c>
       <c r="G14" s="3" t="n">
+        <f aca="false">ROUND(F14*0.0025,0)*D14</f>
         <v>0</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="n">
@@ -1335,10 +1339,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>19</v>
@@ -1347,17 +1351,18 @@
         <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>658</v>
+        <v>136</v>
       </c>
       <c r="G15" s="3" t="n">
+        <f aca="false">ROUND(F15*0.0025,0)*D15</f>
         <v>0</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="n">
@@ -1376,10 +1381,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>19</v>
@@ -1388,23 +1393,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1114</v>
+        <v>1010</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J16" s="3"/>
       <c r="K16" s="3" t="n">
         <v>8</v>
       </c>
@@ -1418,87 +1419,78 @@
         <v>0</v>
       </c>
       <c r="O16" s="3"/>
-      <c r="P16" s="2" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="6"/>
-      <c r="Q17" s="8" t="s">
-        <v>62</v>
-      </c>
+      <c r="C17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>658</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>521</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <f aca="false">ROUND(F18*0.0025,0)*D18</f>
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>8</v>
@@ -1514,50 +1506,54 @@
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4"/>
+      <c r="Q19" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <f aca="false">ROUND(F19*0.0025,0)*D19</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -1576,16 +1572,21 @@
         <v>1</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>574</v>
+        <v>521</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3"/>
+        <f aca="false">ROUND(F20*0.0025,0)*D20</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="I20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
@@ -1599,25 +1600,28 @@
         <v>0</v>
       </c>
       <c r="O20" s="3"/>
+      <c r="P20" s="2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>70</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>73</v>
       </c>
       <c r="G21" s="3" t="n">
         <f aca="false">ROUND(F21*0.0025,0)*D21</f>
@@ -1625,7 +1629,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="n">
@@ -1644,10 +1648,10 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>19</v>
@@ -1656,18 +1660,17 @@
         <v>1</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>171</v>
+        <v>574</v>
       </c>
       <c r="G22" s="3" t="n">
-        <f aca="false">ROUND(F22*0.0025,0)*D22</f>
         <v>0</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="n">
@@ -1686,29 +1689,30 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>607</v>
+        <v>73</v>
       </c>
       <c r="G23" s="3" t="n">
+        <f aca="false">ROUND(F23*0.0025,0)*D23</f>
         <v>0</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="n">
@@ -1727,10 +1731,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>19</v>
@@ -1739,17 +1743,18 @@
         <v>1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>340</v>
+        <v>171</v>
       </c>
       <c r="G24" s="3" t="n">
+        <f aca="false">ROUND(F24*0.0025,0)*D24</f>
         <v>0</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="n">
@@ -1768,10 +1773,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>19</v>
@@ -1780,18 +1785,17 @@
         <v>1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>191</v>
+        <v>607</v>
       </c>
       <c r="G25" s="3" t="n">
-        <f aca="false">ROUND(F25*0.0025,0)*D25</f>
         <v>0</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="n">
@@ -1810,10 +1814,10 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>19</v>
@@ -1825,14 +1829,14 @@
         <v>1</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>729</v>
+        <v>340</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="n">
@@ -1850,12 +1854,12 @@
       <c r="O26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>83</v>
       </c>
+      <c r="B27" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="C27" s="4" t="s">
         <v>19</v>
       </c>
@@ -1863,24 +1867,20 @@
         <v>1</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="G27" s="3" t="n">
         <f aca="false">ROUND(F27*0.0025,0)*D27</f>
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>84</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>85</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J27" s="3"/>
       <c r="K27" s="3" t="n">
         <v>8</v>
       </c>
@@ -1894,36 +1894,32 @@
         <v>0</v>
       </c>
       <c r="O27" s="3"/>
-      <c r="P27" s="2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="C28" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>22</v>
+        <v>729</v>
       </c>
       <c r="G28" s="3" t="n">
-        <f aca="false">ROUND(F28*0.0025,0)*D28</f>
         <v>0</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="n">
@@ -1941,33 +1937,37 @@
       <c r="O28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="G29" s="3" t="n">
         <f aca="false">ROUND(F29*0.0025,0)*D29</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="I29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="K29" s="3" t="n">
         <v>8</v>
       </c>
@@ -1981,38 +1981,38 @@
         <v>0</v>
       </c>
       <c r="O29" s="3"/>
+      <c r="P29" s="2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>698</v>
+        <v>22</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>92</v>
-      </c>
+        <f aca="false">ROUND(F30*0.0025,0)*D30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="3"/>
       <c r="I30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>93</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J30" s="3"/>
       <c r="K30" s="3" t="n">
         <v>8</v>
       </c>
@@ -2026,28 +2026,25 @@
         <v>0</v>
       </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="C31" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="G31" s="3" t="n">
         <f aca="false">ROUND(F31*0.0025,0)*D31</f>
@@ -2055,7 +2052,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="n">
@@ -2074,32 +2071,35 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>698</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <f aca="false">ROUND(F32*0.0025,0)*D32</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
@@ -2113,13 +2113,16 @@
         <v>0</v>
       </c>
       <c r="O32" s="3"/>
+      <c r="P32" s="2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>19</v>
@@ -2128,205 +2131,203 @@
         <v>1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>92</v>
-      </c>
+        <f aca="false">ROUND(F33*0.0025,0)*D33</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="2" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>986</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>104</v>
-      </c>
+      <c r="G34" s="3" t="n">
+        <f aca="false">ROUND(F34*0.0025,0)*D34</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3"/>
+      <c r="P35" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <f aca="false">ROUND(F35*0.0025,0)*D35</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>986</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>313</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="3"/>
+      <c r="I36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4"/>
+      <c r="P36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>110</v>
-      </c>
+        <f aca="false">ROUND(F37*0.0025,0)*D37</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="3"/>
       <c r="I37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J37" s="3"/>
       <c r="K37" s="3" t="n">
         <v>8</v>
       </c>
@@ -2340,9 +2341,6 @@
         <v>0</v>
       </c>
       <c r="O37" s="3"/>
-      <c r="P37" s="0" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
@@ -2355,21 +2353,20 @@
         <v>19</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>119</v>
+        <v>313</v>
       </c>
       <c r="G38" s="3" t="n">
-        <f aca="false">ROUND(F38*0.0025,0)*D38</f>
         <v>0</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="n">
@@ -2393,29 +2390,29 @@
       <c r="B39" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="I39" s="3" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>8</v>
@@ -2430,128 +2427,128 @@
         <v>0</v>
       </c>
       <c r="O39" s="3"/>
+      <c r="P39" s="2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="G40" s="3" t="n">
+        <f aca="false">ROUND(F40*0.0025,0)*D40</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J40" s="3" t="s">
+      <c r="D41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="3"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="I41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B42" s="4" t="s">
+      <c r="C42" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="K42" s="3" t="n">
         <v>8</v>
       </c>
@@ -2565,11 +2562,33 @@
         <v>0</v>
       </c>
       <c r="O42" s="3"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="B43" s="0"/>
+      <c r="C43" s="0"/>
+      <c r="D43" s="0"/>
+      <c r="E43" s="0"/>
+      <c r="F43" s="0"/>
+      <c r="G43" s="0"/>
+      <c r="H43" s="0"/>
+      <c r="I43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="0"/>
+      <c r="C44" s="0"/>
+      <c r="D44" s="0"/>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0"/>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+      <c r="I44" s="0"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q9" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
-    <hyperlink ref="Q17" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
+    <hyperlink ref="Q11" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
+    <hyperlink ref="Q19" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -2623,8 +2642,8 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>122</v>
+      <c r="A2" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -2644,7 +2663,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
@@ -2663,16 +2682,16 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="I3" s="11"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
@@ -2689,14 +2708,14 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="11"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
@@ -2713,14 +2732,14 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="11"/>
+      <c r="I5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
@@ -2736,19 +2755,19 @@
         <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="11"/>
+        <v>35</v>
+      </c>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
@@ -2765,14 +2784,14 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="11"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
@@ -2788,19 +2807,19 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="11"/>
+        <v>41</v>
+      </c>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
@@ -2816,19 +2835,19 @@
         <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="I9" s="11"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
@@ -2845,14 +2864,14 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="11"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
@@ -2868,19 +2887,19 @@
         <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="11"/>
+        <v>51</v>
+      </c>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -2897,14 +2916,14 @@
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="11"/>
+      <c r="I12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
@@ -2921,14 +2940,14 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="11"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>1</v>
@@ -2945,14 +2964,14 @@
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="11"/>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
@@ -2969,14 +2988,14 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="11"/>
+      <c r="I15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>1</v>
@@ -2993,14 +3012,14 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="11"/>
+      <c r="I16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1</v>
@@ -3019,16 +3038,16 @@
         <v>20</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I17" s="11"/>
+        <v>64</v>
+      </c>
+      <c r="I17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>1</v>
@@ -3045,14 +3064,14 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="11"/>
+      <c r="I18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>1</v>
@@ -3068,19 +3087,19 @@
         <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="11"/>
+        <v>70</v>
+      </c>
+      <c r="I19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
@@ -3097,14 +3116,14 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="11"/>
+      <c r="I20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>1</v>
@@ -3121,14 +3140,14 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="11"/>
+      <c r="I21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
@@ -3145,14 +3164,14 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="11"/>
+      <c r="I22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>1</v>
@@ -3169,14 +3188,14 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="11"/>
+      <c r="I23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>1</v>
@@ -3193,14 +3212,14 @@
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="11"/>
+      <c r="I24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>1</v>
@@ -3217,14 +3236,14 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="11"/>
-    </row>
-    <row r="26" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>1</v>
@@ -3241,14 +3260,14 @@
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="11"/>
+      <c r="I26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>1</v>
@@ -3265,14 +3284,14 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="11"/>
+      <c r="I27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>82</v>
+      <c r="A28" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>1</v>
@@ -3288,19 +3307,19 @@
         <v>46</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28" s="11"/>
+        <v>90</v>
+      </c>
+      <c r="I28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>0</v>
@@ -3317,14 +3336,14 @@
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="11"/>
+      <c r="I29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
@@ -3341,14 +3360,14 @@
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="11"/>
+      <c r="I30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>1</v>
@@ -3364,19 +3383,19 @@
         <v>70</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I31" s="11"/>
+        <v>98</v>
+      </c>
+      <c r="I31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
@@ -3393,14 +3412,14 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>1</v>
@@ -3417,14 +3436,14 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="11"/>
+      <c r="I33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>1</v>
@@ -3440,19 +3459,19 @@
         <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I34" s="11"/>
+        <v>98</v>
+      </c>
+      <c r="I34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
-        <v>100</v>
+      <c r="A35" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>1</v>
@@ -3469,14 +3488,14 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="11"/>
+      <c r="I35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
@@ -3493,14 +3512,14 @@
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="11"/>
+      <c r="I36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>1</v>
@@ -3517,14 +3536,14 @@
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="11"/>
+      <c r="I37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>1</v>
@@ -3540,19 +3559,19 @@
         <v>40</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I38" s="11"/>
+      <c r="I38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>0</v>
@@ -3569,10 +3588,10 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H39" s="3"/>
-      <c r="I39" s="11"/>
+      <c r="I39" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3665,10 +3684,10 @@
         <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>8</v>
@@ -3700,13 +3719,13 @@
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>8</v>
@@ -3723,7 +3742,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
@@ -3742,7 +3761,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>29</v>
@@ -3762,7 +3781,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
@@ -3777,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8</v>
@@ -3794,7 +3813,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
@@ -3809,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>8</v>
@@ -3826,7 +3845,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
@@ -3842,13 +3861,13 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>8</v>
@@ -3865,7 +3884,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
@@ -3880,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>8</v>
@@ -3897,7 +3916,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
@@ -3913,13 +3932,13 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>8</v>
@@ -3936,7 +3955,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -3951,10 +3970,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>27</v>
@@ -3974,7 +3993,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
@@ -3990,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>8</v>
@@ -4007,7 +4026,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
@@ -4022,13 +4041,13 @@
         <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>8</v>
@@ -4045,7 +4064,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
@@ -4060,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>8</v>
@@ -4077,7 +4096,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>1</v>
@@ -4093,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>8</v>
@@ -4110,7 +4129,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>1</v>
@@ -4126,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>8</v>
@@ -4143,7 +4162,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>1</v>
@@ -4158,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>8</v>
@@ -4175,7 +4194,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1</v>
@@ -4190,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>8</v>
@@ -4207,7 +4226,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>1</v>
@@ -4225,10 +4244,10 @@
         <v>20</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>8</v>
@@ -4245,7 +4264,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>1</v>
@@ -4261,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>8</v>
@@ -4278,7 +4297,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>1</v>
@@ -4294,13 +4313,13 @@
         <v>1</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>8</v>
@@ -4317,7 +4336,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
@@ -4333,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>8</v>
@@ -4350,7 +4369,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>1</v>
@@ -4365,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>8</v>
@@ -4382,7 +4401,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
@@ -4398,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>8</v>
@@ -4415,7 +4434,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>1</v>
@@ -4431,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>8</v>
@@ -4448,7 +4467,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>1</v>
@@ -4463,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>8</v>
@@ -4480,7 +4499,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>1</v>
@@ -4495,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>8</v>
@@ -4512,7 +4531,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>1</v>
@@ -4528,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>8</v>
@@ -4545,7 +4564,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>1</v>
@@ -4560,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8</v>
@@ -4577,7 +4596,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>1</v>
@@ -4593,13 +4612,13 @@
         <v>1</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>8</v>
@@ -4616,7 +4635,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
@@ -4632,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>8</v>
@@ -4649,7 +4668,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
@@ -4665,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>8</v>
@@ -4682,7 +4701,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>1</v>
@@ -4697,13 +4716,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>8</v>
@@ -4720,7 +4739,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>1</v>
@@ -4736,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>8</v>
@@ -4753,7 +4772,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>1</v>
@@ -4769,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>8</v>
@@ -4786,7 +4805,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>1</v>
@@ -4801,13 +4820,13 @@
         <v>1</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>8</v>
@@ -4824,7 +4843,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>1</v>
@@ -4839,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>8</v>
@@ -4856,7 +4875,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>1</v>
@@ -4872,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>8</v>
@@ -4889,7 +4908,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>1</v>
@@ -4904,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>8</v>
@@ -4921,7 +4940,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>1</v>
@@ -4940,10 +4959,10 @@
         <v>131</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>8</v>
@@ -4960,7 +4979,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
@@ -4976,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>8</v>
@@ -5008,13 +5027,13 @@
         <v>1</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>8</v>
@@ -5046,13 +5065,13 @@
         <v>1</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>8</v>
@@ -5152,10 +5171,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>19</v>
@@ -5177,7 +5196,7 @@
         <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>29</v>
@@ -5201,10 +5220,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -5222,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>8</v>
@@ -5240,10 +5259,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
@@ -5261,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>8</v>
@@ -5279,10 +5298,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>19</v>
@@ -5301,13 +5320,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>8</v>
@@ -5328,10 +5347,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>19</v>
@@ -5349,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>8</v>
@@ -5367,10 +5386,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
@@ -5389,13 +5408,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>8</v>
@@ -5416,10 +5435,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>19</v>
@@ -5437,10 +5456,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>27</v>
@@ -5464,10 +5483,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -5486,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>8</v>
@@ -5504,10 +5523,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -5525,13 +5544,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>8</v>
@@ -5552,10 +5571,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>19</v>
@@ -5573,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>8</v>
@@ -5591,10 +5610,10 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>19</v>
@@ -5613,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>8</v>
@@ -5631,10 +5650,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>19</v>
@@ -5653,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
@@ -5671,10 +5690,10 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>19</v>
@@ -5692,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>8</v>
@@ -5710,10 +5729,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>19</v>
@@ -5731,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>8</v>
@@ -5749,10 +5768,10 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>19</v>
@@ -5773,10 +5792,10 @@
         <v>20</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>8</v>
@@ -5797,10 +5816,10 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>19</v>
@@ -5819,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>8</v>
@@ -5837,10 +5856,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>19</v>
@@ -5859,13 +5878,13 @@
         <v>1</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>8</v>
@@ -5886,10 +5905,10 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>19</v>
@@ -5908,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>8</v>
@@ -5926,10 +5945,10 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>19</v>
@@ -5947,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>8</v>
@@ -5965,10 +5984,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>19</v>
@@ -5987,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>8</v>
@@ -6005,10 +6024,10 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>19</v>
@@ -6027,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>8</v>
@@ -6045,10 +6064,10 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>19</v>
@@ -6066,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>8</v>
@@ -6084,10 +6103,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>19</v>
@@ -6105,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>8</v>
@@ -6123,10 +6142,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>19</v>
@@ -6145,7 +6164,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>8</v>
@@ -6163,10 +6182,10 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>19</v>
@@ -6184,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>8</v>
@@ -6202,10 +6221,10 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>19</v>
@@ -6224,13 +6243,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>8</v>
@@ -6251,10 +6270,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>19</v>
@@ -6273,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>8</v>
@@ -6291,10 +6310,10 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>19</v>
@@ -6313,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8</v>
@@ -6331,10 +6350,10 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>19</v>
@@ -6352,13 +6371,13 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>8</v>
@@ -6379,10 +6398,10 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>19</v>
@@ -6401,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>8</v>
@@ -6419,10 +6438,10 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>19</v>
@@ -6441,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
@@ -6459,10 +6478,10 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>19</v>
@@ -6480,13 +6499,13 @@
         <v>1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>8</v>
@@ -6507,10 +6526,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>19</v>
@@ -6528,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>8</v>
@@ -6546,10 +6565,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>19</v>
@@ -6568,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>8</v>
@@ -6586,10 +6605,10 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>19</v>
@@ -6607,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>8</v>
@@ -6625,10 +6644,10 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>19</v>
@@ -6647,13 +6666,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>8</v>
@@ -6671,10 +6690,10 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>19</v>
@@ -6693,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>8</v>
@@ -6711,13 +6730,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1</v>
@@ -6732,13 +6751,13 @@
         <v>1</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>8</v>
@@ -6756,14 +6775,14 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="D40" s="3" t="n">
         <v>1</v>
       </c>
@@ -6777,13 +6796,13 @@
         <v>1</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>8</v>
@@ -6801,13 +6820,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>1</v>
@@ -6825,10 +6844,10 @@
         <v>20</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>8</v>
@@ -6846,13 +6865,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>1</v>
@@ -6867,13 +6886,13 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>8</v>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -791,6 +791,9 @@
         <v>0</v>
       </c>
       <c r="O2" s="3"/>
+      <c r="P2" s="0" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -836,6 +839,9 @@
         <v>0</v>
       </c>
       <c r="O3" s="3"/>
+      <c r="P3" s="0" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -5,11 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="local_model" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="full_local_model" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="theta_model" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="verified_theta_model" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="131">
   <si>
     <t xml:space="preserve">Hippocampome_Neurons_Names</t>
   </si>
@@ -401,15 +401,6 @@
   </si>
   <si>
     <t xml:space="preserve">neurons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaPhase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MeanFiringRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0</t>
   </si>
   <si>
     <t xml:space="preserve">CA1 Pyramidal (deep)</t>
@@ -434,7 +425,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -458,29 +449,30 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFDBB6"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -517,7 +509,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -543,18 +535,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -567,6 +579,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFDBB6"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -754,7 +826,7 @@
       <c r="B2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="4" t="n">
@@ -791,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="3"/>
-      <c r="P2" s="0" t="n">
+      <c r="P2" s="2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -802,7 +874,7 @@
       <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="4" t="n">
@@ -839,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="3"/>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1161,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
@@ -1208,7 +1280,7 @@
       <c r="P11" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q11" s="7" t="s">
+      <c r="Q11" s="6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1343,7 +1415,7 @@
       </c>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
@@ -1384,6 +1456,8 @@
         <v>0</v>
       </c>
       <c r="O15" s="3"/>
+      <c r="P15" s="0"/>
+      <c r="Q15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -1515,7 +1589,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>65</v>
       </c>
@@ -1557,7 +1631,8 @@
         <v>0</v>
       </c>
       <c r="O19" s="4"/>
-      <c r="Q19" s="7" t="s">
+      <c r="P19" s="2"/>
+      <c r="Q19" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2255,7 +2330,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>105</v>
       </c>
@@ -2570,26 +2645,12 @@
       <c r="O42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0"/>
-      <c r="B43" s="0"/>
-      <c r="C43" s="0"/>
-      <c r="D43" s="0"/>
-      <c r="E43" s="0"/>
-      <c r="F43" s="0"/>
-      <c r="G43" s="0"/>
-      <c r="H43" s="0"/>
-      <c r="I43" s="0"/>
+      <c r="A43" s="2"/>
+      <c r="C43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0"/>
-      <c r="B44" s="0"/>
-      <c r="C44" s="0"/>
-      <c r="D44" s="0"/>
-      <c r="E44" s="0"/>
-      <c r="F44" s="0"/>
-      <c r="G44" s="0"/>
-      <c r="H44" s="0"/>
-      <c r="I44" s="0"/>
+      <c r="A44" s="2"/>
+      <c r="C44" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2611,995 +2672,3723 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="23.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="15.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" s="8"/>
+      <c r="P4" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" s="8"/>
+      <c r="P8" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>125</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="M9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="N9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="8"/>
+      <c r="P9" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="8"/>
+      <c r="P10" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="8"/>
+      <c r="P11" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" s="8"/>
+      <c r="P12" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" s="8"/>
+      <c r="P13" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" s="8"/>
+      <c r="P14" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" s="8"/>
+      <c r="P15" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" s="8"/>
+      <c r="P16" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>245</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" s="8"/>
+      <c r="P17" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" s="8"/>
+      <c r="P18" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>275</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" s="8"/>
+      <c r="P19" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>290</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="8"/>
+      <c r="P20" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>305</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" s="8"/>
+      <c r="P21" s="9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" s="12"/>
+      <c r="P22" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" s="12"/>
+      <c r="P23" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="12"/>
+      <c r="P24" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" s="12"/>
+      <c r="P25" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" s="12"/>
+      <c r="P26" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" s="12"/>
+      <c r="P27" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" s="12"/>
+      <c r="P28" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" s="12"/>
+      <c r="P29" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="12"/>
+      <c r="P30" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" s="12"/>
+      <c r="P31" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" s="12"/>
+      <c r="P32" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" s="12"/>
+      <c r="P33" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" s="12"/>
+      <c r="P34" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" s="12"/>
+      <c r="P35" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" s="12"/>
+      <c r="P36" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" s="12"/>
+      <c r="P37" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" s="12"/>
+      <c r="P38" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>270</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" s="12"/>
+      <c r="P39" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>285</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O40" s="12"/>
+      <c r="P40" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O41" s="12"/>
+      <c r="P41" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="B42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>312</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <f aca="false">ROUND(D3/10,0)*B3</f>
+      <c r="G42" s="3" t="n">
+        <f aca="false">ROUND(F42*0.0025,0)*D42</f>
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+      <c r="P42" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="C44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>793</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>336</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <f aca="false">ROUND(F45*0.0025,0)*D45</f>
+        <v>1</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3"/>
+      <c r="P45" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <f aca="false">ROUND(F47*0.0025,0)*D47</f>
+        <v>1</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+      <c r="P47" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>804</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3"/>
+      <c r="P48" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4"/>
+      <c r="P49" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+      <c r="P50" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>837</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <f aca="false">ROUND(F52*0.0025,0)*D52</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <f aca="false">ROUND(F53*0.0025,0)*D53</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>658</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="I3" s="9"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <f aca="false">ROUND(D4/10,0)*B4</f>
+      <c r="I56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="3"/>
+      <c r="P56" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>793</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <f aca="false">ROUND(D5/10,0)*B5</f>
+      <c r="I57" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <f aca="false">ROUND(F58*0.0025,0)*D58</f>
+        <v>1</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+      <c r="P58" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <f aca="false">ROUND(F59*0.0025,0)*D59</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>574</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <f aca="false">ROUND(F61*0.0025,0)*D61</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <f aca="false">ROUND(F62*0.0025,0)*D62</f>
+        <v>0</v>
+      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>336</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <f aca="false">ROUND(D6/10,0)*B6</f>
-        <v>34</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>333</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <f aca="false">ROUND(D7/10,0)*B7</f>
-        <v>33</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <f aca="false">ROUND(D8/10,0)*B8</f>
-        <v>40</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>804</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <f aca="false">ROUND(D9/10,0)*B9</f>
+      <c r="B63" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="C63" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>607</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <f aca="false">ROUND(F65*0.0025,0)*D65</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <f aca="false">ROUND(F67*0.0025,0)*D67</f>
+        <v>1</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="3"/>
+      <c r="P67" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <f aca="false">ROUND(F68*0.0025,0)*D68</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <f aca="false">ROUND(F69*0.0025,0)*D69</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>698</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <f aca="false">ROUND(F71*0.0025,0)*D71</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <f aca="false">ROUND(F72*0.0025,0)*D72</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+      <c r="P73" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>986</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="4"/>
+      <c r="P74" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q74" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <f aca="false">ROUND(F75*0.0025,0)*D75</f>
+        <v>0</v>
+      </c>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+      <c r="P77" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <f aca="false">ROUND(F78*0.0025,0)*D78</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <f aca="false">ROUND(D10/10,0)*B10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>778</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <f aca="false">ROUND(D11/10,0)*B11</f>
-        <v>78</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>837</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <f aca="false">ROUND(D12/10,0)*B12</f>
-        <v>84</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <f aca="false">ROUND(D13/10,0)*B13</f>
-        <v>17</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <f aca="false">ROUND(D14/10,0)*B14</f>
-        <v>14</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <f aca="false">ROUND(D15/10,0)*B15</f>
-        <v>101</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>658</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <f aca="false">ROUND(D16/10,0)*B16</f>
-        <v>66</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>1114</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <f aca="false">ROUND(D17/10,0)*B17</f>
-        <v>111</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <f aca="false">ROUND(D18/10,0)*B18</f>
-        <v>10</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>521</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <f aca="false">ROUND(D19/10,0)*B19</f>
-        <v>52</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <f aca="false">ROUND(D20/10,0)*B20</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>574</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <f aca="false">ROUND(D21/10,0)*B21</f>
-        <v>57</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <f aca="false">ROUND(D22/10,0)*B22</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <f aca="false">ROUND(D23/10,0)*B23</f>
-        <v>17</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>607</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <f aca="false">ROUND(D24/10,0)*B24</f>
-        <v>61</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>340</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <f aca="false">ROUND(D25/10,0)*B25</f>
-        <v>34</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <f aca="false">ROUND(D26/10,0)*B26</f>
-        <v>19</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>729</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <f aca="false">ROUND(D27/10,0)*B27</f>
-        <v>73</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="9"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>463</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <f aca="false">ROUND(D28/10,0)*B28</f>
-        <v>46</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="n">
+      <c r="B79" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <f aca="false">ROUND(D29/10,0)*B29</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <f aca="false">ROUND(D30/10,0)*B30</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>698</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <f aca="false">ROUND(D31/10,0)*B31</f>
-        <v>70</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="K79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="3"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <f aca="false">ROUND(D32/10,0)*B32</f>
-        <v>13</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <f aca="false">ROUND(D33/10,0)*B33</f>
-        <v>9</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="9"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <f aca="false">ROUND(D34/10,0)*B34</f>
-        <v>17</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>986</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <f aca="false">ROUND(D35/10,0)*B35</f>
-        <v>99</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="9"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <f aca="false">ROUND(D36/10,0)*B36</f>
-        <v>8</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>313</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <f aca="false">ROUND(D37/10,0)*B37</f>
-        <v>31</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>401</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <f aca="false">ROUND(D38/10,0)*B38</f>
-        <v>40</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <f aca="false">ROUND(D39/10,0)*B39</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="9"/>
+      <c r="I80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q49" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
+    <hyperlink ref="Q57" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3672,7 +6461,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -3710,7 +6499,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
@@ -4962,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>27</v>
@@ -5018,7 +7807,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>1</v>
@@ -5056,7 +7845,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>1</v>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="local_model" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="135">
   <si>
     <t xml:space="preserve">Hippocampome_Neurons_Names</t>
   </si>
@@ -398,6 +398,18 @@
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x_anat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y_anat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84</t>
   </si>
   <si>
     <t xml:space="preserve">neurons</t>
@@ -455,7 +467,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,7 +483,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FF99CCFF"/>
+        <bgColor rgb="FFD4EA6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACB20C"/>
+        <bgColor rgb="FF808000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FFAFD095"/>
       </patternFill>
     </fill>
   </fills>
@@ -509,7 +533,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -538,6 +562,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -547,10 +575,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -566,7 +590,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -616,14 +648,14 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFD4EA6B"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFDBB6"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFACB20C"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -754,7 +786,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -975,7 +1007,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1</v>
@@ -1016,7 +1048,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1</v>
@@ -1106,7 +1138,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
@@ -1343,7 +1375,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1384,7 +1416,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -1426,7 +1458,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1</v>
@@ -1456,8 +1488,6 @@
         <v>0</v>
       </c>
       <c r="O15" s="3"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -1470,7 +1500,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -1511,7 +1541,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -1600,7 +1630,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
@@ -1738,7 +1768,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1</v>
@@ -1821,7 +1851,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
@@ -1863,7 +1893,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>1</v>
@@ -1904,7 +1934,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
@@ -1945,7 +1975,7 @@
         <v>19</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0</v>
@@ -1987,7 +2017,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
@@ -2209,7 +2239,7 @@
         <v>19</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>1</v>
@@ -2251,7 +2281,7 @@
         <v>19</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
@@ -2392,7 +2422,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0</v>
@@ -2434,7 +2464,7 @@
         <v>19</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
@@ -2475,7 +2505,7 @@
         <v>19</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>1</v>
@@ -2661,8 +2691,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2672,13 +2702,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S127"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="23.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="23.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="19.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="15.88"/>
@@ -2736,968 +2766,1134 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="2" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="C2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" s="8" t="n">
+      <c r="K2" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P2" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N3" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="9" t="n">
+      <c r="O3" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="R3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="C4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" s="8" t="n">
+      <c r="K4" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="9" t="n">
+      <c r="O6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P6" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="R6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="G7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="8" t="n">
+      <c r="K7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P7" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="R7" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="M8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N8" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O4" s="8"/>
-      <c r="P4" s="9" t="n">
+      <c r="O8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P8" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="R8" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="C9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="G9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8" t="n">
+      <c r="K9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="9" t="n">
+      <c r="O12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P12" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="R12" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="C13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="G13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="8" t="n">
+      <c r="K13" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="9" t="n">
+      <c r="O15" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P15" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="R15" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S15" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="C16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="G16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" s="8" t="n">
+      <c r="K16" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S16" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="9" t="n">
+      <c r="O18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P18" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="R18" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S18" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="C19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>160000</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="G19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K19" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S20" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="9" t="n">
+      <c r="O21" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="P21" s="10" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" s="8"/>
-      <c r="P10" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>170</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>185</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O14" s="8"/>
-      <c r="P14" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>215</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>230</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>245</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>260</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O18" s="8"/>
-      <c r="P18" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>275</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>290</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O20" s="8"/>
-      <c r="P20" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>305</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" s="8"/>
-      <c r="P21" s="9" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R21" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
         <v>17</v>
       </c>
@@ -3732,20 +3928,28 @@
         <v>8</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M22" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M22" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O22" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P22" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
         <v>17</v>
       </c>
@@ -3780,20 +3984,28 @@
         <v>8</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M23" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M23" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O23" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P23" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
         <v>17</v>
       </c>
@@ -3828,20 +4040,28 @@
         <v>8</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="M24" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O24" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P24" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="25" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
         <v>17</v>
       </c>
@@ -3876,20 +4096,28 @@
         <v>8</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="M25" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M25" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O25" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P25" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
         <v>17</v>
       </c>
@@ -3924,20 +4152,28 @@
         <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="M26" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="M26" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O26" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P26" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="27" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
         <v>17</v>
       </c>
@@ -3972,20 +4208,28 @@
         <v>8</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="M27" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="M27" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O27" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P27" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="28" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R27" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S27" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
         <v>17</v>
       </c>
@@ -4020,20 +4264,28 @@
         <v>8</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="M28" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M28" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O28" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P28" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R28" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
         <v>17</v>
       </c>
@@ -4068,20 +4320,28 @@
         <v>8</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="M29" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M29" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O29" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P29" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="30" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R29" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
         <v>17</v>
       </c>
@@ -4116,20 +4376,28 @@
         <v>8</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="M30" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="M30" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O30" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P30" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R30" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
         <v>17</v>
       </c>
@@ -4164,20 +4432,28 @@
         <v>8</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="M31" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O31" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P31" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R31" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S31" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
         <v>17</v>
       </c>
@@ -4212,20 +4488,28 @@
         <v>8</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>165</v>
-      </c>
-      <c r="M32" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O32" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P32" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="33" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R32" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S32" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
         <v>17</v>
       </c>
@@ -4260,20 +4544,28 @@
         <v>8</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>180</v>
-      </c>
-      <c r="M33" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="M33" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O33" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P33" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="34" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R33" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
         <v>17</v>
       </c>
@@ -4308,20 +4600,28 @@
         <v>8</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>195</v>
-      </c>
-      <c r="M34" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="M34" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O34" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P34" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="35" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R34" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S34" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
         <v>17</v>
       </c>
@@ -4356,20 +4656,28 @@
         <v>8</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="M35" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="M35" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O35" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P35" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="36" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R35" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
         <v>17</v>
       </c>
@@ -4404,20 +4712,28 @@
         <v>8</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>225</v>
-      </c>
-      <c r="M36" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M36" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O36" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P36" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="37" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R36" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S36" s="10" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
         <v>17</v>
       </c>
@@ -4452,20 +4768,28 @@
         <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="M37" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="M37" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O37" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P37" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R37" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S37" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
         <v>17</v>
       </c>
@@ -4500,20 +4824,28 @@
         <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>255</v>
-      </c>
-      <c r="M38" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="M38" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O38" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P38" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="39" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R38" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S38" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
         <v>17</v>
       </c>
@@ -4548,20 +4880,28 @@
         <v>8</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>270</v>
-      </c>
-      <c r="M39" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="M39" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O39" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O39" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P39" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R39" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S39" s="10" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
         <v>17</v>
       </c>
@@ -4596,20 +4936,28 @@
         <v>8</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="M40" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="M40" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O40" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O40" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P40" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R40" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S40" s="10" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
         <v>17</v>
       </c>
@@ -4644,17 +4992,25 @@
         <v>8</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="M41" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M41" s="9" t="n">
         <v>5</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O41" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="O41" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="P41" s="13" t="n">
         <v>50</v>
+      </c>
+      <c r="R41" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="S41" s="10" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4717,7 +5073,7 @@
         <v>19</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>1</v>
@@ -4758,7 +5114,7 @@
         <v>19</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
@@ -4848,7 +5204,7 @@
         <v>19</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>1</v>
@@ -5085,7 +5441,7 @@
         <v>19</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>0</v>
@@ -5126,7 +5482,7 @@
         <v>19</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>0</v>
@@ -5168,7 +5524,7 @@
         <v>19</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>1</v>
@@ -5210,7 +5566,7 @@
         <v>19</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -5251,7 +5607,7 @@
         <v>19</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>0</v>
@@ -5340,7 +5696,7 @@
         <v>19</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>1</v>
@@ -5478,7 +5834,7 @@
         <v>19</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>1</v>
@@ -5561,7 +5917,7 @@
         <v>19</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>0</v>
@@ -5603,7 +5959,7 @@
         <v>19</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>1</v>
@@ -5644,7 +6000,7 @@
         <v>19</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>1</v>
@@ -5685,7 +6041,7 @@
         <v>19</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>0</v>
@@ -5727,7 +6083,7 @@
         <v>19</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>1</v>
@@ -5949,7 +6305,7 @@
         <v>19</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>1</v>
@@ -5991,7 +6347,7 @@
         <v>19</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>1</v>
@@ -6132,7 +6488,7 @@
         <v>19</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0</v>
@@ -6174,7 +6530,7 @@
         <v>19</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>1</v>
@@ -6215,7 +6571,7 @@
         <v>19</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>1</v>
@@ -6295,94 +6651,2149 @@
       <c r="O78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="D79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I79" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J79" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>0</v>
+      <c r="K79" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L79" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M79" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M80" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N80" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" s="3"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K82" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L82" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="M82" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N82" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I83" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K83" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L83" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="M83" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N83" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I84" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K84" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="M84" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I85" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K85" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L85" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="M85" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N85" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I86" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K86" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="M86" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N86" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I87" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="M87" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N87" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I88" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K88" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="M88" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N88" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I89" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K89" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="M89" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N89" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K90" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="M90" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N90" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I91" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K91" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="M91" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N91" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I92" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L92" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="M92" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N92" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I93" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L93" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="M93" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N93" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I94" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L94" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="M94" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N94" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I95" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="M95" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N95" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I96" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L96" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="M96" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N96" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I97" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K97" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="M97" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N97" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I98" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K98" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M98" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N98" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I99" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K99" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="M99" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N99" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I100" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K100" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L100" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="M100" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N100" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I101" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K101" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="M101" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N101" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J102" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K102" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="M102" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N102" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B103" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C103" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="3" t="s">
+      <c r="D103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I103" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J103" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K80" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="3"/>
+      <c r="K103" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M103" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N103" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" s="3"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J104" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K104" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M104" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N104" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J105" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K105" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M105" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N105" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K106" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L106" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="M106" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N106" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K107" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L107" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="M107" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N107" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K108" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="M108" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N108" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I109" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J109" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K109" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L109" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="M109" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N109" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D110" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K110" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="M110" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N110" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D111" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I111" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K111" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="M111" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N111" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K112" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L112" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="M112" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N112" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K113" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L113" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="M113" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N113" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D114" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I114" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J114" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K114" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="M114" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N114" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D115" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I115" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K115" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="M115" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N115" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C116" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D116" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I116" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J116" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K116" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L116" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="M116" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N116" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I117" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J117" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K117" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="M117" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N117" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D118" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I118" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J118" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K118" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="M118" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N118" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I119" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J119" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K119" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L119" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="M119" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N119" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" s="3"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C120" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D120" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I120" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J120" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K120" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L120" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="M120" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N120" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D121" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I121" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J121" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K121" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="M121" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N121" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I122" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J122" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K122" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L122" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N122" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D123" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I123" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J123" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K123" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L123" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="M123" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N123" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I124" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J124" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K124" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L124" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M124" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N124" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B125" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C125" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I125" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J125" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K125" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="M125" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N125" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B126" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I126" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J126" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K126" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L126" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="M126" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N126" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J127" s="16"/>
+      <c r="K127" s="16"/>
+      <c r="L127" s="16"/>
+      <c r="M127" s="16"/>
+      <c r="N127" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6393,8 +8804,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6405,7 +8816,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -6420,7 +8831,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -6461,7 +8872,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -6499,7 +8910,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
@@ -7751,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>27</v>
@@ -7807,7 +10218,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>1</v>
@@ -7845,7 +10256,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>1</v>
@@ -7886,8 +10297,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -7898,7 +10309,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -9708,8 +12119,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="local_model" sheetId="1" state="visible" r:id="rId3"/>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -533,7 +533,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -559,10 +559,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -596,10 +592,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -786,7 +778,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -2691,8 +2683,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2703,7 +2695,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S127"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.77"/>
@@ -2766,2250 +2758,2250 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+    <row r="2" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="8" t="n">
+      <c r="C2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" s="9" t="n">
+      <c r="K2" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R12" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="M2" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="9" t="n">
+      <c r="N13" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O13" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="P2" s="10" t="n">
+      <c r="P13" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="R2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="R13" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="8" t="n">
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="8" t="s">
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" s="9" t="n">
+      <c r="K14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="I15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="M15" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N3" s="9" t="n">
+      <c r="N15" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O15" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="P3" s="10" t="n">
+      <c r="P15" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="R3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="R15" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S15" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8" t="n">
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="9" t="n">
+      <c r="K16" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S19" s="9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S20" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O21" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="P21" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="R4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="10" t="n">
+      <c r="R21" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S21" s="9" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P22" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="5" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="25" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="B25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="G25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="M5" s="9" t="n">
+      <c r="K25" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="M25" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P5" s="10" t="n">
+      <c r="N25" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="10" t="n">
+      <c r="R25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="6" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="26" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8" t="n">
+      <c r="B26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="G26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="M6" s="9" t="n">
+      <c r="K26" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P6" s="10" t="n">
+      <c r="N26" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="10" t="n">
+      <c r="R26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="7" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="27" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="n">
+      <c r="B27" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="G27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="M7" s="9" t="n">
+      <c r="K27" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P7" s="10" t="n">
+      <c r="N27" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R7" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S7" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="R27" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="B28" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="G28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="M8" s="9" t="n">
+      <c r="K28" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P8" s="10" t="n">
+      <c r="N28" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R8" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S8" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="R28" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="n">
+      <c r="B29" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="G29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="9" t="n">
+      <c r="K29" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P29" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="R29" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P9" s="10" t="n">
+      <c r="N30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R9" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S9" s="10" t="n">
+      <c r="R30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P31" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P32" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R32" s="9" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="10" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="S32" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8" t="n">
+      <c r="B33" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="8" t="s">
+      <c r="G33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="M10" s="9" t="n">
+      <c r="K33" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="M33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P10" s="10" t="n">
+      <c r="N33" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P33" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R10" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S10" s="10" t="n">
+      <c r="R33" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P34" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R34" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P35" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R35" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S35" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="11" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    <row r="36" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="B36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="G36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J36" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="M11" s="9" t="n">
+      <c r="K36" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="M36" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N11" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P11" s="10" t="n">
+      <c r="N36" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P36" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R11" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S11" s="10" t="n">
+      <c r="R36" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S36" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="12" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="37" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="B37" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="G37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J37" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="M12" s="9" t="n">
+      <c r="K37" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="10" t="n">
+      <c r="N37" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P37" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R37" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S37" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P38" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R38" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S38" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O39" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P39" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R39" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S39" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="S12" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+    </row>
+    <row r="40" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8" t="n">
+      <c r="B40" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="8" t="s">
+      <c r="G40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J40" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="M13" s="9" t="n">
+      <c r="K40" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="M40" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P13" s="10" t="n">
+      <c r="N40" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O40" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P40" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R13" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S13" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="R40" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S40" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="B41" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="G41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J41" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="M14" s="9" t="n">
+      <c r="K41" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="M41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N14" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P14" s="10" t="n">
+      <c r="N41" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P41" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="R14" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S14" s="10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P15" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R15" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S15" s="10" t="n">
+      <c r="R41" s="9" t="n">
         <v>300</v>
       </c>
-    </row>
-    <row r="16" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P16" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R16" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S16" s="10" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P17" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R17" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S17" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P18" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R18" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S18" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P19" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R19" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S19" s="10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P20" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R20" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S20" s="10" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="P21" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R21" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S21" s="10" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P22" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P23" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O24" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P24" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P25" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="10" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P26" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="10" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="27" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P27" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S27" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P28" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R28" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S28" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M29" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P29" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R29" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P30" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R30" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S30" s="10" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P31" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R31" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S31" s="10" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="32" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P32" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R32" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S32" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M33" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P33" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R33" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S33" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P34" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R34" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S34" s="10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O35" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P35" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R35" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S35" s="10" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P36" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R36" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S36" s="10" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="37" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P37" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R37" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S37" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O38" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P38" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R38" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S38" s="10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O39" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P39" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R39" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S39" s="10" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="M40" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N40" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O40" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P40" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R40" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S40" s="10" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="41" s="13" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O41" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="P41" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="R41" s="10" t="n">
-        <v>300</v>
-      </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="9" t="n">
         <v>400</v>
       </c>
     </row>
@@ -6651,2149 +6643,2149 @@
       <c r="O78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="14" t="s">
+      <c r="D79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I79" s="14" t="s">
+      <c r="I79" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="14" t="s">
+      <c r="J79" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K79" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="14" t="n">
+      <c r="K79" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L79" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="M79" s="14" t="n">
+      <c r="M79" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N79" s="14" t="n">
+      <c r="N79" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="14" t="s">
+      <c r="D80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I80" s="14" t="s">
+      <c r="I80" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J80" s="14" t="s">
+      <c r="J80" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K80" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" s="14" t="n">
+      <c r="K80" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="M80" s="14" t="n">
+      <c r="M80" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N80" s="14" t="n">
+      <c r="N80" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D81" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="14" t="s">
+      <c r="D81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I81" s="14" t="s">
+      <c r="I81" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J81" s="14" t="s">
+      <c r="J81" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K81" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L81" s="14" t="n">
+      <c r="K81" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="M81" s="14" t="n">
+      <c r="M81" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N81" s="14" t="n">
+      <c r="N81" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D82" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="14" t="s">
+      <c r="D82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I82" s="14" t="s">
+      <c r="I82" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J82" s="14" t="s">
+      <c r="J82" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K82" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L82" s="14" t="n">
+      <c r="K82" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L82" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="M82" s="14" t="n">
+      <c r="M82" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N82" s="14" t="n">
+      <c r="N82" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="14" t="s">
+      <c r="D83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I83" s="14" t="s">
+      <c r="I83" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J83" s="14" t="s">
+      <c r="J83" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K83" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L83" s="14" t="n">
+      <c r="K83" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L83" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="M83" s="14" t="n">
+      <c r="M83" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N83" s="14" t="n">
+      <c r="N83" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D84" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="14" t="s">
+      <c r="D84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I84" s="14" t="s">
+      <c r="I84" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J84" s="14" t="s">
+      <c r="J84" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K84" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L84" s="14" t="n">
+      <c r="K84" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="M84" s="14" t="n">
+      <c r="M84" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N84" s="14" t="n">
+      <c r="N84" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="14" t="s">
+      <c r="D85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I85" s="14" t="s">
+      <c r="I85" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J85" s="14" t="s">
+      <c r="J85" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K85" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L85" s="14" t="n">
+      <c r="K85" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L85" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="M85" s="14" t="n">
+      <c r="M85" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N85" s="14" t="n">
+      <c r="N85" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="14" t="s">
+      <c r="D86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I86" s="14" t="s">
+      <c r="I86" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J86" s="14" t="s">
+      <c r="J86" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K86" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L86" s="14" t="n">
+      <c r="K86" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="M86" s="14" t="n">
+      <c r="M86" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N86" s="14" t="n">
+      <c r="N86" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="14" t="s">
+      <c r="D87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I87" s="14" t="s">
+      <c r="I87" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J87" s="14" t="s">
+      <c r="J87" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K87" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" s="14" t="n">
+      <c r="K87" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="M87" s="14" t="n">
+      <c r="M87" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N87" s="14" t="n">
+      <c r="N87" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="14" t="s">
+      <c r="D88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I88" s="14" t="s">
+      <c r="I88" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J88" s="14" t="s">
+      <c r="J88" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K88" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" s="14" t="n">
+      <c r="K88" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="M88" s="14" t="n">
+      <c r="M88" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N88" s="14" t="n">
+      <c r="N88" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D89" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="14" t="s">
+      <c r="D89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I89" s="14" t="s">
+      <c r="I89" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J89" s="14" t="s">
+      <c r="J89" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K89" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L89" s="14" t="n">
+      <c r="K89" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="M89" s="14" t="n">
+      <c r="M89" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N89" s="14" t="n">
+      <c r="N89" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D90" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="14" t="s">
+      <c r="D90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I90" s="14" t="s">
+      <c r="I90" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J90" s="14" t="s">
+      <c r="J90" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K90" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L90" s="14" t="n">
+      <c r="K90" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="M90" s="14" t="n">
+      <c r="M90" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N90" s="14" t="n">
+      <c r="N90" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" s="14" t="s">
+      <c r="D91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I91" s="14" t="s">
+      <c r="I91" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J91" s="14" t="s">
+      <c r="J91" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K91" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L91" s="14" t="n">
+      <c r="K91" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="M91" s="14" t="n">
+      <c r="M91" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N91" s="14" t="n">
+      <c r="N91" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D92" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="14" t="s">
+      <c r="D92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I92" s="14" t="s">
+      <c r="I92" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J92" s="14" t="s">
+      <c r="J92" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K92" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L92" s="14" t="n">
+      <c r="K92" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L92" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="M92" s="14" t="n">
+      <c r="M92" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N92" s="14" t="n">
+      <c r="N92" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="14" t="s">
+      <c r="D93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I93" s="14" t="s">
+      <c r="I93" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J93" s="14" t="s">
+      <c r="J93" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K93" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L93" s="14" t="n">
+      <c r="K93" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L93" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="M93" s="14" t="n">
+      <c r="M93" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N93" s="14" t="n">
+      <c r="N93" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D94" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="14" t="s">
+      <c r="D94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I94" s="14" t="s">
+      <c r="I94" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J94" s="14" t="s">
+      <c r="J94" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K94" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L94" s="14" t="n">
+      <c r="K94" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L94" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="M94" s="14" t="n">
+      <c r="M94" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N94" s="14" t="n">
+      <c r="N94" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D95" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="14" t="s">
+      <c r="D95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I95" s="14" t="s">
+      <c r="I95" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J95" s="14" t="s">
+      <c r="J95" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K95" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L95" s="14" t="n">
+      <c r="K95" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="M95" s="14" t="n">
+      <c r="M95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N95" s="14" t="n">
+      <c r="N95" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D96" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="14" t="s">
+      <c r="D96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I96" s="14" t="s">
+      <c r="I96" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J96" s="14" t="s">
+      <c r="J96" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K96" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L96" s="14" t="n">
+      <c r="K96" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L96" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="M96" s="14" t="n">
+      <c r="M96" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N96" s="14" t="n">
+      <c r="N96" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="14" t="s">
+      <c r="C97" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D97" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="14" t="s">
+      <c r="D97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I97" s="14" t="s">
+      <c r="I97" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J97" s="14" t="s">
+      <c r="J97" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K97" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L97" s="14" t="n">
+      <c r="K97" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" s="13" t="n">
         <v>95</v>
       </c>
-      <c r="M97" s="14" t="n">
+      <c r="M97" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N97" s="14" t="n">
+      <c r="N97" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D98" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" s="14" t="s">
+      <c r="D98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I98" s="14" t="s">
+      <c r="I98" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J98" s="14" t="s">
+      <c r="J98" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K98" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L98" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="M98" s="14" t="n">
+      <c r="K98" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M98" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N98" s="14" t="n">
+      <c r="N98" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D99" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" s="14" t="s">
+      <c r="D99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I99" s="14" t="s">
+      <c r="I99" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J99" s="14" t="s">
+      <c r="J99" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K99" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="14" t="n">
+      <c r="K99" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="13" t="n">
         <v>105</v>
       </c>
-      <c r="M99" s="14" t="n">
+      <c r="M99" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N99" s="14" t="n">
+      <c r="N99" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="14" t="s">
+      <c r="A100" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C100" s="14" t="s">
+      <c r="C100" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D100" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="14" t="s">
+      <c r="D100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I100" s="14" t="s">
+      <c r="I100" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J100" s="14" t="s">
+      <c r="J100" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K100" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L100" s="14" t="n">
+      <c r="K100" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L100" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="M100" s="14" t="n">
+      <c r="M100" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N100" s="14" t="n">
+      <c r="N100" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="B101" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C101" s="14" t="s">
+      <c r="C101" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D101" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" s="14" t="s">
+      <c r="D101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I101" s="14" t="s">
+      <c r="I101" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J101" s="14" t="s">
+      <c r="J101" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K101" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L101" s="14" t="n">
+      <c r="K101" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="13" t="n">
         <v>115</v>
       </c>
-      <c r="M101" s="14" t="n">
+      <c r="M101" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N101" s="14" t="n">
+      <c r="N101" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D102" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="14" t="s">
+      <c r="D102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I102" s="14" t="s">
+      <c r="I102" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J102" s="14" t="s">
+      <c r="J102" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K102" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L102" s="14" t="n">
+      <c r="K102" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="M102" s="14" t="n">
+      <c r="M102" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N102" s="14" t="n">
+      <c r="N102" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="15" t="s">
+      <c r="A103" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="15" t="s">
+      <c r="D103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I103" s="15" t="s">
+      <c r="I103" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J103" s="15" t="s">
+      <c r="J103" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K103" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" s="15" t="n">
+      <c r="K103" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M103" s="14" t="n">
+      <c r="M103" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N103" s="15" t="n">
+      <c r="N103" s="14" t="n">
         <v>2</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="15" t="s">
+      <c r="A104" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B104" s="15" t="s">
+      <c r="B104" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D104" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="15" t="s">
+      <c r="D104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I104" s="15" t="s">
+      <c r="I104" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J104" s="15" t="s">
+      <c r="J104" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K104" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="15" t="n">
+      <c r="K104" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="M104" s="14" t="n">
+      <c r="M104" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N104" s="15" t="n">
+      <c r="N104" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="15" t="s">
+      <c r="A105" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="15" t="s">
+      <c r="D105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I105" s="15" t="s">
+      <c r="I105" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J105" s="15" t="s">
+      <c r="J105" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K105" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L105" s="15" t="n">
+      <c r="K105" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="M105" s="14" t="n">
+      <c r="M105" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N105" s="15" t="n">
+      <c r="N105" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="15" t="s">
+      <c r="A106" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B106" s="15" t="s">
+      <c r="B106" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D106" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="15" t="s">
+      <c r="D106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I106" s="15" t="s">
+      <c r="I106" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J106" s="15" t="s">
+      <c r="J106" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K106" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L106" s="15" t="n">
+      <c r="K106" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L106" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="M106" s="14" t="n">
+      <c r="M106" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N106" s="15" t="n">
+      <c r="N106" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="15" t="s">
+      <c r="A107" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="15" t="s">
+      <c r="D107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I107" s="15" t="s">
+      <c r="I107" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J107" s="15" t="s">
+      <c r="J107" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K107" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" s="15" t="n">
+      <c r="K107" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L107" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="M107" s="14" t="n">
+      <c r="M107" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N107" s="15" t="n">
+      <c r="N107" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="15" t="s">
+      <c r="A108" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C108" s="15" t="s">
+      <c r="C108" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D108" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" s="15" t="s">
+      <c r="D108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I108" s="15" t="s">
+      <c r="I108" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J108" s="15" t="s">
+      <c r="J108" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K108" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L108" s="15" t="n">
+      <c r="K108" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="M108" s="14" t="n">
+      <c r="M108" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N108" s="15" t="n">
+      <c r="N108" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="15" t="s">
+      <c r="A109" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="15" t="s">
+      <c r="D109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I109" s="15" t="s">
+      <c r="I109" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J109" s="15" t="s">
+      <c r="J109" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K109" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L109" s="15" t="n">
+      <c r="K109" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L109" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="M109" s="14" t="n">
+      <c r="M109" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N109" s="15" t="n">
+      <c r="N109" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="15" t="s">
+      <c r="A110" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B110" s="15" t="s">
+      <c r="B110" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C110" s="15" t="s">
+      <c r="C110" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D110" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" s="15" t="s">
+      <c r="D110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I110" s="15" t="s">
+      <c r="I110" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J110" s="15" t="s">
+      <c r="J110" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K110" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L110" s="15" t="n">
+      <c r="K110" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="M110" s="14" t="n">
+      <c r="M110" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N110" s="15" t="n">
+      <c r="N110" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="15" t="s">
+      <c r="A111" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C111" s="15" t="s">
+      <c r="C111" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D111" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="15" t="s">
+      <c r="D111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I111" s="15" t="s">
+      <c r="I111" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J111" s="15" t="s">
+      <c r="J111" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K111" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L111" s="15" t="n">
+      <c r="K111" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="M111" s="14" t="n">
+      <c r="M111" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N111" s="15" t="n">
+      <c r="N111" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="15" t="s">
+      <c r="A112" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C112" s="15" t="s">
+      <c r="C112" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H112" s="15" t="s">
+      <c r="D112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I112" s="15" t="s">
+      <c r="I112" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J112" s="15" t="s">
+      <c r="J112" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K112" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L112" s="15" t="n">
+      <c r="K112" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L112" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="M112" s="14" t="n">
+      <c r="M112" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N112" s="15" t="n">
+      <c r="N112" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="15" t="s">
+      <c r="A113" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="15" t="s">
+      <c r="D113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I113" s="15" t="s">
+      <c r="I113" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J113" s="15" t="s">
+      <c r="J113" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K113" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L113" s="15" t="n">
+      <c r="K113" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L113" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="M113" s="14" t="n">
+      <c r="M113" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N113" s="15" t="n">
+      <c r="N113" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="15" t="s">
+      <c r="A114" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B114" s="15" t="s">
+      <c r="B114" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C114" s="15" t="s">
+      <c r="C114" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D114" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" s="15" t="s">
+      <c r="D114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I114" s="15" t="s">
+      <c r="I114" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J114" s="15" t="s">
+      <c r="J114" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K114" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L114" s="15" t="n">
+      <c r="K114" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="M114" s="14" t="n">
+      <c r="M114" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N114" s="15" t="n">
+      <c r="N114" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="15" t="s">
+      <c r="A115" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B115" s="15" t="s">
+      <c r="B115" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D115" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" s="15" t="s">
+      <c r="D115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I115" s="15" t="s">
+      <c r="I115" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J115" s="15" t="s">
+      <c r="J115" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K115" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L115" s="15" t="n">
+      <c r="K115" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="M115" s="14" t="n">
+      <c r="M115" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N115" s="15" t="n">
+      <c r="N115" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="15" t="s">
+      <c r="A116" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B116" s="15" t="s">
+      <c r="B116" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C116" s="15" t="s">
+      <c r="C116" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="15" t="s">
+      <c r="D116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I116" s="15" t="s">
+      <c r="I116" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J116" s="15" t="s">
+      <c r="J116" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K116" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L116" s="15" t="n">
+      <c r="K116" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L116" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="M116" s="14" t="n">
+      <c r="M116" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N116" s="15" t="n">
+      <c r="N116" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="15" t="s">
+      <c r="A117" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B117" s="15" t="s">
+      <c r="B117" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D117" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H117" s="15" t="s">
+      <c r="D117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I117" s="15" t="s">
+      <c r="I117" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J117" s="15" t="s">
+      <c r="J117" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K117" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L117" s="15" t="n">
+      <c r="K117" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="M117" s="14" t="n">
+      <c r="M117" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N117" s="15" t="n">
+      <c r="N117" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="15" t="s">
+      <c r="A118" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="15" t="s">
+      <c r="B118" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C118" s="15" t="s">
+      <c r="C118" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D118" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H118" s="15" t="s">
+      <c r="D118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I118" s="15" t="s">
+      <c r="I118" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J118" s="15" t="s">
+      <c r="J118" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K118" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L118" s="15" t="n">
+      <c r="K118" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="M118" s="14" t="n">
+      <c r="M118" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N118" s="15" t="n">
+      <c r="N118" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="15" t="s">
+      <c r="A119" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B119" s="15" t="s">
+      <c r="B119" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C119" s="15" t="s">
+      <c r="C119" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D119" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H119" s="15" t="s">
+      <c r="D119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I119" s="15" t="s">
+      <c r="I119" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J119" s="15" t="s">
+      <c r="J119" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K119" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L119" s="15" t="n">
+      <c r="K119" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L119" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="M119" s="14" t="n">
+      <c r="M119" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N119" s="15" t="n">
+      <c r="N119" s="14" t="n">
         <v>2</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="15" t="s">
+      <c r="A120" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B120" s="15" t="s">
+      <c r="B120" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C120" s="15" t="s">
+      <c r="C120" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D120" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" s="15" t="s">
+      <c r="D120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I120" s="15" t="s">
+      <c r="I120" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J120" s="15" t="s">
+      <c r="J120" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K120" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L120" s="15" t="n">
+      <c r="K120" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L120" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="M120" s="14" t="n">
+      <c r="M120" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N120" s="15" t="n">
+      <c r="N120" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="15" t="s">
+      <c r="A121" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B121" s="15" t="s">
+      <c r="B121" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C121" s="15" t="s">
+      <c r="C121" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D121" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" s="15" t="s">
+      <c r="D121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I121" s="15" t="s">
+      <c r="I121" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J121" s="15" t="s">
+      <c r="J121" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K121" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L121" s="15" t="n">
+      <c r="K121" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="M121" s="14" t="n">
+      <c r="M121" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N121" s="15" t="n">
+      <c r="N121" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="15" t="s">
+      <c r="A122" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C122" s="15" t="s">
+      <c r="C122" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D122" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H122" s="15" t="s">
+      <c r="D122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I122" s="15" t="s">
+      <c r="I122" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J122" s="15" t="s">
+      <c r="J122" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K122" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L122" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="M122" s="14" t="n">
+      <c r="K122" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L122" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N122" s="15" t="n">
+      <c r="N122" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="15" t="s">
+      <c r="A123" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C123" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D123" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="15" t="s">
+      <c r="D123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I123" s="15" t="s">
+      <c r="I123" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J123" s="15" t="s">
+      <c r="J123" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K123" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L123" s="15" t="n">
+      <c r="K123" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L123" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="M123" s="14" t="n">
+      <c r="M123" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N123" s="15" t="n">
+      <c r="N123" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="15" t="s">
+      <c r="A124" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B124" s="15" t="s">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D124" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="15" t="s">
+      <c r="D124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I124" s="15" t="s">
+      <c r="I124" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J124" s="15" t="s">
+      <c r="J124" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K124" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="15" t="n">
+      <c r="K124" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L124" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="M124" s="14" t="n">
+      <c r="M124" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N124" s="15" t="n">
+      <c r="N124" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="15" t="s">
+      <c r="A125" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B125" s="15" t="s">
+      <c r="B125" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C125" s="15" t="s">
+      <c r="C125" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D125" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H125" s="15" t="s">
+      <c r="D125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I125" s="15" t="s">
+      <c r="I125" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J125" s="15" t="s">
+      <c r="J125" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K125" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L125" s="15" t="n">
+      <c r="K125" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="14" t="n">
         <v>115</v>
       </c>
-      <c r="M125" s="14" t="n">
+      <c r="M125" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N125" s="15" t="n">
+      <c r="N125" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="15" t="s">
+      <c r="A126" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B126" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C126" s="15" t="s">
+      <c r="C126" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D126" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="15" t="s">
+      <c r="D126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I126" s="15" t="s">
+      <c r="I126" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J126" s="15" t="s">
+      <c r="J126" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K126" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" s="15" t="n">
+      <c r="K126" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L126" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="M126" s="14" t="n">
+      <c r="M126" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N126" s="15" t="n">
+      <c r="N126" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J127" s="16"/>
-      <c r="K127" s="16"/>
-      <c r="L127" s="16"/>
-      <c r="M127" s="16"/>
-      <c r="N127" s="16"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
+      <c r="N127" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8804,8 +8796,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -8816,7 +8808,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -10297,8 +10289,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10309,7 +10301,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -12119,8 +12111,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="137">
   <si>
     <t xml:space="preserve">Hippocampome_Neurons_Names</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta_eta_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta_eta_min</t>
   </si>
   <si>
     <t xml:space="preserve">x_anat</t>
@@ -437,7 +443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -465,6 +471,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -533,7 +544,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -562,6 +573,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -571,6 +590,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -778,7 +801,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -2683,8 +2706,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2694,8 +2717,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S127"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:U127"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.77"/>
@@ -2704,6 +2727,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="15.88"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="17" style="7" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2755,2253 +2779,2499 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="T1" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="C2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" s="0" t="n">
+      <c r="K2" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="M2" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N2" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P2" s="9" t="n">
+      <c r="O2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P2" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="Q2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" s="0" t="n">
+      <c r="K3" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N3" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P3" s="9" t="n">
+      <c r="O3" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P3" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="Q3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" s="0" t="n">
+      <c r="K4" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P4" s="9" t="n">
+      <c r="O4" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P4" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9" t="n">
+      <c r="Q4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="5" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+    <row r="5" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="C5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="0" t="n">
+      <c r="K5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P5" s="9" t="n">
+      <c r="O5" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P5" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="9" t="n">
+      <c r="Q5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="6" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+    <row r="6" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="C6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="M6" s="8" t="n">
+      <c r="K6" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P6" s="9" t="n">
+      <c r="O6" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P6" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="9" t="n">
+      <c r="Q6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="7" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+    <row r="7" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="C7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" s="0" t="n">
+      <c r="K7" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P7" s="9" t="n">
+      <c r="O7" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P7" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R7" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S7" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="Q7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="C8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="0" t="n">
+      <c r="K8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P8" s="9" t="n">
+      <c r="O8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P8" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R8" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="Q8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U8" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="C9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="G9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="0" t="n">
+      <c r="K9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="N9" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P9" s="9" t="n">
+      <c r="O9" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P9" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S9" s="9" t="n">
+      <c r="Q9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+    <row r="10" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="n">
+      <c r="C10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="0" t="n">
+      <c r="K10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O10" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P10" s="9" t="n">
+      <c r="O10" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P10" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R10" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S10" s="9" t="n">
+      <c r="Q10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T10" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+    <row r="11" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="n">
+      <c r="C11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="0" t="n">
+      <c r="K11" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="N11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O11" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P11" s="9" t="n">
+      <c r="O11" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P11" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R11" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S11" s="9" t="n">
+      <c r="Q11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T11" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+    <row r="12" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7" t="n">
+      <c r="C12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="0" t="n">
+      <c r="K12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O12" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="9" t="n">
+      <c r="O12" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P12" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="Q12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T12" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S12" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="U12" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="n">
+      <c r="C13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="0" t="n">
+      <c r="K13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O13" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P13" s="9" t="n">
+      <c r="O13" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P13" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="Q13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T13" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="U13" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="7" t="n">
+      <c r="C14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="0" t="n">
+      <c r="K14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O14" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P14" s="9" t="n">
+      <c r="O14" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P14" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="Q14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T14" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="U14" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="15" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+    <row r="15" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7" t="n">
+      <c r="C15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="G15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="0" t="n">
+      <c r="K15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O15" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P15" s="9" t="n">
+      <c r="O15" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P15" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="Q15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T15" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="U15" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="16" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+    <row r="16" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="n">
+      <c r="C16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L16" s="0" t="n">
+      <c r="K16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="N16" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P16" s="9" t="n">
+      <c r="O16" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P16" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="Q16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T16" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S16" s="9" t="n">
+      <c r="U16" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="17" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+    <row r="17" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="7" t="n">
+      <c r="C17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="s">
+      <c r="G17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" s="0" t="n">
+      <c r="K17" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O17" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P17" s="9" t="n">
+      <c r="O17" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P17" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="Q17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T17" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="U17" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="C18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="0" t="n">
+      <c r="K18" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O18" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P18" s="9" t="n">
+      <c r="O18" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P18" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="Q18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T18" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S18" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="U18" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7" t="n">
+      <c r="C19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7" t="s">
+      <c r="G19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" s="0" t="n">
+      <c r="K19" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O19" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P19" s="9" t="n">
+      <c r="O19" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P19" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="Q19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T19" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="U19" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+    <row r="20" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7" t="n">
+      <c r="C20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="G20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="0" t="n">
+      <c r="K20" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O20" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P20" s="9" t="n">
+      <c r="O20" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P20" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="Q20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T20" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="U20" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="21" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    <row r="21" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="n">
+      <c r="C21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>160000</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="s">
+      <c r="G21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="0" t="n">
+      <c r="K21" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O21" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="P21" s="9" t="n">
+      <c r="O21" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P21" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="Q21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T21" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="U21" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="22" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+    <row r="22" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="10" t="n">
+      <c r="C22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10" t="s">
+      <c r="G22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="0" t="n">
+      <c r="K22" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="N22" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O22" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P22" s="12" t="n">
+      <c r="O22" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P22" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="Q22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10" t="n">
+      <c r="C23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="10" t="s">
+      <c r="G23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K23" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L23" s="0" t="n">
+      <c r="K23" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="N23" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P23" s="12" t="n">
+      <c r="O23" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P23" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
+      <c r="Q23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10" t="n">
+      <c r="C24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="10" t="s">
+      <c r="G24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" s="0" t="n">
+      <c r="K24" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="N24" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O24" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P24" s="12" t="n">
+      <c r="O24" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P24" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="9" t="n">
+      <c r="Q24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="25" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
+    <row r="25" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="10" t="n">
+      <c r="C25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="10" t="s">
+      <c r="G25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" s="0" t="n">
+      <c r="K25" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="N25" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O25" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P25" s="12" t="n">
+      <c r="O25" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P25" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="9" t="n">
+      <c r="Q25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="26" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
+    <row r="26" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="C26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="10" t="s">
+      <c r="G26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L26" s="0" t="n">
+      <c r="K26" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N26" s="11" t="n">
+      <c r="N26" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O26" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P26" s="12" t="n">
+      <c r="O26" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P26" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="9" t="n">
+      <c r="Q26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="27" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
+    <row r="27" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="10" t="n">
+      <c r="C27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="10" t="s">
+      <c r="G27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L27" s="0" t="n">
+      <c r="K27" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N27" s="11" t="n">
+      <c r="N27" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O27" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P27" s="12" t="n">
+      <c r="O27" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P27" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R27" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S27" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
+      <c r="Q27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T27" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U27" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="10" t="n">
+      <c r="C28" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="10" t="s">
+      <c r="G28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" s="0" t="n">
+      <c r="K28" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N28" s="11" t="n">
+      <c r="N28" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O28" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P28" s="12" t="n">
+      <c r="O28" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P28" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R28" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S28" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
+      <c r="Q28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T28" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="10" t="n">
+      <c r="C29" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="10" t="s">
+      <c r="G29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L29" s="0" t="n">
+      <c r="K29" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N29" s="11" t="n">
+      <c r="N29" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O29" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P29" s="12" t="n">
+      <c r="O29" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P29" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R29" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S29" s="9" t="n">
+      <c r="Q29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U29" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="30" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
+    <row r="30" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="10" t="n">
+      <c r="C30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="10" t="s">
+      <c r="G30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J30" s="10" t="s">
+      <c r="J30" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" s="0" t="n">
+      <c r="K30" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M30" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="N30" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O30" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P30" s="12" t="n">
+      <c r="O30" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P30" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S30" s="9" t="n">
+      <c r="Q30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T30" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="31" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+    <row r="31" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="10" t="n">
+      <c r="C31" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="10" t="s">
+      <c r="G31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L31" s="0" t="n">
+      <c r="K31" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N31" s="11" t="n">
+      <c r="N31" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O31" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P31" s="12" t="n">
+      <c r="O31" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P31" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R31" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="S31" s="9" t="n">
+      <c r="Q31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T31" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="32" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+    <row r="32" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="10" t="n">
+      <c r="C32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="10" t="s">
+      <c r="G32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K32" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="0" t="n">
-        <v>27</v>
-      </c>
-      <c r="M32" s="8" t="n">
+      <c r="K32" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="M32" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N32" s="11" t="n">
+      <c r="N32" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O32" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P32" s="12" t="n">
+      <c r="O32" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P32" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="Q32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T32" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S32" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
+      <c r="U32" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="10" t="n">
+      <c r="C33" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="10" t="s">
+      <c r="G33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K33" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L33" s="0" t="n">
+      <c r="K33" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N33" s="11" t="n">
+      <c r="N33" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O33" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P33" s="12" t="n">
+      <c r="O33" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P33" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="Q33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T33" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
+      <c r="U33" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="10" t="n">
+      <c r="C34" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="10" t="s">
+      <c r="G34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L34" s="0" t="n">
+      <c r="K34" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="11" t="n">
+      <c r="N34" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O34" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P34" s="12" t="n">
+      <c r="O34" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P34" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="Q34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T34" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="U34" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="35" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
+    <row r="35" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="10" t="n">
+      <c r="C35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="10" t="s">
+      <c r="G35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L35" s="0" t="n">
+      <c r="K35" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="11" t="n">
+      <c r="N35" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O35" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P35" s="12" t="n">
+      <c r="O35" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P35" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="Q35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T35" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S35" s="9" t="n">
+      <c r="U35" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="36" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
+    <row r="36" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="10" t="n">
+      <c r="C36" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="10" t="s">
+      <c r="G36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I36" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L36" s="0" t="n">
+      <c r="K36" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N36" s="11" t="n">
+      <c r="N36" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O36" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P36" s="12" t="n">
+      <c r="O36" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P36" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="Q36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T36" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="U36" s="11" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="37" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
+    <row r="37" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="10" t="n">
+      <c r="C37" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="10" t="s">
+      <c r="G37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L37" s="0" t="n">
+      <c r="K37" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L37" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N37" s="11" t="n">
+      <c r="N37" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O37" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P37" s="12" t="n">
+      <c r="O37" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P37" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="Q37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T37" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="s">
+      <c r="U37" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="10" t="n">
+      <c r="C38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="10" t="s">
+      <c r="G38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L38" s="0" t="n">
+      <c r="K38" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N38" s="11" t="n">
+      <c r="N38" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O38" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P38" s="12" t="n">
+      <c r="O38" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P38" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="Q38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T38" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
+      <c r="U38" s="11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="10" t="n">
+      <c r="C39" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="10" t="s">
+      <c r="G39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="0" t="n">
+      <c r="K39" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N39" s="11" t="n">
+      <c r="N39" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O39" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P39" s="12" t="n">
+      <c r="O39" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P39" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="Q39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T39" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="U39" s="11" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="40" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
+    <row r="40" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="10" t="n">
+      <c r="C40" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="10" t="s">
+      <c r="G40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="0" t="n">
+      <c r="K40" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N40" s="11" t="n">
+      <c r="N40" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O40" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P40" s="12" t="n">
+      <c r="O40" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P40" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="Q40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T40" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="U40" s="11" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="41" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="s">
+    <row r="41" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="10" t="n">
+      <c r="C41" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="13" t="n">
         <v>160000</v>
       </c>
-      <c r="G41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="10" t="s">
+      <c r="G41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="0" t="n">
+      <c r="K41" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N41" s="11" t="n">
+      <c r="N41" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O41" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="P41" s="12" t="n">
+      <c r="O41" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="P41" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="Q41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="T41" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="U41" s="11" t="n">
         <v>400</v>
       </c>
     </row>
@@ -5053,6 +5323,12 @@
       <c r="P42" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
@@ -5094,6 +5370,9 @@
         <v>0</v>
       </c>
       <c r="O43" s="3"/>
+      <c r="Q43" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
@@ -5135,6 +5414,9 @@
         <v>0</v>
       </c>
       <c r="O44" s="3"/>
+      <c r="Q44" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
@@ -5184,6 +5466,12 @@
       <c r="P45" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
@@ -5225,6 +5513,9 @@
         <v>0</v>
       </c>
       <c r="O46" s="3"/>
+      <c r="Q46" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
@@ -5274,6 +5565,12 @@
       <c r="P47" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
@@ -5322,6 +5619,12 @@
       <c r="P48" s="2" t="n">
         <v>15</v>
       </c>
+      <c r="Q48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
@@ -5370,7 +5673,11 @@
       <c r="P49" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q49" s="6" t="s">
+      <c r="Q49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" s="12"/>
+      <c r="S49" s="6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5421,6 +5728,12 @@
       <c r="P50" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
@@ -5462,6 +5775,9 @@
         <v>0</v>
       </c>
       <c r="O51" s="3"/>
+      <c r="Q51" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
@@ -5504,6 +5820,9 @@
         <v>0</v>
       </c>
       <c r="O52" s="3"/>
+      <c r="Q52" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
@@ -5546,6 +5865,9 @@
         <v>0</v>
       </c>
       <c r="O53" s="3"/>
+      <c r="Q53" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
@@ -5587,6 +5909,9 @@
         <v>0</v>
       </c>
       <c r="O54" s="3"/>
+      <c r="Q54" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
@@ -5628,6 +5953,9 @@
         <v>0</v>
       </c>
       <c r="O55" s="3"/>
+      <c r="Q55" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
@@ -5676,6 +6004,12 @@
       <c r="P56" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
@@ -5720,7 +6054,11 @@
       </c>
       <c r="O57" s="4"/>
       <c r="P57" s="2"/>
-      <c r="Q57" s="6" t="s">
+      <c r="Q57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" s="12"/>
+      <c r="S57" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5772,6 +6110,12 @@
       <c r="P58" s="2" t="n">
         <v>15</v>
       </c>
+      <c r="Q58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" s="12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
@@ -5814,6 +6158,9 @@
         <v>0</v>
       </c>
       <c r="O59" s="3"/>
+      <c r="Q59" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
@@ -5855,6 +6202,9 @@
         <v>0</v>
       </c>
       <c r="O60" s="3"/>
+      <c r="Q60" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
@@ -5897,6 +6247,9 @@
         <v>0</v>
       </c>
       <c r="O61" s="3"/>
+      <c r="Q61" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
@@ -5939,6 +6292,9 @@
         <v>0</v>
       </c>
       <c r="O62" s="3"/>
+      <c r="Q62" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
@@ -5980,6 +6336,9 @@
         <v>0</v>
       </c>
       <c r="O63" s="3"/>
+      <c r="Q63" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
@@ -6021,6 +6380,9 @@
         <v>0</v>
       </c>
       <c r="O64" s="3"/>
+      <c r="Q64" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
@@ -6063,6 +6425,9 @@
         <v>0</v>
       </c>
       <c r="O65" s="3"/>
+      <c r="Q65" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
@@ -6104,6 +6469,9 @@
         <v>0</v>
       </c>
       <c r="O66" s="3"/>
+      <c r="Q66" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
@@ -6153,6 +6521,12 @@
       <c r="P67" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
@@ -6195,6 +6569,9 @@
         <v>0</v>
       </c>
       <c r="O68" s="3"/>
+      <c r="Q68" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
@@ -6237,6 +6614,9 @@
         <v>0</v>
       </c>
       <c r="O69" s="3"/>
+      <c r="Q69" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
@@ -6285,6 +6665,12 @@
       <c r="P70" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
@@ -6327,6 +6713,9 @@
         <v>0</v>
       </c>
       <c r="O71" s="3"/>
+      <c r="Q71" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
@@ -6369,6 +6758,9 @@
         <v>0</v>
       </c>
       <c r="O72" s="3"/>
+      <c r="Q72" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
@@ -6417,6 +6809,12 @@
       <c r="P73" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
@@ -6465,7 +6863,13 @@
       <c r="P74" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q74" s="5" t="s">
+      <c r="Q74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="S74" s="5" t="s">
         <v>109</v>
       </c>
     </row>
@@ -6510,6 +6914,9 @@
         <v>0</v>
       </c>
       <c r="O75" s="3"/>
+      <c r="Q75" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
@@ -6551,6 +6958,9 @@
         <v>0</v>
       </c>
       <c r="O76" s="3"/>
+      <c r="Q76" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
@@ -6599,6 +7009,12 @@
       <c r="P77" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="Q77" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" s="12" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
@@ -6641,2142 +7057,2143 @@
         <v>0</v>
       </c>
       <c r="O78" s="3"/>
+      <c r="Q78" s="12"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="13" t="s">
+      <c r="D79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I79" s="13" t="s">
+      <c r="I79" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="13" t="s">
+      <c r="J79" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K79" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="13" t="n">
+      <c r="K79" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L79" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="M79" s="13" t="n">
+      <c r="M79" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N79" s="13" t="n">
+      <c r="N79" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="13" t="s">
+      <c r="D80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I80" s="13" t="s">
+      <c r="I80" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J80" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K80" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" s="13" t="n">
+      <c r="K80" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="M80" s="13" t="n">
+      <c r="M80" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N80" s="13" t="n">
+      <c r="N80" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D81" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="13" t="s">
+      <c r="D81" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I81" s="13" t="s">
+      <c r="I81" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J81" s="13" t="s">
+      <c r="J81" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K81" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L81" s="13" t="n">
+      <c r="K81" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="M81" s="13" t="n">
+      <c r="M81" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N81" s="13" t="n">
+      <c r="N81" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D82" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="13" t="s">
+      <c r="D82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I82" s="13" t="s">
+      <c r="I82" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="J82" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K82" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L82" s="13" t="n">
+      <c r="K82" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L82" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="M82" s="13" t="n">
+      <c r="M82" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N82" s="13" t="n">
+      <c r="N82" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D83" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="13" t="s">
+      <c r="D83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I83" s="13" t="s">
+      <c r="I83" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J83" s="13" t="s">
+      <c r="J83" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K83" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L83" s="13" t="n">
+      <c r="K83" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L83" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="M83" s="13" t="n">
+      <c r="M83" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N83" s="13" t="n">
+      <c r="N83" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D84" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="13" t="s">
+      <c r="D84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I84" s="13" t="s">
+      <c r="I84" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J84" s="13" t="s">
+      <c r="J84" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K84" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L84" s="13" t="n">
+      <c r="K84" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="M84" s="13" t="n">
+      <c r="M84" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N84" s="13" t="n">
+      <c r="N84" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D85" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="13" t="s">
+      <c r="D85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I85" s="13" t="s">
+      <c r="I85" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J85" s="13" t="s">
+      <c r="J85" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K85" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L85" s="13" t="n">
+      <c r="K85" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L85" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="M85" s="13" t="n">
+      <c r="M85" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N85" s="13" t="n">
+      <c r="N85" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="13" t="s">
+      <c r="D86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I86" s="13" t="s">
+      <c r="I86" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J86" s="13" t="s">
+      <c r="J86" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K86" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L86" s="13" t="n">
+      <c r="K86" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="M86" s="13" t="n">
+      <c r="M86" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N86" s="13" t="n">
+      <c r="N86" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="13" t="s">
+      <c r="D87" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I87" s="13" t="s">
+      <c r="I87" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J87" s="13" t="s">
+      <c r="J87" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K87" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" s="13" t="n">
+      <c r="K87" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="M87" s="13" t="n">
+      <c r="M87" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N87" s="13" t="n">
+      <c r="N87" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="13" t="s">
+      <c r="D88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I88" s="13" t="s">
+      <c r="I88" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J88" s="13" t="s">
+      <c r="J88" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K88" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" s="13" t="n">
+      <c r="K88" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="M88" s="13" t="n">
+      <c r="M88" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N88" s="13" t="n">
+      <c r="N88" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D89" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="13" t="s">
+      <c r="D89" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I89" s="13" t="s">
+      <c r="I89" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J89" s="13" t="s">
+      <c r="J89" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K89" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L89" s="13" t="n">
+      <c r="K89" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="M89" s="13" t="n">
+      <c r="M89" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N89" s="13" t="n">
+      <c r="N89" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D90" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="13" t="s">
+      <c r="D90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I90" s="13" t="s">
+      <c r="I90" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J90" s="13" t="s">
+      <c r="J90" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K90" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L90" s="13" t="n">
+      <c r="K90" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="M90" s="13" t="n">
+      <c r="M90" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N90" s="13" t="n">
+      <c r="N90" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D91" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" s="13" t="s">
+      <c r="D91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I91" s="13" t="s">
+      <c r="I91" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J91" s="13" t="s">
+      <c r="J91" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K91" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L91" s="13" t="n">
+      <c r="K91" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" s="16" t="n">
         <v>65</v>
       </c>
-      <c r="M91" s="13" t="n">
+      <c r="M91" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N91" s="13" t="n">
+      <c r="N91" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D92" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="13" t="s">
+      <c r="D92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I92" s="13" t="s">
+      <c r="I92" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J92" s="13" t="s">
+      <c r="J92" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K92" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L92" s="13" t="n">
+      <c r="K92" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L92" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="M92" s="13" t="n">
+      <c r="M92" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N92" s="13" t="n">
+      <c r="N92" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D93" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="13" t="s">
+      <c r="D93" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I93" s="13" t="s">
+      <c r="I93" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J93" s="13" t="s">
+      <c r="J93" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K93" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L93" s="13" t="n">
+      <c r="K93" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L93" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="M93" s="13" t="n">
+      <c r="M93" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N93" s="13" t="n">
+      <c r="N93" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D94" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="13" t="s">
+      <c r="D94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I94" s="13" t="s">
+      <c r="I94" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J94" s="13" t="s">
+      <c r="J94" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K94" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L94" s="13" t="n">
+      <c r="K94" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L94" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="M94" s="13" t="n">
+      <c r="M94" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N94" s="13" t="n">
+      <c r="N94" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D95" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="13" t="s">
+      <c r="D95" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I95" s="13" t="s">
+      <c r="I95" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J95" s="13" t="s">
+      <c r="J95" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K95" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L95" s="13" t="n">
+      <c r="K95" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" s="16" t="n">
         <v>85</v>
       </c>
-      <c r="M95" s="13" t="n">
+      <c r="M95" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N95" s="13" t="n">
+      <c r="N95" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D96" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="13" t="s">
+      <c r="D96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I96" s="13" t="s">
+      <c r="I96" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J96" s="13" t="s">
+      <c r="J96" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K96" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L96" s="13" t="n">
+      <c r="K96" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L96" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="M96" s="13" t="n">
+      <c r="M96" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N96" s="13" t="n">
+      <c r="N96" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D97" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="13" t="s">
+      <c r="D97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I97" s="13" t="s">
+      <c r="I97" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J97" s="13" t="s">
+      <c r="J97" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K97" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L97" s="13" t="n">
+      <c r="K97" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" s="16" t="n">
         <v>95</v>
       </c>
-      <c r="M97" s="13" t="n">
+      <c r="M97" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N97" s="13" t="n">
+      <c r="N97" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D98" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" s="13" t="s">
+      <c r="D98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I98" s="13" t="s">
+      <c r="I98" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J98" s="13" t="s">
+      <c r="J98" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K98" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L98" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="M98" s="13" t="n">
+      <c r="K98" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="M98" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N98" s="13" t="n">
+      <c r="N98" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D99" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" s="13" t="s">
+      <c r="D99" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I99" s="13" t="s">
+      <c r="I99" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J99" s="13" t="s">
+      <c r="J99" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K99" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="13" t="n">
+      <c r="K99" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="M99" s="13" t="n">
+      <c r="M99" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N99" s="13" t="n">
+      <c r="N99" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D100" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="13" t="s">
+      <c r="D100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I100" s="13" t="s">
+      <c r="I100" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J100" s="13" t="s">
+      <c r="J100" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K100" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L100" s="13" t="n">
+      <c r="K100" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L100" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="M100" s="13" t="n">
+      <c r="M100" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N100" s="13" t="n">
+      <c r="N100" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D101" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" s="13" t="s">
+      <c r="D101" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I101" s="13" t="s">
+      <c r="I101" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J101" s="13" t="s">
+      <c r="J101" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K101" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L101" s="13" t="n">
+      <c r="K101" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="16" t="n">
         <v>115</v>
       </c>
-      <c r="M101" s="13" t="n">
+      <c r="M101" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N101" s="13" t="n">
+      <c r="N101" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D102" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="13" t="s">
+      <c r="D102" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I102" s="13" t="s">
+      <c r="I102" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J102" s="13" t="s">
+      <c r="J102" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K102" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L102" s="13" t="n">
+      <c r="K102" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="M102" s="13" t="n">
+      <c r="M102" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N102" s="13" t="n">
+      <c r="N102" s="16" t="n">
         <v>5</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C103" s="14" t="s">
+      <c r="C103" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="14" t="s">
+      <c r="D103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I103" s="14" t="s">
+      <c r="I103" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J103" s="14" t="s">
+      <c r="J103" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K103" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" s="14" t="n">
+      <c r="K103" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="M103" s="13" t="n">
+      <c r="M103" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N103" s="14" t="n">
+      <c r="N103" s="17" t="n">
         <v>2</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="14" t="s">
+      <c r="D104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I104" s="14" t="s">
+      <c r="I104" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J104" s="14" t="s">
+      <c r="J104" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K104" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="14" t="n">
+      <c r="K104" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M104" s="13" t="n">
+      <c r="M104" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N104" s="14" t="n">
+      <c r="N104" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="14" t="s">
+      <c r="A105" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C105" s="14" t="s">
+      <c r="C105" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="14" t="s">
+      <c r="D105" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I105" s="14" t="s">
+      <c r="I105" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J105" s="14" t="s">
+      <c r="J105" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K105" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L105" s="14" t="n">
+      <c r="K105" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="M105" s="13" t="n">
+      <c r="M105" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N105" s="14" t="n">
+      <c r="N105" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B106" s="14" t="s">
+      <c r="B106" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C106" s="14" t="s">
+      <c r="C106" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D106" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="14" t="s">
+      <c r="D106" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I106" s="14" t="s">
+      <c r="I106" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J106" s="14" t="s">
+      <c r="J106" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K106" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L106" s="14" t="n">
+      <c r="K106" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L106" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="M106" s="13" t="n">
+      <c r="M106" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N106" s="14" t="n">
+      <c r="N106" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C107" s="14" t="s">
+      <c r="C107" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D107" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="14" t="s">
+      <c r="D107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I107" s="14" t="s">
+      <c r="I107" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J107" s="14" t="s">
+      <c r="J107" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K107" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" s="14" t="n">
+      <c r="K107" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L107" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="M107" s="13" t="n">
+      <c r="M107" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N107" s="14" t="n">
+      <c r="N107" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D108" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" s="14" t="s">
+      <c r="D108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I108" s="14" t="s">
+      <c r="I108" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J108" s="14" t="s">
+      <c r="J108" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K108" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L108" s="14" t="n">
+      <c r="K108" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="M108" s="13" t="n">
+      <c r="M108" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N108" s="14" t="n">
+      <c r="N108" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="14" t="s">
+      <c r="A109" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B109" s="14" t="s">
+      <c r="B109" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C109" s="14" t="s">
+      <c r="C109" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D109" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="14" t="s">
+      <c r="D109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I109" s="14" t="s">
+      <c r="I109" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J109" s="14" t="s">
+      <c r="J109" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K109" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L109" s="14" t="n">
+      <c r="K109" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L109" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="M109" s="13" t="n">
+      <c r="M109" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N109" s="14" t="n">
+      <c r="N109" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D110" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" s="14" t="s">
+      <c r="D110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I110" s="14" t="s">
+      <c r="I110" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J110" s="14" t="s">
+      <c r="J110" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K110" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L110" s="14" t="n">
+      <c r="K110" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="M110" s="13" t="n">
+      <c r="M110" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N110" s="14" t="n">
+      <c r="N110" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C111" s="14" t="s">
+      <c r="C111" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D111" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="14" t="s">
+      <c r="D111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I111" s="14" t="s">
+      <c r="I111" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J111" s="14" t="s">
+      <c r="J111" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K111" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L111" s="14" t="n">
+      <c r="K111" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="M111" s="13" t="n">
+      <c r="M111" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N111" s="14" t="n">
+      <c r="N111" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H112" s="14" t="s">
+      <c r="D112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I112" s="14" t="s">
+      <c r="I112" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J112" s="14" t="s">
+      <c r="J112" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K112" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L112" s="14" t="n">
+      <c r="K112" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L112" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="M112" s="13" t="n">
+      <c r="M112" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N112" s="14" t="n">
+      <c r="N112" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D113" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="14" t="s">
+      <c r="D113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I113" s="14" t="s">
+      <c r="I113" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J113" s="14" t="s">
+      <c r="J113" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K113" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L113" s="14" t="n">
+      <c r="K113" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L113" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="M113" s="13" t="n">
+      <c r="M113" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N113" s="14" t="n">
+      <c r="N113" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C114" s="14" t="s">
+      <c r="C114" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D114" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" s="14" t="s">
+      <c r="D114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I114" s="14" t="s">
+      <c r="I114" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J114" s="14" t="s">
+      <c r="J114" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K114" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L114" s="14" t="n">
+      <c r="K114" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="M114" s="13" t="n">
+      <c r="M114" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N114" s="14" t="n">
+      <c r="N114" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="B115" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C115" s="14" t="s">
+      <c r="C115" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D115" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" s="14" t="s">
+      <c r="D115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I115" s="14" t="s">
+      <c r="I115" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J115" s="14" t="s">
+      <c r="J115" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K115" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L115" s="14" t="n">
+      <c r="K115" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="M115" s="13" t="n">
+      <c r="M115" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N115" s="14" t="n">
+      <c r="N115" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="14" t="s">
+      <c r="A116" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C116" s="14" t="s">
+      <c r="C116" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D116" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="14" t="s">
+      <c r="D116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I116" s="14" t="s">
+      <c r="I116" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J116" s="14" t="s">
+      <c r="J116" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K116" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L116" s="14" t="n">
+      <c r="K116" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L116" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="M116" s="13" t="n">
+      <c r="M116" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N116" s="14" t="n">
+      <c r="N116" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C117" s="14" t="s">
+      <c r="C117" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D117" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H117" s="14" t="s">
+      <c r="D117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I117" s="14" t="s">
+      <c r="I117" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J117" s="14" t="s">
+      <c r="J117" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K117" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L117" s="14" t="n">
+      <c r="K117" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="M117" s="13" t="n">
+      <c r="M117" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N117" s="14" t="n">
+      <c r="N117" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="14" t="s">
+      <c r="A118" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B118" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C118" s="14" t="s">
+      <c r="C118" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D118" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H118" s="14" t="s">
+      <c r="D118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I118" s="14" t="s">
+      <c r="I118" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J118" s="14" t="s">
+      <c r="J118" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K118" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L118" s="14" t="n">
+      <c r="K118" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="M118" s="13" t="n">
+      <c r="M118" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N118" s="14" t="n">
+      <c r="N118" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B119" s="14" t="s">
+      <c r="B119" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C119" s="14" t="s">
+      <c r="C119" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D119" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H119" s="14" t="s">
+      <c r="D119" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I119" s="14" t="s">
+      <c r="I119" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J119" s="14" t="s">
+      <c r="J119" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K119" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L119" s="14" t="n">
+      <c r="K119" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L119" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="M119" s="13" t="n">
+      <c r="M119" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N119" s="14" t="n">
+      <c r="N119" s="17" t="n">
         <v>2</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="14" t="s">
+      <c r="A120" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C120" s="14" t="s">
+      <c r="C120" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D120" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" s="14" t="s">
+      <c r="D120" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I120" s="14" t="s">
+      <c r="I120" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J120" s="14" t="s">
+      <c r="J120" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K120" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L120" s="14" t="n">
+      <c r="K120" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L120" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="M120" s="13" t="n">
+      <c r="M120" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N120" s="14" t="n">
+      <c r="N120" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="14" t="s">
+      <c r="A121" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B121" s="14" t="s">
+      <c r="B121" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C121" s="14" t="s">
+      <c r="C121" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D121" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" s="14" t="s">
+      <c r="D121" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I121" s="14" t="s">
+      <c r="I121" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J121" s="14" t="s">
+      <c r="J121" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K121" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L121" s="14" t="n">
+      <c r="K121" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="17" t="n">
         <v>95</v>
       </c>
-      <c r="M121" s="13" t="n">
+      <c r="M121" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N121" s="14" t="n">
+      <c r="N121" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="14" t="s">
+      <c r="A122" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="14" t="s">
+      <c r="B122" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C122" s="14" t="s">
+      <c r="C122" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D122" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H122" s="14" t="s">
+      <c r="D122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I122" s="14" t="s">
+      <c r="I122" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J122" s="14" t="s">
+      <c r="J122" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K122" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L122" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="M122" s="13" t="n">
+      <c r="K122" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L122" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N122" s="14" t="n">
+      <c r="N122" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="14" t="s">
+      <c r="B123" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="14" t="s">
+      <c r="C123" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D123" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="14" t="s">
+      <c r="D123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I123" s="14" t="s">
+      <c r="I123" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J123" s="14" t="s">
+      <c r="J123" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K123" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L123" s="14" t="n">
+      <c r="K123" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L123" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="M123" s="13" t="n">
+      <c r="M123" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N123" s="14" t="n">
+      <c r="N123" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="14" t="s">
+      <c r="A124" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="14" t="s">
+      <c r="C124" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D124" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="14" t="s">
+      <c r="D124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I124" s="14" t="s">
+      <c r="I124" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J124" s="14" t="s">
+      <c r="J124" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K124" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="14" t="n">
+      <c r="K124" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L124" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="M124" s="13" t="n">
+      <c r="M124" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N124" s="14" t="n">
+      <c r="N124" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="14" t="s">
+      <c r="A125" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D125" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H125" s="14" t="s">
+      <c r="D125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I125" s="14" t="s">
+      <c r="I125" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J125" s="14" t="s">
+      <c r="J125" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K125" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L125" s="14" t="n">
+      <c r="K125" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="17" t="n">
         <v>115</v>
       </c>
-      <c r="M125" s="13" t="n">
+      <c r="M125" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N125" s="14" t="n">
+      <c r="N125" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="14" t="s">
+      <c r="A126" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D126" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="14" t="s">
+      <c r="D126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I126" s="14" t="s">
+      <c r="I126" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J126" s="14" t="s">
+      <c r="J126" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K126" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" s="14" t="n">
+      <c r="K126" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L126" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="M126" s="13" t="n">
+      <c r="M126" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="N126" s="14" t="n">
+      <c r="N126" s="17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8789,15 +9206,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q49" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
-    <hyperlink ref="Q57" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
+    <hyperlink ref="S49" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
+    <hyperlink ref="S57" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -8808,7 +9225,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -8823,7 +9240,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -8864,7 +9281,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>1</v>
@@ -8902,7 +9319,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
@@ -10154,7 +10571,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>27</v>
@@ -10210,7 +10627,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>1</v>
@@ -10248,7 +10665,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>1</v>
@@ -10289,8 +10706,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10301,7 +10718,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -12111,8 +12528,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -400,10 +400,10 @@
     <t xml:space="preserve">1.5</t>
   </si>
   <si>
+    <t xml:space="preserve">Delta_eta_min</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delta_eta_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delta_eta_min</t>
   </si>
   <si>
     <t xml:space="preserve">x_anat</t>
@@ -443,7 +443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -471,11 +471,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -544,7 +539,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -573,14 +568,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -590,10 +577,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -801,7 +784,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -2706,8 +2689,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2718,7 +2701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U127"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.77"/>
@@ -2727,7 +2710,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="15.88"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="17" style="7" width="11.62"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="17" style="2" width="11.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2779,10 +2762,10 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="5" t="s">
         <v>126</v>
       </c>
       <c r="S1" s="2" t="s">
@@ -2795,2483 +2778,2483 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="9" t="n">
+      <c r="C2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="K2" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M2" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="N2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P2" s="11" t="n">
+      <c r="P2" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="12" t="n">
+      <c r="Q2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="T2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="9" t="n">
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="K3" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="M3" s="10" t="n">
+      <c r="M3" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N3" s="10" t="n">
+      <c r="N3" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P3" s="11" t="n">
+      <c r="P3" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="12" t="n">
+      <c r="Q3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="T3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="9" t="s">
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="N4" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="P4" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="12" t="n">
+      <c r="Q4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="11" t="n">
+      <c r="T4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="5" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P5" s="11" t="n">
+      <c r="P5" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="12" t="n">
+      <c r="Q5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="n">
+      <c r="T5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="6" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+    <row r="6" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9" t="n">
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="12" t="n">
+      <c r="Q6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="11" t="n">
+      <c r="T6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="7" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+    <row r="7" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9" t="n">
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="10" t="n">
+      <c r="N7" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="12" t="n">
+      <c r="Q7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T7" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="T7" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="12" t="n">
+      <c r="Q8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T8" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U8" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="T8" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="9" t="n">
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="12" t="n">
+      <c r="Q9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T9" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U9" s="11" t="n">
+      <c r="T9" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="10" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+    <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P10" s="11" t="n">
+      <c r="P10" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="12" t="n">
+      <c r="Q10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T10" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U10" s="11" t="n">
+      <c r="T10" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="11" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+    <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="12" t="n">
+      <c r="Q11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T11" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U11" s="11" t="n">
+      <c r="T11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="12" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+    <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9" t="n">
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K12" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="12" t="n">
+      <c r="Q12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T12" s="11" t="n">
+      <c r="T12" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U12" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="U12" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9" t="n">
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="N13" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="12" t="n">
+      <c r="Q13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T13" s="11" t="n">
+      <c r="T13" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U13" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="U13" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="9" t="n">
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="9" t="s">
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="K14" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N14" s="10" t="n">
+      <c r="N14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="12" t="n">
+      <c r="Q14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T14" s="11" t="n">
+      <c r="T14" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U14" s="11" t="n">
+      <c r="U14" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="15" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+    <row r="15" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9" t="n">
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K15" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="N15" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="12" t="n">
+      <c r="Q15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="U15" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="16" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+    <row r="16" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="n">
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9" t="s">
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N16" s="10" t="n">
+      <c r="N16" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="12" t="n">
+      <c r="Q16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T16" s="11" t="n">
+      <c r="T16" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U16" s="11" t="n">
+      <c r="U16" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="17" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+    <row r="17" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9" t="n">
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="9" t="s">
+      <c r="G17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="10" t="n">
+      <c r="K17" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="N17" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="12" t="n">
+      <c r="Q17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U17" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="U17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="n">
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="9" t="s">
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="K18" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="10" t="n">
+      <c r="N18" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P18" s="11" t="n">
+      <c r="P18" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="12" t="n">
+      <c r="Q18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T18" s="11" t="n">
+      <c r="T18" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U18" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="U18" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="n">
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="9" t="s">
+      <c r="G19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="10" t="n">
+      <c r="K19" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N19" s="10" t="n">
+      <c r="N19" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O19" s="10" t="s">
+      <c r="O19" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="12" t="n">
+      <c r="Q19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="20" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+    <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9" t="n">
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="9" t="s">
+      <c r="G20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="10" t="n">
+      <c r="K20" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="10" t="n">
+      <c r="N20" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O20" s="10" t="s">
+      <c r="O20" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" s="12" t="n">
+      <c r="Q20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U20" s="11" t="n">
+      <c r="U20" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="21" s="11" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+    <row r="21" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9" t="n">
+      <c r="C21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="9" t="s">
+      <c r="G21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="K21" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N21" s="10" t="n">
+      <c r="N21" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="O21" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="Q21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" s="12" t="n">
+      <c r="Q21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T21" s="11" t="n">
+      <c r="T21" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U21" s="11" t="n">
+      <c r="U21" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="22" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+    <row r="22" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="13" t="n">
+      <c r="C22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="13" t="s">
+      <c r="G22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="I22" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="14" t="n">
+      <c r="K22" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N22" s="14" t="n">
+      <c r="N22" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O22" s="14" t="s">
+      <c r="O22" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P22" s="15" t="n">
+      <c r="P22" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="12" t="n">
+      <c r="Q22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="T22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="13" t="n">
+      <c r="C23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="13" t="s">
+      <c r="G23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="J23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N23" s="14" t="n">
+      <c r="N23" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="14" t="s">
+      <c r="O23" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P23" s="15" t="n">
+      <c r="P23" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" s="12" t="n">
+      <c r="Q23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="T23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="13" t="n">
+      <c r="C24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="G24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="14" t="n">
+      <c r="K24" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N24" s="14" t="n">
+      <c r="N24" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O24" s="14" t="s">
+      <c r="O24" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P24" s="15" t="n">
+      <c r="P24" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" s="12" t="n">
+      <c r="Q24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="11" t="n">
+      <c r="T24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="25" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+    <row r="25" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="13" t="n">
+      <c r="C25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="G25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N25" s="14" t="n">
+      <c r="N25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O25" s="14" t="s">
+      <c r="O25" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P25" s="15" t="n">
+      <c r="P25" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="12" t="n">
+      <c r="Q25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="11" t="n">
+      <c r="T25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="26" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+    <row r="26" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="13" t="n">
+      <c r="C26" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="13" t="s">
+      <c r="G26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="14" t="n">
+      <c r="K26" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N26" s="14" t="n">
+      <c r="N26" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O26" s="14" t="s">
+      <c r="O26" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P26" s="15" t="n">
+      <c r="P26" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" s="12" t="n">
+      <c r="Q26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="n">
+      <c r="T26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="27" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+    <row r="27" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="13" t="n">
+      <c r="C27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="13" t="s">
+      <c r="G27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="13" t="s">
+      <c r="I27" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="14" t="n">
+      <c r="K27" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N27" s="14" t="n">
+      <c r="N27" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O27" s="14" t="s">
+      <c r="O27" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P27" s="15" t="n">
+      <c r="P27" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="12" t="n">
+      <c r="Q27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T27" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U27" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="T27" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="13" t="n">
+      <c r="C28" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="13" t="s">
+      <c r="G28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="14" t="n">
+      <c r="K28" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N28" s="14" t="n">
+      <c r="N28" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O28" s="14" t="s">
+      <c r="O28" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P28" s="15" t="n">
+      <c r="P28" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" s="12" t="n">
+      <c r="Q28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T28" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U28" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="T28" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="13" t="n">
+      <c r="C29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="13" t="s">
+      <c r="G29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="14" t="n">
+      <c r="K29" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N29" s="14" t="n">
+      <c r="N29" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O29" s="14" t="s">
+      <c r="O29" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P29" s="15" t="n">
+      <c r="P29" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" s="12" t="n">
+      <c r="Q29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T29" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U29" s="11" t="n">
+      <c r="T29" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U29" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="30" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+    <row r="30" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="13" t="n">
+      <c r="C30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="13" t="s">
+      <c r="G30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="I30" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="14" t="n">
+      <c r="K30" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N30" s="14" t="n">
+      <c r="N30" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O30" s="14" t="s">
+      <c r="O30" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P30" s="15" t="n">
+      <c r="P30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" s="12" t="n">
+      <c r="Q30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T30" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U30" s="11" t="n">
+      <c r="T30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="31" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+    <row r="31" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="13" t="n">
+      <c r="C31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="13" t="s">
+      <c r="G31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J31" s="13" t="s">
+      <c r="J31" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="14" t="n">
+      <c r="K31" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N31" s="14" t="n">
+      <c r="N31" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O31" s="14" t="s">
+      <c r="O31" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P31" s="15" t="n">
+      <c r="P31" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" s="12" t="n">
+      <c r="Q31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T31" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="U31" s="11" t="n">
+      <c r="T31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="32" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+    <row r="32" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="13" t="n">
+      <c r="C32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="13" t="s">
+      <c r="G32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="13" t="s">
+      <c r="I32" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K32" s="14" t="n">
+      <c r="K32" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N32" s="14" t="n">
+      <c r="N32" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O32" s="14" t="s">
+      <c r="O32" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P32" s="15" t="n">
+      <c r="P32" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" s="12" t="n">
+      <c r="Q32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T32" s="11" t="n">
+      <c r="T32" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U32" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
+      <c r="U32" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="13" t="n">
+      <c r="C33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="13" t="s">
+      <c r="G33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K33" s="14" t="n">
+      <c r="K33" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N33" s="14" t="n">
+      <c r="N33" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O33" s="14" t="s">
+      <c r="O33" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P33" s="15" t="n">
+      <c r="P33" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" s="12" t="n">
+      <c r="Q33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T33" s="11" t="n">
+      <c r="T33" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U33" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+      <c r="U33" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="13" t="n">
+      <c r="C34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G34" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="13" t="s">
+      <c r="G34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="14" t="n">
+      <c r="K34" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="14" t="n">
+      <c r="N34" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O34" s="14" t="s">
+      <c r="O34" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P34" s="15" t="n">
+      <c r="P34" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" s="12" t="n">
+      <c r="Q34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T34" s="11" t="n">
+      <c r="T34" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U34" s="11" t="n">
+      <c r="U34" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="35" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+    <row r="35" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="13" t="n">
+      <c r="C35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G35" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="13" t="s">
+      <c r="G35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="14" t="n">
+      <c r="K35" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="M35" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="14" t="n">
+      <c r="N35" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O35" s="14" t="s">
+      <c r="O35" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P35" s="15" t="n">
+      <c r="P35" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" s="12" t="n">
+      <c r="Q35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T35" s="11" t="n">
+      <c r="T35" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U35" s="11" t="n">
+      <c r="U35" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="36" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+    <row r="36" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="13" t="n">
+      <c r="C36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G36" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="13" t="s">
+      <c r="G36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="14" t="n">
+      <c r="K36" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N36" s="14" t="n">
+      <c r="N36" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O36" s="14" t="s">
+      <c r="O36" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P36" s="15" t="n">
+      <c r="P36" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" s="12" t="n">
+      <c r="Q36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T36" s="11" t="n">
+      <c r="T36" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="U36" s="11" t="n">
+      <c r="U36" s="9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="37" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+    <row r="37" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="13" t="n">
+      <c r="C37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G37" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="13" t="s">
+      <c r="G37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N37" s="14" t="n">
+      <c r="N37" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O37" s="14" t="s">
+      <c r="O37" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P37" s="15" t="n">
+      <c r="P37" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" s="12" t="n">
+      <c r="Q37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T37" s="11" t="n">
+      <c r="T37" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U37" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+      <c r="U37" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="13" t="n">
+      <c r="C38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="13" t="s">
+      <c r="G38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="14" t="n">
+      <c r="K38" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N38" s="14" t="n">
+      <c r="N38" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O38" s="14" t="s">
+      <c r="O38" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P38" s="15" t="n">
+      <c r="P38" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" s="12" t="n">
+      <c r="Q38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T38" s="11" t="n">
+      <c r="T38" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U38" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
+      <c r="U38" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="13" t="n">
+      <c r="C39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="13" t="s">
+      <c r="G39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J39" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="14" t="n">
+      <c r="K39" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N39" s="14" t="n">
+      <c r="N39" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O39" s="14" t="s">
+      <c r="O39" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P39" s="15" t="n">
+      <c r="P39" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" s="12" t="n">
+      <c r="Q39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T39" s="11" t="n">
+      <c r="T39" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U39" s="11" t="n">
+      <c r="U39" s="9" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="40" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
+    <row r="40" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="13" t="n">
+      <c r="C40" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="13" t="s">
+      <c r="G40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="I40" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="14" t="n">
+      <c r="K40" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N40" s="14" t="n">
+      <c r="N40" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O40" s="14" t="s">
+      <c r="O40" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P40" s="15" t="n">
+      <c r="P40" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" s="12" t="n">
+      <c r="Q40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T40" s="11" t="n">
+      <c r="T40" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U40" s="11" t="n">
+      <c r="U40" s="9" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="41" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+    <row r="41" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="13" t="n">
+      <c r="C41" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="10" t="n">
         <v>160000</v>
       </c>
-      <c r="G41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="13" t="s">
+      <c r="G41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="I41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J41" s="13" t="s">
+      <c r="J41" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="14" t="n">
+      <c r="K41" s="11" t="n">
         <v>8</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N41" s="14" t="n">
+      <c r="N41" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="O41" s="14" t="s">
+      <c r="O41" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P41" s="15" t="n">
+      <c r="P41" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="Q41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" s="12" t="n">
+      <c r="Q41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T41" s="11" t="n">
+      <c r="T41" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="U41" s="11" t="n">
+      <c r="U41" s="9" t="n">
         <v>400</v>
       </c>
     </row>
@@ -5323,10 +5306,10 @@
       <c r="P42" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" s="12" t="n">
+      <c r="Q42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5370,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="3"/>
-      <c r="Q43" s="12" t="n">
+      <c r="Q43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5414,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="3"/>
-      <c r="Q44" s="12" t="n">
+      <c r="Q44" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5466,10 +5449,10 @@
       <c r="P45" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" s="12" t="n">
+      <c r="Q45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5513,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="3"/>
-      <c r="Q46" s="12" t="n">
+      <c r="Q46" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5565,10 +5548,10 @@
       <c r="P47" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" s="12" t="n">
+      <c r="Q47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5619,10 +5602,10 @@
       <c r="P48" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="Q48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" s="12" t="n">
+      <c r="Q48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -5673,10 +5656,9 @@
       <c r="P49" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q49" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" s="12"/>
+      <c r="Q49" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S49" s="6" t="s">
         <v>48</v>
       </c>
@@ -5728,10 +5710,10 @@
       <c r="P50" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" s="12" t="n">
+      <c r="Q50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5775,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="3"/>
-      <c r="Q51" s="12" t="n">
+      <c r="Q51" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5820,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="3"/>
-      <c r="Q52" s="12" t="n">
+      <c r="Q52" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5865,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="3"/>
-      <c r="Q53" s="12" t="n">
+      <c r="Q53" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5909,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="3"/>
-      <c r="Q54" s="12" t="n">
+      <c r="Q54" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5953,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="3"/>
-      <c r="Q55" s="12" t="n">
+      <c r="Q55" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6004,10 +5986,10 @@
       <c r="P56" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q56" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" s="12" t="n">
+      <c r="Q56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6054,10 +6036,9 @@
       </c>
       <c r="O57" s="4"/>
       <c r="P57" s="2"/>
-      <c r="Q57" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" s="12"/>
+      <c r="Q57" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S57" s="6" t="s">
         <v>67</v>
       </c>
@@ -6110,10 +6091,10 @@
       <c r="P58" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="Q58" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" s="12" t="n">
+      <c r="Q58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -6158,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="3"/>
-      <c r="Q59" s="12" t="n">
+      <c r="Q59" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6202,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="3"/>
-      <c r="Q60" s="12" t="n">
+      <c r="Q60" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6247,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3"/>
-      <c r="Q61" s="12" t="n">
+      <c r="Q61" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6292,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="3"/>
-      <c r="Q62" s="12" t="n">
+      <c r="Q62" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6336,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="3"/>
-      <c r="Q63" s="12" t="n">
+      <c r="Q63" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6380,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="3"/>
-      <c r="Q64" s="12" t="n">
+      <c r="Q64" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6425,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="3"/>
-      <c r="Q65" s="12" t="n">
+      <c r="Q65" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6469,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="3"/>
-      <c r="Q66" s="12" t="n">
+      <c r="Q66" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6521,10 +6502,10 @@
       <c r="P67" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q67" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" s="12" t="n">
+      <c r="Q67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6569,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="3"/>
-      <c r="Q68" s="12" t="n">
+      <c r="Q68" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6614,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="3"/>
-      <c r="Q69" s="12" t="n">
+      <c r="Q69" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6665,10 +6646,10 @@
       <c r="P70" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q70" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="12" t="n">
+      <c r="Q70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6713,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="3"/>
-      <c r="Q71" s="12" t="n">
+      <c r="Q71" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6758,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="3"/>
-      <c r="Q72" s="12" t="n">
+      <c r="Q72" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6809,10 +6790,10 @@
       <c r="P73" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" s="12" t="n">
+      <c r="Q73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6863,10 +6844,10 @@
       <c r="P74" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q74" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R74" s="12" t="n">
+      <c r="Q74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" s="2" t="n">
         <v>80</v>
       </c>
       <c r="S74" s="5" t="s">
@@ -6914,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="3"/>
-      <c r="Q75" s="12" t="n">
+      <c r="Q75" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6958,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="3"/>
-      <c r="Q76" s="12" t="n">
+      <c r="Q76" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7009,10 +6990,10 @@
       <c r="P77" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q77" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" s="12" t="n">
+      <c r="Q77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -7057,2143 +7038,2142 @@
         <v>0</v>
       </c>
       <c r="O78" s="3"/>
-      <c r="Q78" s="12"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D79" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="16" t="s">
+      <c r="D79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I79" s="16" t="s">
+      <c r="I79" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="16" t="s">
+      <c r="J79" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K79" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="16" t="n">
+      <c r="K79" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L79" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="M79" s="16" t="n">
+      <c r="M79" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N79" s="16" t="n">
+      <c r="N79" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D80" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="16" t="s">
+      <c r="D80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I80" s="16" t="s">
+      <c r="I80" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J80" s="16" t="s">
+      <c r="J80" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K80" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" s="16" t="n">
+      <c r="K80" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="M80" s="16" t="n">
+      <c r="M80" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N80" s="16" t="n">
+      <c r="N80" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D81" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="16" t="s">
+      <c r="D81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I81" s="16" t="s">
+      <c r="I81" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J81" s="16" t="s">
+      <c r="J81" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K81" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L81" s="16" t="n">
+      <c r="K81" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="M81" s="16" t="n">
+      <c r="M81" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N81" s="16" t="n">
+      <c r="N81" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D82" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="16" t="s">
+      <c r="D82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I82" s="16" t="s">
+      <c r="I82" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J82" s="16" t="s">
+      <c r="J82" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K82" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L82" s="16" t="n">
+      <c r="K82" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L82" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="M82" s="16" t="n">
+      <c r="M82" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N82" s="16" t="n">
+      <c r="N82" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D83" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="16" t="s">
+      <c r="D83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I83" s="16" t="s">
+      <c r="I83" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J83" s="16" t="s">
+      <c r="J83" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K83" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L83" s="16" t="n">
+      <c r="K83" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L83" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="M83" s="16" t="n">
+      <c r="M83" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N83" s="16" t="n">
+      <c r="N83" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B84" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D84" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="16" t="s">
+      <c r="D84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I84" s="16" t="s">
+      <c r="I84" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J84" s="16" t="s">
+      <c r="J84" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K84" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L84" s="16" t="n">
+      <c r="K84" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="M84" s="16" t="n">
+      <c r="M84" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N84" s="16" t="n">
+      <c r="N84" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C85" s="16" t="s">
+      <c r="C85" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="16" t="s">
+      <c r="D85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I85" s="16" t="s">
+      <c r="I85" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J85" s="16" t="s">
+      <c r="J85" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K85" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L85" s="16" t="n">
+      <c r="K85" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L85" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="M85" s="16" t="n">
+      <c r="M85" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N85" s="16" t="n">
+      <c r="N85" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C86" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="16" t="s">
+      <c r="D86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I86" s="16" t="s">
+      <c r="I86" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J86" s="16" t="s">
+      <c r="J86" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K86" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L86" s="16" t="n">
+      <c r="K86" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="M86" s="16" t="n">
+      <c r="M86" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N86" s="16" t="n">
+      <c r="N86" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B87" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="16" t="s">
+      <c r="D87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I87" s="16" t="s">
+      <c r="I87" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J87" s="16" t="s">
+      <c r="J87" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K87" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" s="16" t="n">
+      <c r="K87" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="M87" s="16" t="n">
+      <c r="M87" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N87" s="16" t="n">
+      <c r="N87" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C88" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="16" t="s">
+      <c r="D88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I88" s="16" t="s">
+      <c r="I88" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J88" s="16" t="s">
+      <c r="J88" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K88" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" s="16" t="n">
+      <c r="K88" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="M88" s="16" t="n">
+      <c r="M88" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N88" s="16" t="n">
+      <c r="N88" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D89" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="16" t="s">
+      <c r="D89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I89" s="16" t="s">
+      <c r="I89" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J89" s="16" t="s">
+      <c r="J89" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K89" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L89" s="16" t="n">
+      <c r="K89" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="M89" s="16" t="n">
+      <c r="M89" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N89" s="16" t="n">
+      <c r="N89" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B90" s="16" t="s">
+      <c r="B90" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D90" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="16" t="s">
+      <c r="D90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I90" s="16" t="s">
+      <c r="I90" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J90" s="16" t="s">
+      <c r="J90" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K90" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L90" s="16" t="n">
+      <c r="K90" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="M90" s="16" t="n">
+      <c r="M90" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N90" s="16" t="n">
+      <c r="N90" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D91" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" s="16" t="s">
+      <c r="D91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I91" s="16" t="s">
+      <c r="I91" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J91" s="16" t="s">
+      <c r="J91" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K91" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L91" s="16" t="n">
+      <c r="K91" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="M91" s="16" t="n">
+      <c r="M91" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N91" s="16" t="n">
+      <c r="N91" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B92" s="16" t="s">
+      <c r="B92" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C92" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D92" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="16" t="s">
+      <c r="D92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I92" s="16" t="s">
+      <c r="I92" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J92" s="16" t="s">
+      <c r="J92" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K92" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L92" s="16" t="n">
+      <c r="K92" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L92" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="M92" s="16" t="n">
+      <c r="M92" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N92" s="16" t="n">
+      <c r="N92" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B93" s="16" t="s">
+      <c r="B93" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C93" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D93" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="16" t="s">
+      <c r="D93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I93" s="16" t="s">
+      <c r="I93" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J93" s="16" t="s">
+      <c r="J93" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K93" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L93" s="16" t="n">
+      <c r="K93" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L93" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="M93" s="16" t="n">
+      <c r="M93" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N93" s="16" t="n">
+      <c r="N93" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C94" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D94" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="16" t="s">
+      <c r="D94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I94" s="16" t="s">
+      <c r="I94" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J94" s="16" t="s">
+      <c r="J94" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K94" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L94" s="16" t="n">
+      <c r="K94" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L94" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="M94" s="16" t="n">
+      <c r="M94" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N94" s="16" t="n">
+      <c r="N94" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C95" s="16" t="s">
+      <c r="C95" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D95" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="16" t="s">
+      <c r="D95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I95" s="16" t="s">
+      <c r="I95" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J95" s="16" t="s">
+      <c r="J95" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K95" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L95" s="16" t="n">
+      <c r="K95" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" s="13" t="n">
         <v>85</v>
       </c>
-      <c r="M95" s="16" t="n">
+      <c r="M95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N95" s="16" t="n">
+      <c r="N95" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C96" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D96" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="16" t="s">
+      <c r="D96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I96" s="16" t="s">
+      <c r="I96" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J96" s="16" t="s">
+      <c r="J96" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K96" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L96" s="16" t="n">
+      <c r="K96" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L96" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="M96" s="16" t="n">
+      <c r="M96" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N96" s="16" t="n">
+      <c r="N96" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B97" s="16" t="s">
+      <c r="B97" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C97" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D97" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="16" t="s">
+      <c r="D97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I97" s="16" t="s">
+      <c r="I97" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J97" s="16" t="s">
+      <c r="J97" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K97" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L97" s="16" t="n">
+      <c r="K97" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" s="13" t="n">
         <v>95</v>
       </c>
-      <c r="M97" s="16" t="n">
+      <c r="M97" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N97" s="16" t="n">
+      <c r="N97" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="16" t="s">
+      <c r="A98" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B98" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C98" s="16" t="s">
+      <c r="C98" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D98" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" s="16" t="s">
+      <c r="D98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I98" s="16" t="s">
+      <c r="I98" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J98" s="16" t="s">
+      <c r="J98" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K98" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L98" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="M98" s="16" t="n">
+      <c r="K98" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M98" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N98" s="16" t="n">
+      <c r="N98" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="C99" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D99" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" s="16" t="s">
+      <c r="D99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I99" s="16" t="s">
+      <c r="I99" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J99" s="16" t="s">
+      <c r="J99" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K99" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="16" t="n">
+      <c r="K99" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="13" t="n">
         <v>105</v>
       </c>
-      <c r="M99" s="16" t="n">
+      <c r="M99" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N99" s="16" t="n">
+      <c r="N99" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B100" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="C100" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D100" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="16" t="s">
+      <c r="D100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I100" s="16" t="s">
+      <c r="I100" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J100" s="16" t="s">
+      <c r="J100" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K100" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L100" s="16" t="n">
+      <c r="K100" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L100" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="M100" s="16" t="n">
+      <c r="M100" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N100" s="16" t="n">
+      <c r="N100" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O100" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C101" s="16" t="s">
+      <c r="C101" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D101" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" s="16" t="s">
+      <c r="D101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I101" s="16" t="s">
+      <c r="I101" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J101" s="16" t="s">
+      <c r="J101" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K101" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L101" s="16" t="n">
+      <c r="K101" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="13" t="n">
         <v>115</v>
       </c>
-      <c r="M101" s="16" t="n">
+      <c r="M101" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N101" s="16" t="n">
+      <c r="N101" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C102" s="16" t="s">
+      <c r="C102" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D102" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="16" t="s">
+      <c r="D102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I102" s="16" t="s">
+      <c r="I102" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J102" s="16" t="s">
+      <c r="J102" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K102" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L102" s="16" t="n">
+      <c r="K102" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="M102" s="16" t="n">
+      <c r="M102" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N102" s="16" t="n">
+      <c r="N102" s="13" t="n">
         <v>5</v>
       </c>
       <c r="O102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B103" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="17" t="s">
+      <c r="D103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I103" s="17" t="s">
+      <c r="I103" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J103" s="17" t="s">
+      <c r="J103" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K103" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" s="17" t="n">
+      <c r="K103" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M103" s="16" t="n">
+      <c r="M103" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N103" s="17" t="n">
+      <c r="N103" s="14" t="n">
         <v>2</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B104" s="17" t="s">
+      <c r="B104" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C104" s="17" t="s">
+      <c r="C104" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D104" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="17" t="s">
+      <c r="D104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I104" s="17" t="s">
+      <c r="I104" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J104" s="17" t="s">
+      <c r="J104" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K104" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="17" t="n">
+      <c r="K104" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="M104" s="16" t="n">
+      <c r="M104" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N104" s="17" t="n">
+      <c r="N104" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B105" s="17" t="s">
+      <c r="B105" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C105" s="17" t="s">
+      <c r="C105" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D105" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="17" t="s">
+      <c r="D105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I105" s="17" t="s">
+      <c r="I105" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J105" s="17" t="s">
+      <c r="J105" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K105" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L105" s="17" t="n">
+      <c r="K105" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="M105" s="16" t="n">
+      <c r="M105" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N105" s="17" t="n">
+      <c r="N105" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="17" t="s">
+      <c r="A106" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B106" s="17" t="s">
+      <c r="B106" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C106" s="17" t="s">
+      <c r="C106" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D106" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="17" t="s">
+      <c r="D106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I106" s="17" t="s">
+      <c r="I106" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J106" s="17" t="s">
+      <c r="J106" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K106" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L106" s="17" t="n">
+      <c r="K106" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L106" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="M106" s="16" t="n">
+      <c r="M106" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N106" s="17" t="n">
+      <c r="N106" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="17" t="s">
+      <c r="A107" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B107" s="17" t="s">
+      <c r="B107" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C107" s="17" t="s">
+      <c r="C107" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D107" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="17" t="s">
+      <c r="D107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I107" s="17" t="s">
+      <c r="I107" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J107" s="17" t="s">
+      <c r="J107" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K107" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" s="17" t="n">
+      <c r="K107" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L107" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="M107" s="16" t="n">
+      <c r="M107" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N107" s="17" t="n">
+      <c r="N107" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="17" t="s">
+      <c r="A108" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B108" s="17" t="s">
+      <c r="B108" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C108" s="17" t="s">
+      <c r="C108" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D108" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" s="17" t="s">
+      <c r="D108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I108" s="17" t="s">
+      <c r="I108" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J108" s="17" t="s">
+      <c r="J108" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K108" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L108" s="17" t="n">
+      <c r="K108" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="M108" s="16" t="n">
+      <c r="M108" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N108" s="17" t="n">
+      <c r="N108" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="17" t="s">
+      <c r="A109" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B109" s="17" t="s">
+      <c r="B109" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C109" s="17" t="s">
+      <c r="C109" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D109" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="17" t="s">
+      <c r="D109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I109" s="17" t="s">
+      <c r="I109" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J109" s="17" t="s">
+      <c r="J109" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K109" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L109" s="17" t="n">
+      <c r="K109" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L109" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="M109" s="16" t="n">
+      <c r="M109" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N109" s="17" t="n">
+      <c r="N109" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="17" t="s">
+      <c r="A110" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B110" s="17" t="s">
+      <c r="B110" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C110" s="17" t="s">
+      <c r="C110" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D110" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" s="17" t="s">
+      <c r="D110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I110" s="17" t="s">
+      <c r="I110" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J110" s="17" t="s">
+      <c r="J110" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K110" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L110" s="17" t="n">
+      <c r="K110" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="M110" s="16" t="n">
+      <c r="M110" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N110" s="17" t="n">
+      <c r="N110" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="17" t="s">
+      <c r="A111" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="17" t="s">
+      <c r="B111" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C111" s="17" t="s">
+      <c r="C111" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D111" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="17" t="s">
+      <c r="D111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I111" s="17" t="s">
+      <c r="I111" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J111" s="17" t="s">
+      <c r="J111" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K111" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L111" s="17" t="n">
+      <c r="K111" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="M111" s="16" t="n">
+      <c r="M111" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N111" s="17" t="n">
+      <c r="N111" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="17" t="s">
+      <c r="A112" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H112" s="17" t="s">
+      <c r="D112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I112" s="17" t="s">
+      <c r="I112" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J112" s="17" t="s">
+      <c r="J112" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K112" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L112" s="17" t="n">
+      <c r="K112" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L112" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="M112" s="16" t="n">
+      <c r="M112" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N112" s="17" t="n">
+      <c r="N112" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D113" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="17" t="s">
+      <c r="D113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I113" s="17" t="s">
+      <c r="I113" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J113" s="17" t="s">
+      <c r="J113" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K113" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L113" s="17" t="n">
+      <c r="K113" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L113" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="M113" s="16" t="n">
+      <c r="M113" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N113" s="17" t="n">
+      <c r="N113" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="17" t="s">
+      <c r="A114" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B114" s="17" t="s">
+      <c r="B114" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="C114" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D114" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" s="17" t="s">
+      <c r="D114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I114" s="17" t="s">
+      <c r="I114" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J114" s="17" t="s">
+      <c r="J114" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K114" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L114" s="17" t="n">
+      <c r="K114" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="M114" s="16" t="n">
+      <c r="M114" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N114" s="17" t="n">
+      <c r="N114" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B115" s="17" t="s">
+      <c r="B115" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C115" s="17" t="s">
+      <c r="C115" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D115" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" s="17" t="s">
+      <c r="D115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I115" s="17" t="s">
+      <c r="I115" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J115" s="17" t="s">
+      <c r="J115" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K115" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L115" s="17" t="n">
+      <c r="K115" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="M115" s="16" t="n">
+      <c r="M115" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N115" s="17" t="n">
+      <c r="N115" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B116" s="17" t="s">
+      <c r="B116" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C116" s="17" t="s">
+      <c r="C116" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D116" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="17" t="s">
+      <c r="D116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I116" s="17" t="s">
+      <c r="I116" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J116" s="17" t="s">
+      <c r="J116" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K116" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L116" s="17" t="n">
+      <c r="K116" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L116" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="M116" s="16" t="n">
+      <c r="M116" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N116" s="17" t="n">
+      <c r="N116" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="17" t="s">
+      <c r="A117" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B117" s="17" t="s">
+      <c r="B117" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C117" s="17" t="s">
+      <c r="C117" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D117" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H117" s="17" t="s">
+      <c r="D117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I117" s="17" t="s">
+      <c r="I117" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J117" s="17" t="s">
+      <c r="J117" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K117" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L117" s="17" t="n">
+      <c r="K117" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="M117" s="16" t="n">
+      <c r="M117" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N117" s="17" t="n">
+      <c r="N117" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="17" t="s">
+      <c r="A118" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="17" t="s">
+      <c r="B118" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C118" s="17" t="s">
+      <c r="C118" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D118" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H118" s="17" t="s">
+      <c r="D118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I118" s="17" t="s">
+      <c r="I118" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J118" s="17" t="s">
+      <c r="J118" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K118" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L118" s="17" t="n">
+      <c r="K118" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="M118" s="16" t="n">
+      <c r="M118" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N118" s="17" t="n">
+      <c r="N118" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="17" t="s">
+      <c r="A119" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B119" s="17" t="s">
+      <c r="B119" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C119" s="17" t="s">
+      <c r="C119" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D119" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H119" s="17" t="s">
+      <c r="D119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I119" s="17" t="s">
+      <c r="I119" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J119" s="17" t="s">
+      <c r="J119" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K119" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L119" s="17" t="n">
+      <c r="K119" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L119" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="M119" s="16" t="n">
+      <c r="M119" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N119" s="17" t="n">
+      <c r="N119" s="14" t="n">
         <v>2</v>
       </c>
       <c r="O119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="17" t="s">
+      <c r="A120" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B120" s="17" t="s">
+      <c r="B120" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C120" s="17" t="s">
+      <c r="C120" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D120" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" s="17" t="s">
+      <c r="D120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I120" s="17" t="s">
+      <c r="I120" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J120" s="17" t="s">
+      <c r="J120" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K120" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L120" s="17" t="n">
+      <c r="K120" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L120" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="M120" s="16" t="n">
+      <c r="M120" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N120" s="17" t="n">
+      <c r="N120" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="17" t="s">
+      <c r="A121" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B121" s="17" t="s">
+      <c r="B121" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D121" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" s="17" t="s">
+      <c r="D121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I121" s="17" t="s">
+      <c r="I121" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J121" s="17" t="s">
+      <c r="J121" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K121" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L121" s="17" t="n">
+      <c r="K121" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="M121" s="16" t="n">
+      <c r="M121" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N121" s="17" t="n">
+      <c r="N121" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="17" t="s">
+      <c r="A122" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B122" s="17" t="s">
+      <c r="B122" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D122" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H122" s="17" t="s">
+      <c r="D122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I122" s="17" t="s">
+      <c r="I122" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J122" s="17" t="s">
+      <c r="J122" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K122" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L122" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="M122" s="16" t="n">
+      <c r="K122" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L122" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M122" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N122" s="17" t="n">
+      <c r="N122" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="17" t="s">
+      <c r="A123" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="17" t="s">
+      <c r="B123" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D123" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="17" t="s">
+      <c r="D123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I123" s="17" t="s">
+      <c r="I123" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J123" s="17" t="s">
+      <c r="J123" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K123" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L123" s="17" t="n">
+      <c r="K123" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L123" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="M123" s="16" t="n">
+      <c r="M123" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N123" s="17" t="n">
+      <c r="N123" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="17" t="s">
+      <c r="A124" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B124" s="17" t="s">
+      <c r="B124" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="17" t="s">
+      <c r="C124" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D124" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="17" t="s">
+      <c r="D124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I124" s="17" t="s">
+      <c r="I124" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J124" s="17" t="s">
+      <c r="J124" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K124" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="17" t="n">
+      <c r="K124" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L124" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="M124" s="16" t="n">
+      <c r="M124" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N124" s="17" t="n">
+      <c r="N124" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="17" t="s">
+      <c r="A125" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B125" s="17" t="s">
+      <c r="B125" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C125" s="17" t="s">
+      <c r="C125" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D125" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H125" s="17" t="s">
+      <c r="D125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I125" s="17" t="s">
+      <c r="I125" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J125" s="17" t="s">
+      <c r="J125" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K125" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L125" s="17" t="n">
+      <c r="K125" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="14" t="n">
         <v>115</v>
       </c>
-      <c r="M125" s="16" t="n">
+      <c r="M125" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N125" s="17" t="n">
+      <c r="N125" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="17" t="s">
+      <c r="A126" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B126" s="17" t="s">
+      <c r="B126" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C126" s="17" t="s">
+      <c r="C126" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D126" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="17" t="s">
+      <c r="D126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I126" s="17" t="s">
+      <c r="I126" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J126" s="17" t="s">
+      <c r="J126" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K126" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" s="17" t="n">
+      <c r="K126" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L126" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="M126" s="16" t="n">
+      <c r="M126" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N126" s="17" t="n">
+      <c r="N126" s="14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9213,8 +9193,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9225,7 +9205,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -10706,8 +10686,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10718,7 +10698,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -12528,8 +12508,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -784,7 +784,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -2689,8 +2689,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2701,7 +2701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U127"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.77"/>
@@ -2812,8 +2812,8 @@
       <c r="K2" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>85</v>
+      <c r="L2" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>5</v>
@@ -2874,8 +2874,8 @@
       <c r="K3" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>40</v>
+      <c r="L3" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M3" s="8" t="n">
         <v>5</v>
@@ -2936,8 +2936,8 @@
       <c r="K4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>110</v>
+      <c r="L4" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>5</v>
@@ -2998,8 +2998,8 @@
       <c r="K5" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>65</v>
+      <c r="L5" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>5</v>
@@ -3060,8 +3060,8 @@
       <c r="K6" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>100</v>
+      <c r="L6" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>5</v>
@@ -3122,8 +3122,8 @@
       <c r="K7" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="2" t="n">
-        <v>90</v>
+      <c r="L7" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M7" s="8" t="n">
         <v>5</v>
@@ -3184,8 +3184,8 @@
       <c r="K8" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>20</v>
+      <c r="L8" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>5</v>
@@ -3246,8 +3246,8 @@
       <c r="K9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>55</v>
+      <c r="L9" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M9" s="8" t="n">
         <v>5</v>
@@ -3308,8 +3308,8 @@
       <c r="K10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="2" t="n">
-        <v>60</v>
+      <c r="L10" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>5</v>
@@ -3370,8 +3370,8 @@
       <c r="K11" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="2" t="n">
-        <v>45</v>
+      <c r="L11" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>5</v>
@@ -3432,8 +3432,8 @@
       <c r="K12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>105</v>
+      <c r="L12" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>5</v>
@@ -3494,8 +3494,8 @@
       <c r="K13" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>15</v>
+      <c r="L13" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>5</v>
@@ -3556,8 +3556,8 @@
       <c r="K14" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>95</v>
+      <c r="L14" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>5</v>
@@ -3618,8 +3618,8 @@
       <c r="K15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="2" t="n">
-        <v>35</v>
+      <c r="L15" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>5</v>
@@ -3680,8 +3680,8 @@
       <c r="K16" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>50</v>
+      <c r="L16" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>5</v>
@@ -3742,8 +3742,8 @@
       <c r="K17" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>30</v>
+      <c r="L17" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M17" s="8" t="n">
         <v>5</v>
@@ -3804,8 +3804,8 @@
       <c r="K18" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L18" s="2" t="n">
-        <v>80</v>
+      <c r="L18" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>5</v>
@@ -3866,8 +3866,8 @@
       <c r="K19" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L19" s="2" t="n">
-        <v>70</v>
+      <c r="L19" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>5</v>
@@ -3928,8 +3928,8 @@
       <c r="K20" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="2" t="n">
-        <v>75</v>
+      <c r="L20" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>5</v>
@@ -3990,8 +3990,8 @@
       <c r="K21" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>25</v>
+      <c r="L21" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>5</v>
@@ -4052,8 +4052,8 @@
       <c r="K22" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>67</v>
+      <c r="L22" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>5</v>
@@ -4114,8 +4114,8 @@
       <c r="K23" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="2" t="n">
-        <v>47</v>
+      <c r="L23" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>5</v>
@@ -4176,8 +4176,8 @@
       <c r="K24" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>72</v>
+      <c r="L24" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>5</v>
@@ -4238,8 +4238,8 @@
       <c r="K25" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>97</v>
+      <c r="L25" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>5</v>
@@ -4300,8 +4300,8 @@
       <c r="K26" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L26" s="2" t="n">
-        <v>77</v>
+      <c r="L26" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>5</v>
@@ -4362,8 +4362,8 @@
       <c r="K27" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L27" s="2" t="n">
-        <v>87</v>
+      <c r="L27" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M27" s="8" t="n">
         <v>5</v>
@@ -4424,8 +4424,8 @@
       <c r="K28" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="2" t="n">
-        <v>32</v>
+      <c r="L28" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>5</v>
@@ -4486,8 +4486,8 @@
       <c r="K29" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="2" t="n">
-        <v>102</v>
+      <c r="L29" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>5</v>
@@ -4548,8 +4548,8 @@
       <c r="K30" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>42</v>
+      <c r="L30" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>5</v>
@@ -4610,8 +4610,8 @@
       <c r="K31" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L31" s="2" t="n">
-        <v>57</v>
+      <c r="L31" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M31" s="8" t="n">
         <v>5</v>
@@ -4672,8 +4672,8 @@
       <c r="K32" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="2" t="n">
-        <v>27</v>
+      <c r="L32" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>5</v>
@@ -4734,8 +4734,8 @@
       <c r="K33" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>17</v>
+      <c r="L33" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>5</v>
@@ -4796,8 +4796,8 @@
       <c r="K34" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L34" s="2" t="n">
-        <v>92</v>
+      <c r="L34" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>5</v>
@@ -4858,8 +4858,8 @@
       <c r="K35" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L35" s="2" t="n">
-        <v>22</v>
+      <c r="L35" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M35" s="8" t="n">
         <v>5</v>
@@ -4920,8 +4920,8 @@
       <c r="K36" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L36" s="2" t="n">
-        <v>62</v>
+      <c r="L36" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M36" s="8" t="n">
         <v>5</v>
@@ -4982,8 +4982,8 @@
       <c r="K37" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L37" s="2" t="n">
-        <v>107</v>
+      <c r="L37" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M37" s="8" t="n">
         <v>5</v>
@@ -5044,8 +5044,8 @@
       <c r="K38" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L38" s="2" t="n">
-        <v>12</v>
+      <c r="L38" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>5</v>
@@ -5106,8 +5106,8 @@
       <c r="K39" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L39" s="2" t="n">
-        <v>82</v>
+      <c r="L39" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>5</v>
@@ -5168,8 +5168,8 @@
       <c r="K40" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="2" t="n">
-        <v>37</v>
+      <c r="L40" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M40" s="8" t="n">
         <v>5</v>
@@ -5230,8 +5230,8 @@
       <c r="K41" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L41" s="2" t="n">
-        <v>52</v>
+      <c r="L41" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M41" s="8" t="n">
         <v>5</v>
@@ -5643,7 +5643,7 @@
       <c r="K49" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="L49" s="3" t="n">
         <v>-100000</v>
       </c>
       <c r="M49" s="4" t="n">
@@ -6025,7 +6025,7 @@
       <c r="K57" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="L57" s="3" t="n">
         <v>-100000</v>
       </c>
       <c r="M57" s="4" t="n">
@@ -6831,7 +6831,7 @@
       <c r="K74" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L74" s="4" t="n">
+      <c r="L74" s="3" t="n">
         <v>-100000</v>
       </c>
       <c r="M74" s="4" t="n">
@@ -7073,8 +7073,8 @@
       <c r="K79" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L79" s="13" t="n">
-        <v>5</v>
+      <c r="L79" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M79" s="13" t="n">
         <v>5</v>
@@ -7118,8 +7118,8 @@
       <c r="K80" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L80" s="13" t="n">
-        <v>10</v>
+      <c r="L80" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M80" s="13" t="n">
         <v>5</v>
@@ -7163,8 +7163,8 @@
       <c r="K81" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L81" s="13" t="n">
-        <v>15</v>
+      <c r="L81" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>5</v>
@@ -7208,8 +7208,8 @@
       <c r="K82" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L82" s="13" t="n">
-        <v>20</v>
+      <c r="L82" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>5</v>
@@ -7253,8 +7253,8 @@
       <c r="K83" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L83" s="13" t="n">
-        <v>25</v>
+      <c r="L83" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>5</v>
@@ -7298,8 +7298,8 @@
       <c r="K84" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L84" s="13" t="n">
-        <v>30</v>
+      <c r="L84" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>5</v>
@@ -7343,8 +7343,8 @@
       <c r="K85" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L85" s="13" t="n">
-        <v>35</v>
+      <c r="L85" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M85" s="13" t="n">
         <v>5</v>
@@ -7388,8 +7388,8 @@
       <c r="K86" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L86" s="13" t="n">
-        <v>40</v>
+      <c r="L86" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M86" s="13" t="n">
         <v>5</v>
@@ -7433,8 +7433,8 @@
       <c r="K87" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L87" s="13" t="n">
-        <v>45</v>
+      <c r="L87" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M87" s="13" t="n">
         <v>5</v>
@@ -7478,8 +7478,8 @@
       <c r="K88" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L88" s="13" t="n">
-        <v>50</v>
+      <c r="L88" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M88" s="13" t="n">
         <v>5</v>
@@ -7523,8 +7523,8 @@
       <c r="K89" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L89" s="13" t="n">
-        <v>55</v>
+      <c r="L89" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M89" s="13" t="n">
         <v>5</v>
@@ -7568,8 +7568,8 @@
       <c r="K90" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L90" s="13" t="n">
-        <v>60</v>
+      <c r="L90" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M90" s="13" t="n">
         <v>5</v>
@@ -7613,8 +7613,8 @@
       <c r="K91" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L91" s="13" t="n">
-        <v>65</v>
+      <c r="L91" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M91" s="13" t="n">
         <v>5</v>
@@ -7658,8 +7658,8 @@
       <c r="K92" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L92" s="13" t="n">
-        <v>70</v>
+      <c r="L92" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M92" s="13" t="n">
         <v>5</v>
@@ -7703,8 +7703,8 @@
       <c r="K93" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L93" s="13" t="n">
-        <v>75</v>
+      <c r="L93" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M93" s="13" t="n">
         <v>5</v>
@@ -7748,8 +7748,8 @@
       <c r="K94" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L94" s="13" t="n">
-        <v>80</v>
+      <c r="L94" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M94" s="13" t="n">
         <v>5</v>
@@ -7793,8 +7793,8 @@
       <c r="K95" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L95" s="13" t="n">
-        <v>85</v>
+      <c r="L95" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M95" s="13" t="n">
         <v>5</v>
@@ -7838,8 +7838,8 @@
       <c r="K96" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L96" s="13" t="n">
-        <v>90</v>
+      <c r="L96" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M96" s="13" t="n">
         <v>5</v>
@@ -7883,8 +7883,8 @@
       <c r="K97" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L97" s="13" t="n">
-        <v>95</v>
+      <c r="L97" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M97" s="13" t="n">
         <v>5</v>
@@ -7928,8 +7928,8 @@
       <c r="K98" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L98" s="13" t="n">
-        <v>100</v>
+      <c r="L98" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M98" s="13" t="n">
         <v>5</v>
@@ -7973,8 +7973,8 @@
       <c r="K99" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L99" s="13" t="n">
-        <v>105</v>
+      <c r="L99" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M99" s="13" t="n">
         <v>5</v>
@@ -8018,8 +8018,8 @@
       <c r="K100" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L100" s="13" t="n">
-        <v>110</v>
+      <c r="L100" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M100" s="13" t="n">
         <v>5</v>
@@ -8063,8 +8063,8 @@
       <c r="K101" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L101" s="13" t="n">
-        <v>115</v>
+      <c r="L101" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M101" s="13" t="n">
         <v>5</v>
@@ -8108,8 +8108,8 @@
       <c r="K102" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L102" s="13" t="n">
-        <v>120</v>
+      <c r="L102" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M102" s="13" t="n">
         <v>5</v>
@@ -8153,8 +8153,8 @@
       <c r="K103" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L103" s="14" t="n">
-        <v>5</v>
+      <c r="L103" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M103" s="13" t="n">
         <v>5</v>
@@ -8198,8 +8198,8 @@
       <c r="K104" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L104" s="14" t="n">
-        <v>10</v>
+      <c r="L104" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M104" s="13" t="n">
         <v>5</v>
@@ -8242,8 +8242,8 @@
       <c r="K105" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L105" s="14" t="n">
-        <v>15</v>
+      <c r="L105" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M105" s="13" t="n">
         <v>5</v>
@@ -8286,8 +8286,8 @@
       <c r="K106" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L106" s="14" t="n">
-        <v>20</v>
+      <c r="L106" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M106" s="13" t="n">
         <v>5</v>
@@ -8330,8 +8330,8 @@
       <c r="K107" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L107" s="14" t="n">
-        <v>25</v>
+      <c r="L107" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>5</v>
@@ -8374,8 +8374,8 @@
       <c r="K108" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L108" s="14" t="n">
-        <v>30</v>
+      <c r="L108" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>5</v>
@@ -8418,8 +8418,8 @@
       <c r="K109" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L109" s="14" t="n">
-        <v>35</v>
+      <c r="L109" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M109" s="13" t="n">
         <v>5</v>
@@ -8462,8 +8462,8 @@
       <c r="K110" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L110" s="14" t="n">
-        <v>40</v>
+      <c r="L110" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>5</v>
@@ -8506,8 +8506,8 @@
       <c r="K111" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L111" s="14" t="n">
-        <v>45</v>
+      <c r="L111" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>5</v>
@@ -8550,8 +8550,8 @@
       <c r="K112" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L112" s="14" t="n">
-        <v>50</v>
+      <c r="L112" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>5</v>
@@ -8594,8 +8594,8 @@
       <c r="K113" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L113" s="14" t="n">
-        <v>55</v>
+      <c r="L113" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>5</v>
@@ -8638,8 +8638,8 @@
       <c r="K114" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L114" s="14" t="n">
-        <v>60</v>
+      <c r="L114" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>5</v>
@@ -8682,8 +8682,8 @@
       <c r="K115" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L115" s="14" t="n">
-        <v>65</v>
+      <c r="L115" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M115" s="13" t="n">
         <v>5</v>
@@ -8726,8 +8726,8 @@
       <c r="K116" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L116" s="14" t="n">
-        <v>70</v>
+      <c r="L116" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>5</v>
@@ -8770,8 +8770,8 @@
       <c r="K117" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L117" s="14" t="n">
-        <v>75</v>
+      <c r="L117" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>5</v>
@@ -8814,8 +8814,8 @@
       <c r="K118" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L118" s="14" t="n">
-        <v>80</v>
+      <c r="L118" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>5</v>
@@ -8858,8 +8858,8 @@
       <c r="K119" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L119" s="14" t="n">
-        <v>85</v>
+      <c r="L119" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>5</v>
@@ -8903,8 +8903,8 @@
       <c r="K120" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L120" s="14" t="n">
-        <v>90</v>
+      <c r="L120" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M120" s="13" t="n">
         <v>5</v>
@@ -8947,8 +8947,8 @@
       <c r="K121" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L121" s="14" t="n">
-        <v>95</v>
+      <c r="L121" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M121" s="13" t="n">
         <v>5</v>
@@ -8991,8 +8991,8 @@
       <c r="K122" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L122" s="14" t="n">
-        <v>100</v>
+      <c r="L122" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>5</v>
@@ -9035,8 +9035,8 @@
       <c r="K123" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L123" s="14" t="n">
-        <v>105</v>
+      <c r="L123" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>5</v>
@@ -9079,8 +9079,8 @@
       <c r="K124" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L124" s="14" t="n">
-        <v>110</v>
+      <c r="L124" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>5</v>
@@ -9123,8 +9123,8 @@
       <c r="K125" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L125" s="14" t="n">
-        <v>115</v>
+      <c r="L125" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>5</v>
@@ -9167,8 +9167,8 @@
       <c r="K126" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L126" s="14" t="n">
-        <v>120</v>
+      <c r="L126" s="3" t="n">
+        <v>-100000</v>
       </c>
       <c r="M126" s="13" t="n">
         <v>5</v>
@@ -9193,8 +9193,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9205,7 +9205,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -10686,8 +10686,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10698,7 +10698,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -12508,8 +12508,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -2812,8 +2812,8 @@
       <c r="K2" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L2" s="3" t="n">
-        <v>-100000</v>
+      <c r="L2" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>5</v>
@@ -2874,8 +2874,8 @@
       <c r="K3" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>-100000</v>
+      <c r="L3" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="M3" s="8" t="n">
         <v>5</v>
@@ -2936,8 +2936,8 @@
       <c r="K4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>-100000</v>
+      <c r="L4" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>5</v>
@@ -2998,8 +2998,8 @@
       <c r="K5" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>-100000</v>
+      <c r="L5" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>5</v>
@@ -3060,8 +3060,8 @@
       <c r="K6" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>-100000</v>
+      <c r="L6" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>5</v>
@@ -3122,8 +3122,8 @@
       <c r="K7" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>-100000</v>
+      <c r="L7" s="2" t="n">
+        <v>90</v>
       </c>
       <c r="M7" s="8" t="n">
         <v>5</v>
@@ -3184,8 +3184,8 @@
       <c r="K8" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>-100000</v>
+      <c r="L8" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>5</v>
@@ -3246,8 +3246,8 @@
       <c r="K9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>-100000</v>
+      <c r="L9" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="M9" s="8" t="n">
         <v>5</v>
@@ -3308,8 +3308,8 @@
       <c r="K10" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="3" t="n">
-        <v>-100000</v>
+      <c r="L10" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>5</v>
@@ -3370,8 +3370,8 @@
       <c r="K11" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>-100000</v>
+      <c r="L11" s="2" t="n">
+        <v>45</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>5</v>
@@ -3432,8 +3432,8 @@
       <c r="K12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>-100000</v>
+      <c r="L12" s="2" t="n">
+        <v>105</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>5</v>
@@ -3494,8 +3494,8 @@
       <c r="K13" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>-100000</v>
+      <c r="L13" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>5</v>
@@ -3556,8 +3556,8 @@
       <c r="K14" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>-100000</v>
+      <c r="L14" s="2" t="n">
+        <v>95</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>5</v>
@@ -3618,8 +3618,8 @@
       <c r="K15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>-100000</v>
+      <c r="L15" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>5</v>
@@ -3680,8 +3680,8 @@
       <c r="K16" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="3" t="n">
-        <v>-100000</v>
+      <c r="L16" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>5</v>
@@ -3742,8 +3742,8 @@
       <c r="K17" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="3" t="n">
-        <v>-100000</v>
+      <c r="L17" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="M17" s="8" t="n">
         <v>5</v>
@@ -3804,8 +3804,8 @@
       <c r="K18" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>-100000</v>
+      <c r="L18" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>5</v>
@@ -3866,8 +3866,8 @@
       <c r="K19" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>-100000</v>
+      <c r="L19" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>5</v>
@@ -3928,8 +3928,8 @@
       <c r="K20" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>-100000</v>
+      <c r="L20" s="2" t="n">
+        <v>75</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>5</v>
@@ -3990,8 +3990,8 @@
       <c r="K21" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>-100000</v>
+      <c r="L21" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>5</v>
@@ -4052,8 +4052,8 @@
       <c r="K22" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>-100000</v>
+      <c r="L22" s="2" t="n">
+        <v>67</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>5</v>
@@ -4114,8 +4114,8 @@
       <c r="K23" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="3" t="n">
-        <v>-100000</v>
+      <c r="L23" s="2" t="n">
+        <v>47</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>5</v>
@@ -4176,8 +4176,8 @@
       <c r="K24" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>-100000</v>
+      <c r="L24" s="2" t="n">
+        <v>72</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>5</v>
@@ -4238,8 +4238,8 @@
       <c r="K25" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>-100000</v>
+      <c r="L25" s="2" t="n">
+        <v>97</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>5</v>
@@ -4300,8 +4300,8 @@
       <c r="K26" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>-100000</v>
+      <c r="L26" s="2" t="n">
+        <v>77</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>5</v>
@@ -4362,8 +4362,8 @@
       <c r="K27" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L27" s="3" t="n">
-        <v>-100000</v>
+      <c r="L27" s="2" t="n">
+        <v>87</v>
       </c>
       <c r="M27" s="8" t="n">
         <v>5</v>
@@ -4424,8 +4424,8 @@
       <c r="K28" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="3" t="n">
-        <v>-100000</v>
+      <c r="L28" s="2" t="n">
+        <v>32</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>5</v>
@@ -4486,8 +4486,8 @@
       <c r="K29" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>-100000</v>
+      <c r="L29" s="2" t="n">
+        <v>102</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>5</v>
@@ -4548,8 +4548,8 @@
       <c r="K30" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L30" s="3" t="n">
-        <v>-100000</v>
+      <c r="L30" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>5</v>
@@ -4610,8 +4610,8 @@
       <c r="K31" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>-100000</v>
+      <c r="L31" s="2" t="n">
+        <v>57</v>
       </c>
       <c r="M31" s="8" t="n">
         <v>5</v>
@@ -4672,8 +4672,8 @@
       <c r="K32" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>-100000</v>
+      <c r="L32" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>5</v>
@@ -4734,8 +4734,8 @@
       <c r="K33" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>-100000</v>
+      <c r="L33" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>5</v>
@@ -4796,8 +4796,8 @@
       <c r="K34" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L34" s="3" t="n">
-        <v>-100000</v>
+      <c r="L34" s="2" t="n">
+        <v>92</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>5</v>
@@ -4858,8 +4858,8 @@
       <c r="K35" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L35" s="3" t="n">
-        <v>-100000</v>
+      <c r="L35" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="M35" s="8" t="n">
         <v>5</v>
@@ -4920,8 +4920,8 @@
       <c r="K36" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>-100000</v>
+      <c r="L36" s="2" t="n">
+        <v>62</v>
       </c>
       <c r="M36" s="8" t="n">
         <v>5</v>
@@ -4982,8 +4982,8 @@
       <c r="K37" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>-100000</v>
+      <c r="L37" s="2" t="n">
+        <v>107</v>
       </c>
       <c r="M37" s="8" t="n">
         <v>5</v>
@@ -5044,8 +5044,8 @@
       <c r="K38" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L38" s="3" t="n">
-        <v>-100000</v>
+      <c r="L38" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>5</v>
@@ -5106,8 +5106,8 @@
       <c r="K39" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>-100000</v>
+      <c r="L39" s="2" t="n">
+        <v>82</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>5</v>
@@ -5168,8 +5168,8 @@
       <c r="K40" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>-100000</v>
+      <c r="L40" s="2" t="n">
+        <v>37</v>
       </c>
       <c r="M40" s="8" t="n">
         <v>5</v>
@@ -5230,8 +5230,8 @@
       <c r="K41" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L41" s="3" t="n">
-        <v>-100000</v>
+      <c r="L41" s="2" t="n">
+        <v>52</v>
       </c>
       <c r="M41" s="8" t="n">
         <v>5</v>
@@ -5643,7 +5643,7 @@
       <c r="K49" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L49" s="3" t="n">
+      <c r="L49" s="4" t="n">
         <v>-100000</v>
       </c>
       <c r="M49" s="4" t="n">
@@ -6025,7 +6025,7 @@
       <c r="K57" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L57" s="3" t="n">
+      <c r="L57" s="4" t="n">
         <v>-100000</v>
       </c>
       <c r="M57" s="4" t="n">
@@ -6831,7 +6831,7 @@
       <c r="K74" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L74" s="3" t="n">
+      <c r="L74" s="4" t="n">
         <v>-100000</v>
       </c>
       <c r="M74" s="4" t="n">
@@ -7073,8 +7073,8 @@
       <c r="K79" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L79" s="3" t="n">
-        <v>-100000</v>
+      <c r="L79" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="M79" s="13" t="n">
         <v>5</v>
@@ -7118,8 +7118,8 @@
       <c r="K80" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L80" s="3" t="n">
-        <v>-100000</v>
+      <c r="L80" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="M80" s="13" t="n">
         <v>5</v>
@@ -7163,8 +7163,8 @@
       <c r="K81" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L81" s="3" t="n">
-        <v>-100000</v>
+      <c r="L81" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>5</v>
@@ -7208,8 +7208,8 @@
       <c r="K82" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L82" s="3" t="n">
-        <v>-100000</v>
+      <c r="L82" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>5</v>
@@ -7253,8 +7253,8 @@
       <c r="K83" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L83" s="3" t="n">
-        <v>-100000</v>
+      <c r="L83" s="13" t="n">
+        <v>25</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>5</v>
@@ -7298,8 +7298,8 @@
       <c r="K84" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L84" s="3" t="n">
-        <v>-100000</v>
+      <c r="L84" s="13" t="n">
+        <v>30</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>5</v>
@@ -7343,8 +7343,8 @@
       <c r="K85" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L85" s="3" t="n">
-        <v>-100000</v>
+      <c r="L85" s="13" t="n">
+        <v>35</v>
       </c>
       <c r="M85" s="13" t="n">
         <v>5</v>
@@ -7388,8 +7388,8 @@
       <c r="K86" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L86" s="3" t="n">
-        <v>-100000</v>
+      <c r="L86" s="13" t="n">
+        <v>40</v>
       </c>
       <c r="M86" s="13" t="n">
         <v>5</v>
@@ -7433,8 +7433,8 @@
       <c r="K87" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L87" s="3" t="n">
-        <v>-100000</v>
+      <c r="L87" s="13" t="n">
+        <v>45</v>
       </c>
       <c r="M87" s="13" t="n">
         <v>5</v>
@@ -7478,8 +7478,8 @@
       <c r="K88" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L88" s="3" t="n">
-        <v>-100000</v>
+      <c r="L88" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="M88" s="13" t="n">
         <v>5</v>
@@ -7523,8 +7523,8 @@
       <c r="K89" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L89" s="3" t="n">
-        <v>-100000</v>
+      <c r="L89" s="13" t="n">
+        <v>55</v>
       </c>
       <c r="M89" s="13" t="n">
         <v>5</v>
@@ -7568,8 +7568,8 @@
       <c r="K90" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L90" s="3" t="n">
-        <v>-100000</v>
+      <c r="L90" s="13" t="n">
+        <v>60</v>
       </c>
       <c r="M90" s="13" t="n">
         <v>5</v>
@@ -7613,8 +7613,8 @@
       <c r="K91" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L91" s="3" t="n">
-        <v>-100000</v>
+      <c r="L91" s="13" t="n">
+        <v>65</v>
       </c>
       <c r="M91" s="13" t="n">
         <v>5</v>
@@ -7658,8 +7658,8 @@
       <c r="K92" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L92" s="3" t="n">
-        <v>-100000</v>
+      <c r="L92" s="13" t="n">
+        <v>70</v>
       </c>
       <c r="M92" s="13" t="n">
         <v>5</v>
@@ -7703,8 +7703,8 @@
       <c r="K93" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L93" s="3" t="n">
-        <v>-100000</v>
+      <c r="L93" s="13" t="n">
+        <v>75</v>
       </c>
       <c r="M93" s="13" t="n">
         <v>5</v>
@@ -7748,8 +7748,8 @@
       <c r="K94" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L94" s="3" t="n">
-        <v>-100000</v>
+      <c r="L94" s="13" t="n">
+        <v>80</v>
       </c>
       <c r="M94" s="13" t="n">
         <v>5</v>
@@ -7793,8 +7793,8 @@
       <c r="K95" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L95" s="3" t="n">
-        <v>-100000</v>
+      <c r="L95" s="13" t="n">
+        <v>85</v>
       </c>
       <c r="M95" s="13" t="n">
         <v>5</v>
@@ -7838,8 +7838,8 @@
       <c r="K96" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L96" s="3" t="n">
-        <v>-100000</v>
+      <c r="L96" s="13" t="n">
+        <v>90</v>
       </c>
       <c r="M96" s="13" t="n">
         <v>5</v>
@@ -7883,8 +7883,8 @@
       <c r="K97" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L97" s="3" t="n">
-        <v>-100000</v>
+      <c r="L97" s="13" t="n">
+        <v>95</v>
       </c>
       <c r="M97" s="13" t="n">
         <v>5</v>
@@ -7928,8 +7928,8 @@
       <c r="K98" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L98" s="3" t="n">
-        <v>-100000</v>
+      <c r="L98" s="13" t="n">
+        <v>100</v>
       </c>
       <c r="M98" s="13" t="n">
         <v>5</v>
@@ -7973,8 +7973,8 @@
       <c r="K99" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L99" s="3" t="n">
-        <v>-100000</v>
+      <c r="L99" s="13" t="n">
+        <v>105</v>
       </c>
       <c r="M99" s="13" t="n">
         <v>5</v>
@@ -8018,8 +8018,8 @@
       <c r="K100" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L100" s="3" t="n">
-        <v>-100000</v>
+      <c r="L100" s="13" t="n">
+        <v>110</v>
       </c>
       <c r="M100" s="13" t="n">
         <v>5</v>
@@ -8063,8 +8063,8 @@
       <c r="K101" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L101" s="3" t="n">
-        <v>-100000</v>
+      <c r="L101" s="13" t="n">
+        <v>115</v>
       </c>
       <c r="M101" s="13" t="n">
         <v>5</v>
@@ -8108,8 +8108,8 @@
       <c r="K102" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L102" s="3" t="n">
-        <v>-100000</v>
+      <c r="L102" s="13" t="n">
+        <v>120</v>
       </c>
       <c r="M102" s="13" t="n">
         <v>5</v>
@@ -8153,8 +8153,8 @@
       <c r="K103" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L103" s="3" t="n">
-        <v>-100000</v>
+      <c r="L103" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="M103" s="13" t="n">
         <v>5</v>
@@ -8198,8 +8198,8 @@
       <c r="K104" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L104" s="3" t="n">
-        <v>-100000</v>
+      <c r="L104" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="M104" s="13" t="n">
         <v>5</v>
@@ -8242,8 +8242,8 @@
       <c r="K105" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L105" s="3" t="n">
-        <v>-100000</v>
+      <c r="L105" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="M105" s="13" t="n">
         <v>5</v>
@@ -8286,8 +8286,8 @@
       <c r="K106" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L106" s="3" t="n">
-        <v>-100000</v>
+      <c r="L106" s="14" t="n">
+        <v>20</v>
       </c>
       <c r="M106" s="13" t="n">
         <v>5</v>
@@ -8330,8 +8330,8 @@
       <c r="K107" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L107" s="3" t="n">
-        <v>-100000</v>
+      <c r="L107" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>5</v>
@@ -8374,8 +8374,8 @@
       <c r="K108" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L108" s="3" t="n">
-        <v>-100000</v>
+      <c r="L108" s="14" t="n">
+        <v>30</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>5</v>
@@ -8418,8 +8418,8 @@
       <c r="K109" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L109" s="3" t="n">
-        <v>-100000</v>
+      <c r="L109" s="14" t="n">
+        <v>35</v>
       </c>
       <c r="M109" s="13" t="n">
         <v>5</v>
@@ -8462,8 +8462,8 @@
       <c r="K110" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L110" s="3" t="n">
-        <v>-100000</v>
+      <c r="L110" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>5</v>
@@ -8506,8 +8506,8 @@
       <c r="K111" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L111" s="3" t="n">
-        <v>-100000</v>
+      <c r="L111" s="14" t="n">
+        <v>45</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>5</v>
@@ -8550,8 +8550,8 @@
       <c r="K112" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L112" s="3" t="n">
-        <v>-100000</v>
+      <c r="L112" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>5</v>
@@ -8594,8 +8594,8 @@
       <c r="K113" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L113" s="3" t="n">
-        <v>-100000</v>
+      <c r="L113" s="14" t="n">
+        <v>55</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>5</v>
@@ -8638,8 +8638,8 @@
       <c r="K114" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L114" s="3" t="n">
-        <v>-100000</v>
+      <c r="L114" s="14" t="n">
+        <v>60</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>5</v>
@@ -8682,8 +8682,8 @@
       <c r="K115" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L115" s="3" t="n">
-        <v>-100000</v>
+      <c r="L115" s="14" t="n">
+        <v>65</v>
       </c>
       <c r="M115" s="13" t="n">
         <v>5</v>
@@ -8726,8 +8726,8 @@
       <c r="K116" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L116" s="3" t="n">
-        <v>-100000</v>
+      <c r="L116" s="14" t="n">
+        <v>70</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>5</v>
@@ -8770,8 +8770,8 @@
       <c r="K117" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L117" s="3" t="n">
-        <v>-100000</v>
+      <c r="L117" s="14" t="n">
+        <v>75</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>5</v>
@@ -8814,8 +8814,8 @@
       <c r="K118" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L118" s="3" t="n">
-        <v>-100000</v>
+      <c r="L118" s="14" t="n">
+        <v>80</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>5</v>
@@ -8858,8 +8858,8 @@
       <c r="K119" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L119" s="3" t="n">
-        <v>-100000</v>
+      <c r="L119" s="14" t="n">
+        <v>85</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>5</v>
@@ -8903,8 +8903,8 @@
       <c r="K120" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L120" s="3" t="n">
-        <v>-100000</v>
+      <c r="L120" s="14" t="n">
+        <v>90</v>
       </c>
       <c r="M120" s="13" t="n">
         <v>5</v>
@@ -8947,8 +8947,8 @@
       <c r="K121" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L121" s="3" t="n">
-        <v>-100000</v>
+      <c r="L121" s="14" t="n">
+        <v>95</v>
       </c>
       <c r="M121" s="13" t="n">
         <v>5</v>
@@ -8991,8 +8991,8 @@
       <c r="K122" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L122" s="3" t="n">
-        <v>-100000</v>
+      <c r="L122" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>5</v>
@@ -9035,8 +9035,8 @@
       <c r="K123" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L123" s="3" t="n">
-        <v>-100000</v>
+      <c r="L123" s="14" t="n">
+        <v>105</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>5</v>
@@ -9079,8 +9079,8 @@
       <c r="K124" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L124" s="3" t="n">
-        <v>-100000</v>
+      <c r="L124" s="14" t="n">
+        <v>110</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>5</v>
@@ -9123,8 +9123,8 @@
       <c r="K125" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L125" s="3" t="n">
-        <v>-100000</v>
+      <c r="L125" s="14" t="n">
+        <v>115</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>5</v>
@@ -9167,8 +9167,8 @@
       <c r="K126" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="L126" s="3" t="n">
-        <v>-100000</v>
+      <c r="L126" s="14" t="n">
+        <v>120</v>
       </c>
       <c r="M126" s="13" t="n">
         <v>5</v>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="137">
   <si>
     <t xml:space="preserve">Hippocampome_Neurons_Names</t>
   </si>
@@ -2700,7 +2700,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U127"/>
+  <dimension ref="A1:U129"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
@@ -2778,7 +2778,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>8</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>85</v>
+        <v>-10000</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>5</v>
@@ -2833,6 +2833,7 @@
       <c r="R2" s="2" t="n">
         <v>80</v>
       </c>
+      <c r="S2" s="9"/>
       <c r="T2" s="9" t="n">
         <v>0</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>1</v>
@@ -2860,7 +2861,7 @@
         <v>160000</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>20</v>
@@ -2875,7 +2876,7 @@
         <v>8</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="M3" s="8" t="n">
         <v>5</v>
@@ -2899,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="U3" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2937,7 +2938,7 @@
         <v>8</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>5</v>
@@ -2961,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2975,7 +2976,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>1</v>
@@ -2984,7 +2985,7 @@
         <v>160000</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
@@ -2999,7 +3000,7 @@
         <v>8</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>5</v>
@@ -3023,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3037,7 +3038,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>1</v>
@@ -3046,7 +3047,7 @@
         <v>160000</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>20</v>
@@ -3061,7 +3062,7 @@
         <v>8</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>5</v>
@@ -3085,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="9" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3099,7 +3100,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1</v>
@@ -3108,7 +3109,7 @@
         <v>160000</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
@@ -3123,7 +3124,7 @@
         <v>8</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M7" s="8" t="n">
         <v>5</v>
@@ -3144,10 +3145,10 @@
         <v>80</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U7" s="9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3161,7 +3162,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>1</v>
@@ -3170,7 +3171,7 @@
         <v>160000</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>20</v>
@@ -3185,7 +3186,7 @@
         <v>8</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>5</v>
@@ -3209,7 +3210,7 @@
         <v>100</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3223,7 +3224,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>1</v>
@@ -3232,7 +3233,7 @@
         <v>160000</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
@@ -3247,7 +3248,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="M9" s="8" t="n">
         <v>5</v>
@@ -3271,7 +3272,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3285,7 +3286,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>1</v>
@@ -3294,7 +3295,7 @@
         <v>160000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
@@ -3309,7 +3310,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>5</v>
@@ -3333,7 +3334,7 @@
         <v>100</v>
       </c>
       <c r="U10" s="9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3347,7 +3348,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>1</v>
@@ -3356,7 +3357,7 @@
         <v>160000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>20</v>
@@ -3371,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>5</v>
@@ -3395,7 +3396,7 @@
         <v>100</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3409,7 +3410,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>1</v>
@@ -3418,7 +3419,7 @@
         <v>160000</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>20</v>
@@ -3433,7 +3434,7 @@
         <v>8</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>5</v>
@@ -3454,10 +3455,10 @@
         <v>80</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U12" s="9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3471,7 +3472,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>1</v>
@@ -3480,7 +3481,7 @@
         <v>160000</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>20</v>
@@ -3495,7 +3496,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>5</v>
@@ -3519,7 +3520,7 @@
         <v>200</v>
       </c>
       <c r="U13" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3533,7 +3534,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>1</v>
@@ -3542,7 +3543,7 @@
         <v>160000</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>20</v>
@@ -3557,7 +3558,7 @@
         <v>8</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>5</v>
@@ -3581,7 +3582,7 @@
         <v>200</v>
       </c>
       <c r="U14" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3595,7 +3596,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>1</v>
@@ -3604,7 +3605,7 @@
         <v>160000</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>20</v>
@@ -3619,7 +3620,7 @@
         <v>8</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>5</v>
@@ -3643,7 +3644,7 @@
         <v>200</v>
       </c>
       <c r="U15" s="9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3657,7 +3658,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1</v>
@@ -3666,7 +3667,7 @@
         <v>160000</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>20</v>
@@ -3681,7 +3682,7 @@
         <v>8</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>5</v>
@@ -3705,7 +3706,7 @@
         <v>200</v>
       </c>
       <c r="U16" s="9" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3719,7 +3720,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>1</v>
@@ -3728,7 +3729,7 @@
         <v>160000</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>20</v>
@@ -3743,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M17" s="8" t="n">
         <v>5</v>
@@ -3764,10 +3765,10 @@
         <v>80</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U17" s="9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3781,7 +3782,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>1</v>
@@ -3790,7 +3791,7 @@
         <v>160000</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>20</v>
@@ -3805,7 +3806,7 @@
         <v>8</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>5</v>
@@ -3829,7 +3830,7 @@
         <v>300</v>
       </c>
       <c r="U18" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3843,7 +3844,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>1</v>
@@ -3852,7 +3853,7 @@
         <v>160000</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>20</v>
@@ -3867,7 +3868,7 @@
         <v>8</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>5</v>
@@ -3891,7 +3892,7 @@
         <v>300</v>
       </c>
       <c r="U19" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3905,7 +3906,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>1</v>
@@ -3914,7 +3915,7 @@
         <v>160000</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>20</v>
@@ -3929,7 +3930,7 @@
         <v>8</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>5</v>
@@ -3953,7 +3954,7 @@
         <v>300</v>
       </c>
       <c r="U20" s="9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3967,7 +3968,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>1</v>
@@ -3976,7 +3977,7 @@
         <v>160000</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>20</v>
@@ -3991,7 +3992,7 @@
         <v>8</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>5</v>
@@ -4015,56 +4016,56 @@
         <v>300</v>
       </c>
       <c r="U21" s="9" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="10" t="n">
+      <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="n">
         <v>160000</v>
       </c>
-      <c r="G22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="10" t="s">
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="8" t="n">
         <v>8</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N22" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="P22" s="12" t="n">
+      <c r="N22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>50</v>
       </c>
       <c r="Q22" s="2" t="n">
@@ -4074,10 +4075,10 @@
         <v>80</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U22" s="9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4115,7 +4116,7 @@
         <v>8</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>47</v>
+        <v>-10000</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>5</v>
@@ -4139,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4153,7 +4154,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>1</v>
@@ -4162,7 +4163,7 @@
         <v>160000</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>24</v>
@@ -4177,7 +4178,7 @@
         <v>8</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>5</v>
@@ -4201,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4215,7 +4216,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>1</v>
@@ -4224,7 +4225,7 @@
         <v>160000</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>24</v>
@@ -4239,7 +4240,7 @@
         <v>8</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="M25" s="8" t="n">
         <v>5</v>
@@ -4263,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="9" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4277,7 +4278,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>1</v>
@@ -4286,7 +4287,7 @@
         <v>160000</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>24</v>
@@ -4301,7 +4302,7 @@
         <v>8</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>5</v>
@@ -4325,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="9" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4339,7 +4340,7 @@
         <v>19</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>1</v>
@@ -4348,7 +4349,7 @@
         <v>160000</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>24</v>
@@ -4363,7 +4364,7 @@
         <v>8</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="M27" s="8" t="n">
         <v>5</v>
@@ -4384,10 +4385,10 @@
         <v>80</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U27" s="9" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4425,7 +4426,7 @@
         <v>8</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>5</v>
@@ -4446,10 +4447,10 @@
         <v>80</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U28" s="9" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4463,7 +4464,7 @@
         <v>19</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>1</v>
@@ -4472,7 +4473,7 @@
         <v>160000</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>24</v>
@@ -4487,7 +4488,7 @@
         <v>8</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>5</v>
@@ -4511,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="U29" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4525,7 +4526,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>1</v>
@@ -4534,7 +4535,7 @@
         <v>160000</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>24</v>
@@ -4549,7 +4550,7 @@
         <v>8</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M30" s="8" t="n">
         <v>5</v>
@@ -4573,7 +4574,7 @@
         <v>100</v>
       </c>
       <c r="U30" s="9" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4587,7 +4588,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>1</v>
@@ -4596,7 +4597,7 @@
         <v>160000</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>24</v>
@@ -4611,7 +4612,7 @@
         <v>8</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="M31" s="8" t="n">
         <v>5</v>
@@ -4635,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="U31" s="9" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4649,7 +4650,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>1</v>
@@ -4658,7 +4659,7 @@
         <v>160000</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>24</v>
@@ -4673,7 +4674,7 @@
         <v>8</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>5</v>
@@ -4694,10 +4695,10 @@
         <v>80</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U32" s="9" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4711,7 +4712,7 @@
         <v>19</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>1</v>
@@ -4720,7 +4721,7 @@
         <v>160000</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>24</v>
@@ -4735,7 +4736,7 @@
         <v>8</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>5</v>
@@ -4756,10 +4757,10 @@
         <v>80</v>
       </c>
       <c r="T33" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U33" s="9" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4773,7 +4774,7 @@
         <v>19</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>1</v>
@@ -4782,7 +4783,7 @@
         <v>160000</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>24</v>
@@ -4797,7 +4798,7 @@
         <v>8</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>5</v>
@@ -4821,7 +4822,7 @@
         <v>200</v>
       </c>
       <c r="U34" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4835,7 +4836,7 @@
         <v>19</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="11" t="n">
         <v>1</v>
@@ -4844,7 +4845,7 @@
         <v>160000</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>24</v>
@@ -4859,7 +4860,7 @@
         <v>8</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M35" s="8" t="n">
         <v>5</v>
@@ -4883,7 +4884,7 @@
         <v>200</v>
       </c>
       <c r="U35" s="9" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,7 +4898,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>1</v>
@@ -4906,7 +4907,7 @@
         <v>160000</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>24</v>
@@ -4921,7 +4922,7 @@
         <v>8</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="M36" s="8" t="n">
         <v>5</v>
@@ -4945,7 +4946,7 @@
         <v>200</v>
       </c>
       <c r="U36" s="9" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4959,7 +4960,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>1</v>
@@ -4968,7 +4969,7 @@
         <v>160000</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>24</v>
@@ -4983,7 +4984,7 @@
         <v>8</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="M37" s="8" t="n">
         <v>5</v>
@@ -5004,10 +5005,10 @@
         <v>80</v>
       </c>
       <c r="T37" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="U37" s="9" t="n">
         <v>300</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5021,7 +5022,7 @@
         <v>19</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>1</v>
@@ -5030,7 +5031,7 @@
         <v>160000</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>24</v>
@@ -5045,7 +5046,7 @@
         <v>8</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>5</v>
@@ -5066,10 +5067,10 @@
         <v>80</v>
       </c>
       <c r="T38" s="9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U38" s="9" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5083,7 +5084,7 @@
         <v>19</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>1</v>
@@ -5092,7 +5093,7 @@
         <v>160000</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>24</v>
@@ -5107,7 +5108,7 @@
         <v>8</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>5</v>
@@ -5131,7 +5132,7 @@
         <v>300</v>
       </c>
       <c r="U39" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5145,7 +5146,7 @@
         <v>19</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>1</v>
@@ -5154,7 +5155,7 @@
         <v>160000</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>24</v>
@@ -5169,7 +5170,7 @@
         <v>8</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="M40" s="8" t="n">
         <v>5</v>
@@ -5193,7 +5194,7 @@
         <v>300</v>
       </c>
       <c r="U40" s="9" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5207,7 +5208,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>1</v>
@@ -5216,7 +5217,7 @@
         <v>160000</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>24</v>
@@ -5231,7 +5232,7 @@
         <v>8</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="M41" s="8" t="n">
         <v>5</v>
@@ -5255,55 +5256,56 @@
         <v>300</v>
       </c>
       <c r="U41" s="9" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <f aca="false">ROUND(F42*0.0025,0)*D42</f>
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3"/>
-      <c r="P42" s="2" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P42" s="12" t="n">
         <v>50</v>
       </c>
       <c r="Q42" s="2" t="n">
@@ -5312,78 +5314,107 @@
       <c r="R42" s="2" t="n">
         <v>80</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3"/>
+      <c r="T42" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="43" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P43" s="12" t="n">
+        <v>50</v>
+      </c>
       <c r="Q43" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T43" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>793</v>
+        <v>312</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3"/>
+        <f aca="false">ROUND(F44*0.0025,0)*D44</f>
+        <v>1</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="I44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J44" s="3"/>
+      <c r="J44" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="K44" s="3" t="n">
         <v>8</v>
       </c>
@@ -5397,42 +5428,43 @@
         <v>0</v>
       </c>
       <c r="O44" s="3"/>
+      <c r="P44" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="Q44" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>336</v>
+        <v>203</v>
       </c>
       <c r="G45" s="3" t="n">
-        <f aca="false">ROUND(F45*0.0025,0)*D45</f>
-        <v>1</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H45" s="3"/>
       <c r="I45" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="J45" s="3"/>
       <c r="K45" s="3" t="n">
         <v>8</v>
       </c>
@@ -5446,22 +5478,16 @@
         <v>0</v>
       </c>
       <c r="O45" s="3"/>
-      <c r="P45" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="Q45" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>19</v>
@@ -5473,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>333</v>
+        <v>793</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>0</v>
@@ -5502,10 +5528,10 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>19</v>
@@ -5517,20 +5543,20 @@
         <v>1</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="G47" s="3" t="n">
         <f aca="false">ROUND(F47*0.0025,0)*D47</f>
         <v>1</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K47" s="3" t="n">
         <v>8</v>
@@ -5552,40 +5578,36 @@
         <v>1</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>804</v>
+        <v>333</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>24</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H48" s="3"/>
       <c r="I48" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J48" s="3" t="n">
-        <v>27</v>
-      </c>
+      <c r="J48" s="3"/>
       <c r="K48" s="3" t="n">
         <v>8</v>
       </c>
@@ -5599,76 +5621,71 @@
         <v>0</v>
       </c>
       <c r="O48" s="3"/>
-      <c r="P48" s="2" t="n">
-        <v>15</v>
-      </c>
       <c r="Q48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R48" s="2" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>45</v>
+      <c r="A49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="4"/>
+      <c r="D49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <f aca="false">ROUND(F49*0.0025,0)*D49</f>
+        <v>1</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
       <c r="P49" s="2" t="n">
         <v>50</v>
       </c>
       <c r="Q49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S49" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="R49" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>19</v>
@@ -5680,19 +5697,19 @@
         <v>1</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>778</v>
+        <v>804</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>51</v>
+      <c r="J50" s="3" t="n">
+        <v>27</v>
       </c>
       <c r="K50" s="3" t="n">
         <v>8</v>
@@ -5708,87 +5725,100 @@
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4"/>
+      <c r="P51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="Q50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>837</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="3"/>
       <c r="Q51" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="S51" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>171</v>
+        <v>778</v>
       </c>
       <c r="G52" s="3" t="n">
-        <f aca="false">ROUND(F52*0.0025,0)*D52</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="I52" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="K52" s="3" t="n">
         <v>8</v>
       </c>
@@ -5802,16 +5832,22 @@
         <v>0</v>
       </c>
       <c r="O52" s="3"/>
+      <c r="P52" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="Q52" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>19</v>
@@ -5820,13 +5856,12 @@
         <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>136</v>
+        <v>837</v>
       </c>
       <c r="G53" s="3" t="n">
-        <f aca="false">ROUND(F53*0.0025,0)*D53</f>
         <v>0</v>
       </c>
       <c r="H53" s="3"/>
@@ -5853,10 +5888,10 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>19</v>
@@ -5868,9 +5903,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1010</v>
+        <v>171</v>
       </c>
       <c r="G54" s="3" t="n">
+        <f aca="false">ROUND(F54*0.0025,0)*D54</f>
         <v>0</v>
       </c>
       <c r="H54" s="3"/>
@@ -5897,10 +5933,10 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>19</v>
@@ -5909,12 +5945,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>658</v>
+        <v>136</v>
       </c>
       <c r="G55" s="3" t="n">
+        <f aca="false">ROUND(F55*0.0025,0)*D55</f>
         <v>0</v>
       </c>
       <c r="H55" s="3"/>
@@ -5941,35 +5978,31 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1114</v>
+        <v>1010</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H56" s="3"/>
       <c r="I56" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="J56" s="3"/>
       <c r="K56" s="3" t="n">
         <v>8</v>
       </c>
@@ -5983,72 +6016,60 @@
         <v>0</v>
       </c>
       <c r="O56" s="3"/>
-      <c r="P56" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="Q56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R56" s="2" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>66</v>
+      <c r="A57" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="4"/>
-      <c r="P57" s="2"/>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>658</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3"/>
       <c r="Q57" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="S57" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>19</v>
@@ -6060,20 +6081,19 @@
         <v>1</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>521</v>
+        <v>1114</v>
       </c>
       <c r="G58" s="3" t="n">
-        <f aca="false">ROUND(F58*0.0025,0)*D58</f>
         <v>1</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>8</v>
@@ -6089,87 +6109,97 @@
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R58" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <f aca="false">ROUND(F59*0.0025,0)*D59</f>
-        <v>0</v>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3"/>
+      <c r="I59" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4"/>
+      <c r="P59" s="2"/>
       <c r="Q59" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="S59" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>574</v>
+        <v>521</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3"/>
+        <f aca="false">ROUND(F60*0.0025,0)*D60</f>
+        <v>1</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="I60" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J60" s="3"/>
+      <c r="J60" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="K60" s="3" t="n">
         <v>8</v>
       </c>
@@ -6183,16 +6213,22 @@
         <v>0</v>
       </c>
       <c r="O60" s="3"/>
+      <c r="P60" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="Q60" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>19</v>
@@ -6201,10 +6237,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G61" s="3" t="n">
         <f aca="false">ROUND(F61*0.0025,0)*D61</f>
@@ -6234,10 +6270,10 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>19</v>
@@ -6246,13 +6282,12 @@
         <v>0</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>171</v>
+        <v>574</v>
       </c>
       <c r="G62" s="3" t="n">
-        <f aca="false">ROUND(F62*0.0025,0)*D62</f>
         <v>0</v>
       </c>
       <c r="H62" s="3"/>
@@ -6279,10 +6314,10 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>19</v>
@@ -6291,12 +6326,13 @@
         <v>0</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>607</v>
+        <v>73</v>
       </c>
       <c r="G63" s="3" t="n">
+        <f aca="false">ROUND(F63*0.0025,0)*D63</f>
         <v>0</v>
       </c>
       <c r="H63" s="3"/>
@@ -6323,10 +6359,10 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>19</v>
@@ -6335,12 +6371,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>340</v>
+        <v>171</v>
       </c>
       <c r="G64" s="3" t="n">
+        <f aca="false">ROUND(F64*0.0025,0)*D64</f>
         <v>0</v>
       </c>
       <c r="H64" s="3"/>
@@ -6367,10 +6404,10 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>19</v>
@@ -6379,13 +6416,12 @@
         <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>191</v>
+        <v>607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <f aca="false">ROUND(F65*0.0025,0)*D65</f>
         <v>0</v>
       </c>
       <c r="H65" s="3"/>
@@ -6412,10 +6448,10 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>19</v>
@@ -6427,7 +6463,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>729</v>
+        <v>340</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
@@ -6455,37 +6491,33 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>88</v>
+      <c r="A67" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="G67" s="3" t="n">
         <f aca="false">ROUND(F67*0.0025,0)*D67</f>
-        <v>1</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H67" s="3"/>
       <c r="I67" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>90</v>
-      </c>
+      <c r="J67" s="3"/>
       <c r="K67" s="3" t="n">
         <v>8</v>
       </c>
@@ -6499,22 +6531,16 @@
         <v>0</v>
       </c>
       <c r="O67" s="3"/>
-      <c r="P67" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="Q67" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="R67" s="2" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>19</v>
@@ -6526,10 +6552,9 @@
         <v>1</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>22</v>
+        <v>729</v>
       </c>
       <c r="G68" s="3" t="n">
-        <f aca="false">ROUND(F68*0.0025,0)*D68</f>
         <v>0</v>
       </c>
       <c r="H68" s="3"/>
@@ -6555,33 +6580,37 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>94</v>
+      <c r="A69" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="G69" s="3" t="n">
         <f aca="false">ROUND(F69*0.0025,0)*D69</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="I69" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="K69" s="3" t="n">
         <v>8</v>
       </c>
@@ -6595,41 +6624,44 @@
         <v>0</v>
       </c>
       <c r="O69" s="3"/>
+      <c r="P69" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="Q69" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>698</v>
+        <v>22</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>97</v>
-      </c>
+        <f aca="false">ROUND(F70*0.0025,0)*D70</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="3"/>
       <c r="I70" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="J70" s="3"/>
       <c r="K70" s="3" t="n">
         <v>8</v>
       </c>
@@ -6643,22 +6675,16 @@
         <v>0</v>
       </c>
       <c r="O70" s="3"/>
-      <c r="P70" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="Q70" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>19</v>
@@ -6670,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="G71" s="3" t="n">
         <f aca="false">ROUND(F71*0.0025,0)*D71</f>
@@ -6700,32 +6726,35 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>93</v>
+        <v>698</v>
       </c>
       <c r="G72" s="3" t="n">
-        <f aca="false">ROUND(F72*0.0025,0)*D72</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="I72" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J72" s="3"/>
+      <c r="J72" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="K72" s="3" t="n">
         <v>8</v>
       </c>
@@ -6739,41 +6768,44 @@
         <v>0</v>
       </c>
       <c r="O72" s="3"/>
+      <c r="P72" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="Q72" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>97</v>
-      </c>
+        <f aca="false">ROUND(F73*0.0025,0)*D73</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="3"/>
       <c r="I73" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J73" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="J73" s="3"/>
       <c r="K73" s="3" t="n">
         <v>8</v>
       </c>
@@ -6787,101 +6819,86 @@
         <v>0</v>
       </c>
       <c r="O73" s="3"/>
-      <c r="P73" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="Q73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R73" s="2" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>106</v>
+      <c r="A74" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>986</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K74" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="4"/>
-      <c r="P74" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <f aca="false">ROUND(F74*0.0025,0)*D74</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
       <c r="Q74" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="R74" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="S74" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="G75" s="3" t="n">
-        <f aca="false">ROUND(F75*0.0025,0)*D75</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="I75" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J75" s="3"/>
+      <c r="J75" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="K75" s="3" t="n">
         <v>8</v>
       </c>
@@ -6895,85 +6912,101 @@
         <v>0</v>
       </c>
       <c r="O75" s="3"/>
+      <c r="P75" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="Q75" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="R75" s="2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>112</v>
+      <c r="A76" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>313</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3"/>
+      <c r="D76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>986</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="4"/>
+      <c r="P76" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="Q76" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="S76" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>115</v>
-      </c>
+        <f aca="false">ROUND(F77*0.0025,0)*D77</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="3"/>
       <c r="I77" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J77" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="J77" s="3"/>
       <c r="K77" s="3" t="n">
         <v>8</v>
       </c>
@@ -6987,22 +7020,16 @@
         <v>0</v>
       </c>
       <c r="O77" s="3"/>
-      <c r="P77" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="Q77" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="R77" s="2" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>19</v>
@@ -7014,10 +7041,9 @@
         <v>1</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>119</v>
+        <v>313</v>
       </c>
       <c r="G78" s="3" t="n">
-        <f aca="false">ROUND(F78*0.0025,0)*D78</f>
         <v>0</v>
       </c>
       <c r="H78" s="3"/>
@@ -7038,94 +7064,103 @@
         <v>0</v>
       </c>
       <c r="O78" s="3"/>
+      <c r="Q78" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B79" s="13" t="s">
+      <c r="A79" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="3"/>
+      <c r="P79" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="I79" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J79" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K79" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="M79" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O79" s="3"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="I80" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J80" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K80" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L80" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M80" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="N80" s="13" t="n">
-        <v>5</v>
+      <c r="G80" s="3" t="n">
+        <f aca="false">ROUND(F80*0.0025,0)*D80</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -7164,7 +7199,7 @@
         <v>8</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M81" s="13" t="n">
         <v>5</v>
@@ -7209,7 +7244,7 @@
         <v>8</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M82" s="13" t="n">
         <v>5</v>
@@ -7254,7 +7289,7 @@
         <v>8</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M83" s="13" t="n">
         <v>5</v>
@@ -7299,7 +7334,7 @@
         <v>8</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M84" s="13" t="n">
         <v>5</v>
@@ -7344,7 +7379,7 @@
         <v>8</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M85" s="13" t="n">
         <v>5</v>
@@ -7389,7 +7424,7 @@
         <v>8</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M86" s="13" t="n">
         <v>5</v>
@@ -7434,7 +7469,7 @@
         <v>8</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M87" s="13" t="n">
         <v>5</v>
@@ -7479,7 +7514,7 @@
         <v>8</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M88" s="13" t="n">
         <v>5</v>
@@ -7524,7 +7559,7 @@
         <v>8</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M89" s="13" t="n">
         <v>5</v>
@@ -7569,7 +7604,7 @@
         <v>8</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M90" s="13" t="n">
         <v>5</v>
@@ -7614,7 +7649,7 @@
         <v>8</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M91" s="13" t="n">
         <v>5</v>
@@ -7659,7 +7694,7 @@
         <v>8</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M92" s="13" t="n">
         <v>5</v>
@@ -7704,7 +7739,7 @@
         <v>8</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="M93" s="13" t="n">
         <v>5</v>
@@ -7749,7 +7784,7 @@
         <v>8</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M94" s="13" t="n">
         <v>5</v>
@@ -7794,7 +7829,7 @@
         <v>8</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M95" s="13" t="n">
         <v>5</v>
@@ -7839,7 +7874,7 @@
         <v>8</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M96" s="13" t="n">
         <v>5</v>
@@ -7884,7 +7919,7 @@
         <v>8</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M97" s="13" t="n">
         <v>5</v>
@@ -7929,7 +7964,7 @@
         <v>8</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M98" s="13" t="n">
         <v>5</v>
@@ -7974,7 +8009,7 @@
         <v>8</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="M99" s="13" t="n">
         <v>5</v>
@@ -8019,7 +8054,7 @@
         <v>8</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M100" s="13" t="n">
         <v>5</v>
@@ -8064,7 +8099,7 @@
         <v>8</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M101" s="13" t="n">
         <v>5</v>
@@ -8109,7 +8144,7 @@
         <v>8</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M102" s="13" t="n">
         <v>5</v>
@@ -8120,93 +8155,94 @@
       <c r="O102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B103" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C103" s="14" t="s">
+      <c r="A103" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C103" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I103" s="14" t="s">
+      <c r="D103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I103" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J103" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K103" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" s="14" t="n">
-        <v>5</v>
+      <c r="J103" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K103" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="13" t="n">
+        <v>115</v>
       </c>
       <c r="M103" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N103" s="14" t="n">
-        <v>2</v>
+      <c r="N103" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="O103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B104" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C104" s="14" t="s">
+      <c r="A104" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I104" s="14" t="s">
+      <c r="D104" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I104" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J104" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K104" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="14" t="n">
-        <v>10</v>
+      <c r="J104" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K104" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="13" t="n">
+        <v>120</v>
       </c>
       <c r="M104" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N104" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="N104" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
@@ -8243,7 +8279,7 @@
         <v>8</v>
       </c>
       <c r="L105" s="14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M105" s="13" t="n">
         <v>5</v>
@@ -8251,6 +8287,7 @@
       <c r="N105" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="O105" s="3"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="14" t="s">
@@ -8287,7 +8324,7 @@
         <v>8</v>
       </c>
       <c r="L106" s="14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M106" s="13" t="n">
         <v>5</v>
@@ -8331,7 +8368,7 @@
         <v>8</v>
       </c>
       <c r="L107" s="14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>5</v>
@@ -8375,7 +8412,7 @@
         <v>8</v>
       </c>
       <c r="L108" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>5</v>
@@ -8419,7 +8456,7 @@
         <v>8</v>
       </c>
       <c r="L109" s="14" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M109" s="13" t="n">
         <v>5</v>
@@ -8463,7 +8500,7 @@
         <v>8</v>
       </c>
       <c r="L110" s="14" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>5</v>
@@ -8507,7 +8544,7 @@
         <v>8</v>
       </c>
       <c r="L111" s="14" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>5</v>
@@ -8551,7 +8588,7 @@
         <v>8</v>
       </c>
       <c r="L112" s="14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>5</v>
@@ -8595,7 +8632,7 @@
         <v>8</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>5</v>
@@ -8639,7 +8676,7 @@
         <v>8</v>
       </c>
       <c r="L114" s="14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>5</v>
@@ -8683,7 +8720,7 @@
         <v>8</v>
       </c>
       <c r="L115" s="14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M115" s="13" t="n">
         <v>5</v>
@@ -8727,7 +8764,7 @@
         <v>8</v>
       </c>
       <c r="L116" s="14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>5</v>
@@ -8771,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="L117" s="14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>5</v>
@@ -8815,7 +8852,7 @@
         <v>8</v>
       </c>
       <c r="L118" s="14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>5</v>
@@ -8859,7 +8896,7 @@
         <v>8</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>5</v>
@@ -8867,7 +8904,6 @@
       <c r="N119" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="O119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="14" t="s">
@@ -8904,7 +8940,7 @@
         <v>8</v>
       </c>
       <c r="L120" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M120" s="13" t="n">
         <v>5</v>
@@ -8948,7 +8984,7 @@
         <v>8</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M121" s="13" t="n">
         <v>5</v>
@@ -8956,6 +8992,7 @@
       <c r="N121" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="O121" s="3"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
@@ -8992,7 +9029,7 @@
         <v>8</v>
       </c>
       <c r="L122" s="14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>5</v>
@@ -9036,7 +9073,7 @@
         <v>8</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>5</v>
@@ -9080,7 +9117,7 @@
         <v>8</v>
       </c>
       <c r="L124" s="14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>5</v>
@@ -9124,7 +9161,7 @@
         <v>8</v>
       </c>
       <c r="L125" s="14" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>5</v>
@@ -9168,7 +9205,7 @@
         <v>8</v>
       </c>
       <c r="L126" s="14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M126" s="13" t="n">
         <v>5</v>
@@ -9178,16 +9215,104 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
-      <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
-      <c r="N127" s="2"/>
+      <c r="A127" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I127" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J127" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K127" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L127" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="M127" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N127" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B128" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I128" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J128" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K128" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L128" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="M128" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+      <c r="M129" s="2"/>
+      <c r="N129" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S49" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
-    <hyperlink ref="S57" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
+    <hyperlink ref="S51" r:id="rId1" display="http://www.ncbi.nlm.nih.gov/pubmed?term=PMID:%2018829959"/>
+    <hyperlink ref="S59" r:id="rId2" display="https://www.jneurosci.org/content/30/5/1595.long"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="137">
   <si>
     <t xml:space="preserve">Hippocampome_Neurons_Names</t>
   </si>
@@ -2700,7 +2700,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U129"/>
+  <dimension ref="A1:U131"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
@@ -8245,47 +8245,47 @@
       <c r="O104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B105" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C105" s="14" t="s">
+      <c r="A105" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C105" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I105" s="14" t="s">
+      <c r="D105" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I105" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J105" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K105" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L105" s="14" t="n">
-        <v>5</v>
+      <c r="J105" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K105" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="13" t="n">
+        <v>-10000</v>
       </c>
       <c r="M105" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="N105" s="14" t="n">
-        <v>2</v>
+      <c r="N105" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="O105" s="3"/>
     </row>
@@ -8324,7 +8324,7 @@
         <v>8</v>
       </c>
       <c r="L106" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M106" s="13" t="n">
         <v>5</v>
@@ -8332,6 +8332,7 @@
       <c r="N106" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="O106" s="3"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="14" t="s">
@@ -8368,7 +8369,7 @@
         <v>8</v>
       </c>
       <c r="L107" s="14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M107" s="13" t="n">
         <v>5</v>
@@ -8412,7 +8413,7 @@
         <v>8</v>
       </c>
       <c r="L108" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M108" s="13" t="n">
         <v>5</v>
@@ -8456,7 +8457,7 @@
         <v>8</v>
       </c>
       <c r="L109" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M109" s="13" t="n">
         <v>5</v>
@@ -8500,7 +8501,7 @@
         <v>8</v>
       </c>
       <c r="L110" s="14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M110" s="13" t="n">
         <v>5</v>
@@ -8544,7 +8545,7 @@
         <v>8</v>
       </c>
       <c r="L111" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M111" s="13" t="n">
         <v>5</v>
@@ -8588,7 +8589,7 @@
         <v>8</v>
       </c>
       <c r="L112" s="14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M112" s="13" t="n">
         <v>5</v>
@@ -8632,7 +8633,7 @@
         <v>8</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M113" s="13" t="n">
         <v>5</v>
@@ -8676,7 +8677,7 @@
         <v>8</v>
       </c>
       <c r="L114" s="14" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M114" s="13" t="n">
         <v>5</v>
@@ -8720,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="L115" s="14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M115" s="13" t="n">
         <v>5</v>
@@ -8764,7 +8765,7 @@
         <v>8</v>
       </c>
       <c r="L116" s="14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M116" s="13" t="n">
         <v>5</v>
@@ -8808,7 +8809,7 @@
         <v>8</v>
       </c>
       <c r="L117" s="14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M117" s="13" t="n">
         <v>5</v>
@@ -8852,7 +8853,7 @@
         <v>8</v>
       </c>
       <c r="L118" s="14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M118" s="13" t="n">
         <v>5</v>
@@ -8896,7 +8897,7 @@
         <v>8</v>
       </c>
       <c r="L119" s="14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M119" s="13" t="n">
         <v>5</v>
@@ -8940,7 +8941,7 @@
         <v>8</v>
       </c>
       <c r="L120" s="14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M120" s="13" t="n">
         <v>5</v>
@@ -8984,7 +8985,7 @@
         <v>8</v>
       </c>
       <c r="L121" s="14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="M121" s="13" t="n">
         <v>5</v>
@@ -8992,7 +8993,6 @@
       <c r="N121" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="O121" s="3"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
@@ -9029,7 +9029,7 @@
         <v>8</v>
       </c>
       <c r="L122" s="14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M122" s="13" t="n">
         <v>5</v>
@@ -9037,6 +9037,7 @@
       <c r="N122" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="O122" s="3"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="14" t="s">
@@ -9073,7 +9074,7 @@
         <v>8</v>
       </c>
       <c r="L123" s="14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M123" s="13" t="n">
         <v>5</v>
@@ -9117,7 +9118,7 @@
         <v>8</v>
       </c>
       <c r="L124" s="14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M124" s="13" t="n">
         <v>5</v>
@@ -9161,7 +9162,7 @@
         <v>8</v>
       </c>
       <c r="L125" s="14" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M125" s="13" t="n">
         <v>5</v>
@@ -9205,7 +9206,7 @@
         <v>8</v>
       </c>
       <c r="L126" s="14" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M126" s="13" t="n">
         <v>5</v>
@@ -9249,7 +9250,7 @@
         <v>8</v>
       </c>
       <c r="L127" s="14" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="M127" s="13" t="n">
         <v>5</v>
@@ -9293,7 +9294,7 @@
         <v>8</v>
       </c>
       <c r="L128" s="14" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="M128" s="13" t="n">
         <v>5</v>
@@ -9303,11 +9304,99 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
-      <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
+      <c r="A129" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B129" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I129" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J129" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K129" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L129" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="M129" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I130" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J130" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K130" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L130" s="14" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N130" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
